--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -398,6 +398,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AR14"/>
+  <cols>
+    <col min="1" max="1" width="24.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" customWidth="1"/>
+    <col min="5" max="5" width="3.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="8.83203125" customWidth="1"/>
+    <col min="10" max="10" width="3.83203125" customWidth="1"/>
+    <col min="11" max="11" width="24.83203125" customWidth="1"/>
+    <col min="12" max="12" width="16.83203125" customWidth="1"/>
+    <col min="13" max="13" width="10.83203125" customWidth="1"/>
+    <col min="14" max="14" width="8.83203125" customWidth="1"/>
+    <col min="15" max="15" width="3.83203125" customWidth="1"/>
+    <col min="16" max="16" width="24.83203125" customWidth="1"/>
+    <col min="17" max="17" width="16.83203125" customWidth="1"/>
+    <col min="18" max="18" width="10.83203125" customWidth="1"/>
+    <col min="19" max="19" width="8.83203125" customWidth="1"/>
+    <col min="20" max="20" width="3.83203125" customWidth="1"/>
+    <col min="21" max="21" width="24.83203125" customWidth="1"/>
+    <col min="22" max="22" width="16.83203125" customWidth="1"/>
+    <col min="23" max="23" width="10.83203125" customWidth="1"/>
+    <col min="24" max="24" width="8.83203125" customWidth="1"/>
+    <col min="25" max="25" width="3.83203125" customWidth="1"/>
+    <col min="26" max="26" width="24.83203125" customWidth="1"/>
+    <col min="27" max="27" width="16.83203125" customWidth="1"/>
+    <col min="28" max="28" width="10.83203125" customWidth="1"/>
+    <col min="29" max="29" width="8.83203125" customWidth="1"/>
+    <col min="30" max="30" width="3.83203125" customWidth="1"/>
+    <col min="31" max="31" width="24.83203125" customWidth="1"/>
+    <col min="32" max="32" width="16.83203125" customWidth="1"/>
+    <col min="33" max="33" width="10.83203125" customWidth="1"/>
+    <col min="34" max="34" width="8.83203125" customWidth="1"/>
+    <col min="35" max="35" width="3.83203125" customWidth="1"/>
+    <col min="36" max="36" width="24.83203125" customWidth="1"/>
+    <col min="37" max="37" width="16.83203125" customWidth="1"/>
+    <col min="38" max="38" width="10.83203125" customWidth="1"/>
+    <col min="39" max="39" width="8.83203125" customWidth="1"/>
+    <col min="40" max="40" width="3.83203125" customWidth="1"/>
+    <col min="41" max="41" width="24.83203125" customWidth="1"/>
+    <col min="42" max="42" width="16.83203125" customWidth="1"/>
+    <col min="43" max="43" width="10.83203125" customWidth="1"/>
+    <col min="44" max="44" width="8.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -406,6 +452,9 @@
       <c r="B1" t="str">
         <v/>
       </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
       <c r="D1" t="str">
         <v/>
       </c>
@@ -418,6 +467,9 @@
       <c r="G1" t="str">
         <v/>
       </c>
+      <c r="H1" t="str">
+        <v/>
+      </c>
       <c r="I1" t="str">
         <v/>
       </c>
@@ -445,6 +497,9 @@
       <c r="Q1" t="str">
         <v/>
       </c>
+      <c r="R1" t="str">
+        <v/>
+      </c>
       <c r="S1" t="str">
         <v/>
       </c>
@@ -457,6 +512,9 @@
       <c r="V1" t="str">
         <v/>
       </c>
+      <c r="W1" t="str">
+        <v/>
+      </c>
       <c r="X1" t="str">
         <v/>
       </c>
@@ -469,6 +527,9 @@
       <c r="AA1" t="str">
         <v/>
       </c>
+      <c r="AB1" t="str">
+        <v/>
+      </c>
       <c r="AC1" t="str">
         <v/>
       </c>
@@ -481,6 +542,9 @@
       <c r="AF1" t="str">
         <v/>
       </c>
+      <c r="AG1" t="str">
+        <v/>
+      </c>
       <c r="AH1" t="str">
         <v/>
       </c>
@@ -493,6 +557,9 @@
       <c r="AK1" t="str">
         <v/>
       </c>
+      <c r="AL1" t="str">
+        <v/>
+      </c>
       <c r="AM1" t="str">
         <v/>
       </c>
@@ -503,6 +570,9 @@
         <v>Sumit's Team</v>
       </c>
       <c r="AP1" t="str">
+        <v/>
+      </c>
+      <c r="AQ1" t="str">
         <v/>
       </c>
       <c r="AR1" t="str">
@@ -516,6 +586,9 @@
       <c r="B2" t="str">
         <v>IPL Team</v>
       </c>
+      <c r="C2" t="str">
+        <v>Price (Cr)</v>
+      </c>
       <c r="D2" t="str">
         <v>Points</v>
       </c>
@@ -528,6 +601,9 @@
       <c r="G2" t="str">
         <v>IPL Team</v>
       </c>
+      <c r="H2" t="str">
+        <v>Price (Cr)</v>
+      </c>
       <c r="I2" t="str">
         <v>Points</v>
       </c>
@@ -555,6 +631,9 @@
       <c r="Q2" t="str">
         <v>IPL Team</v>
       </c>
+      <c r="R2" t="str">
+        <v>Price (Cr)</v>
+      </c>
       <c r="S2" t="str">
         <v>Points</v>
       </c>
@@ -567,6 +646,9 @@
       <c r="V2" t="str">
         <v>IPL Team</v>
       </c>
+      <c r="W2" t="str">
+        <v>Price (Cr)</v>
+      </c>
       <c r="X2" t="str">
         <v>Points</v>
       </c>
@@ -579,6 +661,9 @@
       <c r="AA2" t="str">
         <v>IPL Team</v>
       </c>
+      <c r="AB2" t="str">
+        <v>Price (Cr)</v>
+      </c>
       <c r="AC2" t="str">
         <v>Points</v>
       </c>
@@ -591,6 +676,9 @@
       <c r="AF2" t="str">
         <v>IPL Team</v>
       </c>
+      <c r="AG2" t="str">
+        <v>Price (Cr)</v>
+      </c>
       <c r="AH2" t="str">
         <v>Points</v>
       </c>
@@ -603,6 +691,9 @@
       <c r="AK2" t="str">
         <v>IPL Team</v>
       </c>
+      <c r="AL2" t="str">
+        <v>Price (Cr)</v>
+      </c>
       <c r="AM2" t="str">
         <v>Points</v>
       </c>
@@ -614,6 +705,9 @@
       </c>
       <c r="AP2" t="str">
         <v>IPL Team</v>
+      </c>
+      <c r="AQ2" t="str">
+        <v>Price (Cr)</v>
       </c>
       <c r="AR2" t="str">
         <v>Points</v>
@@ -621,25 +715,31 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Ishan Kishan (C)</v>
+        <v>Pat Cummins</v>
       </c>
       <c r="B3" t="str">
         <v>Sunrisers Hyderabad</v>
       </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
       <c r="D3">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>Trent Boult</v>
+        <v>Ajinkya Rahane</v>
       </c>
       <c r="G3" t="str">
-        <v>Mumbai Indians</v>
+        <v>Kolkata Knight Riders</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -654,28 +754,34 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O3" t="str">
         <v/>
       </c>
       <c r="P3" t="str">
-        <v>Jasprit Bumrah</v>
+        <v>Tim David</v>
       </c>
       <c r="Q3" t="str">
-        <v>Mumbai Indians</v>
+        <v>Royal Challengers Bengaluru</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="T3" t="str">
         <v/>
       </c>
       <c r="U3" t="str">
-        <v>Hardik Pandya</v>
+        <v>Priyansh Arya</v>
       </c>
       <c r="V3" t="str">
-        <v>Mumbai Indians</v>
+        <v>Punjab Kings</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
       </c>
       <c r="X3">
         <v>0</v>
@@ -689,6 +795,9 @@
       <c r="AA3" t="str">
         <v>Punjab Kings</v>
       </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
       <c r="AC3">
         <v>0</v>
       </c>
@@ -696,10 +805,13 @@
         <v/>
       </c>
       <c r="AE3" t="str">
-        <v>Rohit Sharma</v>
+        <v>Jacob Bethell</v>
       </c>
       <c r="AF3" t="str">
-        <v>Mumbai Indians</v>
+        <v>Royal Challengers Bengaluru</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -708,11 +820,14 @@
         <v/>
       </c>
       <c r="AJ3" t="str">
-        <v>Shubman Gill (VC)</v>
+        <v>Shubman Gill</v>
       </c>
       <c r="AK3" t="str">
         <v>Gujarat Titans</v>
       </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
       <c r="AM3">
         <v>0</v>
       </c>
@@ -720,10 +835,13 @@
         <v/>
       </c>
       <c r="AO3" t="str">
-        <v>KL Rahul (VC)</v>
+        <v>KL Rahul</v>
       </c>
       <c r="AP3" t="str">
         <v>Delhi Capitals</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -731,10 +849,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Pat Cummins</v>
+        <v>Will Jacks</v>
       </c>
       <c r="B4" t="str">
-        <v>Sunrisers Hyderabad</v>
+        <v>Mumbai Indians</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -748,6 +869,9 @@
       <c r="G4" t="str">
         <v>Gujarat Titans</v>
       </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
       <c r="I4">
         <v>0</v>
       </c>
@@ -770,22 +894,28 @@
         <v/>
       </c>
       <c r="P4" t="str">
-        <v>Finn Allen</v>
+        <v>Jitesh Sharma</v>
       </c>
       <c r="Q4" t="str">
-        <v>Kolkata Knight Riders</v>
+        <v>Royal Challengers Bengaluru</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T4" t="str">
         <v/>
       </c>
       <c r="U4" t="str">
-        <v>Ruturaj Gaikwad</v>
+        <v>Liam Livingstone</v>
       </c>
       <c r="V4" t="str">
-        <v>Chennai Super Kings</v>
+        <v>Sunrisers Hyderabad</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
       </c>
       <c r="X4">
         <v>0</v>
@@ -799,6 +929,9 @@
       <c r="AA4" t="str">
         <v>Punjab Kings</v>
       </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
       <c r="AC4">
         <v>0</v>
       </c>
@@ -806,10 +939,13 @@
         <v/>
       </c>
       <c r="AE4" t="str">
-        <v>Suryakumar Yadav</v>
+        <v>Glenn Phillips</v>
       </c>
       <c r="AF4" t="str">
-        <v>Mumbai Indians</v>
+        <v>Gujarat Titans</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -818,10 +954,13 @@
         <v/>
       </c>
       <c r="AJ4" t="str">
-        <v>Yashasvi Jaiswal</v>
+        <v>Axar Patel</v>
       </c>
       <c r="AK4" t="str">
-        <v>Rajasthan Royals</v>
+        <v>Delhi Capitals</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
@@ -834,6 +973,9 @@
       </c>
       <c r="AP4" t="str">
         <v>Punjab Kings</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -841,10 +983,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Will Jacks</v>
+        <v>Rahul Chahar</v>
       </c>
       <c r="B5" t="str">
-        <v>Mumbai Indians</v>
+        <v>Chennai Super Kings</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -858,6 +1003,9 @@
       <c r="G5" t="str">
         <v>Punjab Kings</v>
       </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
       <c r="I5">
         <v>0</v>
       </c>
@@ -865,16 +1013,16 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>Ravindra Jadeja</v>
+        <v>Noor Ahmad</v>
       </c>
       <c r="L5" t="str">
-        <v>Rajasthan Royals</v>
+        <v>Chennai Super Kings</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -885,6 +1033,9 @@
       <c r="Q5" t="str">
         <v>Royal Challengers Bengaluru</v>
       </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
       <c r="S5">
         <v>0</v>
       </c>
@@ -892,10 +1043,13 @@
         <v/>
       </c>
       <c r="U5" t="str">
-        <v>Sunil Narine</v>
+        <v>Mohammed Shami</v>
       </c>
       <c r="V5" t="str">
-        <v>Kolkata Knight Riders</v>
+        <v>Lucknow Super Giants</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
       </c>
       <c r="X5">
         <v>0</v>
@@ -909,6 +1063,9 @@
       <c r="AA5" t="str">
         <v>Delhi Capitals</v>
       </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
       <c r="AC5">
         <v>0</v>
       </c>
@@ -916,10 +1073,13 @@
         <v/>
       </c>
       <c r="AE5" t="str">
-        <v>Tilak Varma</v>
+        <v>Marcus Stoinis</v>
       </c>
       <c r="AF5" t="str">
-        <v>Mumbai Indians</v>
+        <v>Punjab Kings</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -928,10 +1088,13 @@
         <v/>
       </c>
       <c r="AJ5" t="str">
-        <v>Axar Patel</v>
+        <v>Nicholas Pooran</v>
       </c>
       <c r="AK5" t="str">
-        <v>Delhi Capitals</v>
+        <v>Lucknow Super Giants</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
@@ -945,16 +1108,22 @@
       <c r="AP5" t="str">
         <v>Chennai Super Kings</v>
       </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
       <c r="AR5">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Vaibhav Sooryavanshi</v>
+        <v>Prithvi Shaw</v>
       </c>
       <c r="B6" t="str">
-        <v>Rajasthan Royals</v>
+        <v>Delhi Capitals</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -968,17 +1137,20 @@
       <c r="G6" t="str">
         <v>Rajasthan Royals</v>
       </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
       <c r="I6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J6" t="str">
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>Noor Ahmad</v>
+        <v>Aiden Markram</v>
       </c>
       <c r="L6" t="str">
-        <v>Chennai Super Kings</v>
+        <v>Lucknow Super Giants</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -995,6 +1167,9 @@
       <c r="Q6" t="str">
         <v>Chennai Super Kings</v>
       </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
       <c r="S6">
         <v>0</v>
       </c>
@@ -1002,10 +1177,13 @@
         <v/>
       </c>
       <c r="U6" t="str">
-        <v>Priyansh Arya</v>
+        <v>T Natarajan</v>
       </c>
       <c r="V6" t="str">
-        <v>Punjab Kings</v>
+        <v>Delhi Capitals</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
       </c>
       <c r="X6">
         <v>0</v>
@@ -1019,6 +1197,9 @@
       <c r="AA6" t="str">
         <v>Delhi Capitals</v>
       </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
       <c r="AC6">
         <v>0</v>
       </c>
@@ -1026,34 +1207,43 @@
         <v/>
       </c>
       <c r="AE6" t="str">
-        <v>Jacob Bethell</v>
+        <v>Tilak Varma</v>
       </c>
       <c r="AF6" t="str">
+        <v>Mumbai Indians</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>58</v>
+      </c>
+      <c r="AI6" t="str">
+        <v/>
+      </c>
+      <c r="AJ6" t="str">
+        <v>Kuldeep Yadav</v>
+      </c>
+      <c r="AK6" t="str">
+        <v>Delhi Capitals</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="str">
+        <v/>
+      </c>
+      <c r="AO6" t="str">
+        <v>Krunal Pandya</v>
+      </c>
+      <c r="AP6" t="str">
         <v>Royal Challengers Bengaluru</v>
       </c>
-      <c r="AH6">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="str">
-        <v/>
-      </c>
-      <c r="AJ6" t="str">
-        <v>Nicholas Pooran</v>
-      </c>
-      <c r="AK6" t="str">
-        <v>Lucknow Super Giants</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="str">
-        <v/>
-      </c>
-      <c r="AO6" t="str">
-        <v>Rishabh Pant</v>
-      </c>
-      <c r="AP6" t="str">
-        <v>Lucknow Super Giants</v>
+      <c r="AQ6">
+        <v>0</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -1061,97 +1251,118 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Varun Chakravarthy</v>
+        <v>Ishant Sharma</v>
       </c>
       <c r="B7" t="str">
+        <v>Gujarat Titans</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>Venkatesh Iyer</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Royal Challengers Bengaluru</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v>Shashank Singh</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Punjab Kings</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v>Tim Seifert</v>
+      </c>
+      <c r="Q7" t="str">
         <v>Kolkata Knight Riders</v>
       </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v>Ajinkya Rahane</v>
-      </c>
-      <c r="G7" t="str">
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7" t="str">
+        <v/>
+      </c>
+      <c r="U7" t="str">
+        <v>Rachin Ravindra</v>
+      </c>
+      <c r="V7" t="str">
         <v>Kolkata Knight Riders</v>
       </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v>Aiden Markram</v>
-      </c>
-      <c r="L7" t="str">
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="str">
+        <v/>
+      </c>
+      <c r="Z7" t="str">
+        <v>Rahul Tewatia</v>
+      </c>
+      <c r="AA7" t="str">
+        <v>Gujarat Titans</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="str">
+        <v/>
+      </c>
+      <c r="AE7" t="str">
+        <v>Quinton de Kock</v>
+      </c>
+      <c r="AF7" t="str">
+        <v>Mumbai Indians</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="str">
+        <v/>
+      </c>
+      <c r="AJ7" t="str">
+        <v>Digvesh Rathi</v>
+      </c>
+      <c r="AK7" t="str">
         <v>Lucknow Super Giants</v>
       </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7" t="str">
-        <v>Dhruv Jurel</v>
-      </c>
-      <c r="Q7" t="str">
-        <v>Rajasthan Royals</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7" t="str">
-        <v/>
-      </c>
-      <c r="U7" t="str">
-        <v>Liam Livingstone</v>
-      </c>
-      <c r="V7" t="str">
-        <v>Sunrisers Hyderabad</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="str">
-        <v/>
-      </c>
-      <c r="Z7" t="str">
-        <v>Riyan Parag</v>
-      </c>
-      <c r="AA7" t="str">
-        <v>Rajasthan Royals</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="str">
-        <v/>
-      </c>
-      <c r="AE7" t="str">
-        <v>Glenn Phillips</v>
-      </c>
-      <c r="AF7" t="str">
-        <v>Gujarat Titans</v>
-      </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="str">
-        <v/>
-      </c>
-      <c r="AJ7" t="str">
-        <v>Kuldeep Yadav</v>
-      </c>
-      <c r="AK7" t="str">
-        <v>Delhi Capitals</v>
+      <c r="AL7">
+        <v>0</v>
       </c>
       <c r="AM7">
         <v>0</v>
@@ -1160,10 +1371,13 @@
         <v/>
       </c>
       <c r="AO7" t="str">
-        <v>Avesh Khan</v>
+        <v>Rishabh Pant</v>
       </c>
       <c r="AP7" t="str">
         <v>Lucknow Super Giants</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -1171,10 +1385,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Cameron Green</v>
+        <v>David Miller</v>
       </c>
       <c r="B8" t="str">
-        <v>Kolkata Knight Riders</v>
+        <v>Delhi Capitals</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1183,10 +1400,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>Venkatesh Iyer</v>
+        <v>Mitchell Starc</v>
       </c>
       <c r="G8" t="str">
-        <v>Royal Challengers Bengaluru</v>
+        <v>Delhi Capitals</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1195,7 +1415,7 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>Shashank Singh</v>
+        <v>Azmatullah Omarzai</v>
       </c>
       <c r="L8" t="str">
         <v>Punjab Kings</v>
@@ -1210,10 +1430,13 @@
         <v/>
       </c>
       <c r="P8" t="str">
-        <v>Tim Seifert</v>
+        <v>Rashid Khan</v>
       </c>
       <c r="Q8" t="str">
-        <v>Kolkata Knight Riders</v>
+        <v>Gujarat Titans</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1222,58 +1445,73 @@
         <v/>
       </c>
       <c r="U8" t="str">
-        <v>Mohammed Shami</v>
+        <v>Hardik Pandya</v>
       </c>
       <c r="V8" t="str">
+        <v>Mumbai Indians</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>84</v>
+      </c>
+      <c r="Y8" t="str">
+        <v/>
+      </c>
+      <c r="Z8" t="str">
+        <v>Marco Jansen</v>
+      </c>
+      <c r="AA8" t="str">
+        <v>Punjab Kings</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="str">
+        <v/>
+      </c>
+      <c r="AE8" t="str">
+        <v>Kagiso Rabada</v>
+      </c>
+      <c r="AF8" t="str">
+        <v>Gujarat Titans</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="str">
+        <v/>
+      </c>
+      <c r="AJ8" t="str">
+        <v>MS Dhoni</v>
+      </c>
+      <c r="AK8" t="str">
+        <v>Chennai Super Kings</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="str">
+        <v/>
+      </c>
+      <c r="AO8" t="str">
+        <v>Avesh Khan</v>
+      </c>
+      <c r="AP8" t="str">
         <v>Lucknow Super Giants</v>
       </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="str">
-        <v/>
-      </c>
-      <c r="Z8" t="str">
-        <v>Rahul Tewatia</v>
-      </c>
-      <c r="AA8" t="str">
-        <v>Gujarat Titans</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="str">
-        <v/>
-      </c>
-      <c r="AE8" t="str">
-        <v>Marcus Stoinis</v>
-      </c>
-      <c r="AF8" t="str">
-        <v>Punjab Kings</v>
-      </c>
-      <c r="AH8">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="str">
-        <v/>
-      </c>
-      <c r="AJ8" t="str">
-        <v>Angkrish Raghuvanshi</v>
-      </c>
-      <c r="AK8" t="str">
-        <v>Kolkata Knight Riders</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="str">
-        <v/>
-      </c>
-      <c r="AO8" t="str">
-        <v>Mohammed Siraj</v>
-      </c>
-      <c r="AP8" t="str">
-        <v>Gujarat Titans</v>
+      <c r="AQ8">
+        <v>0</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -1281,49 +1519,58 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Rahul Chahar</v>
+        <v>Cameron Green</v>
       </c>
       <c r="B9" t="str">
-        <v>Chennai Super Kings</v>
+        <v>Kolkata Knight Riders</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Mitchell Starc</v>
+        <v>Virat Kohli</v>
       </c>
       <c r="G9" t="str">
-        <v>Delhi Capitals</v>
+        <v>Royal Challengers Bengaluru</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="J9" t="str">
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>Azmatullah Omarzai</v>
+        <v>Matheesha Pathirana</v>
       </c>
       <c r="L9" t="str">
+        <v>Kolkata Knight Riders</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v>Nehal Wadhera</v>
+      </c>
+      <c r="Q9" t="str">
         <v>Punjab Kings</v>
       </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="str">
-        <v/>
-      </c>
-      <c r="P9" t="str">
-        <v>Sherfane Rutherford</v>
-      </c>
-      <c r="Q9" t="str">
-        <v>Mumbai Indians</v>
+      <c r="R9">
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1332,10 +1579,13 @@
         <v/>
       </c>
       <c r="U9" t="str">
-        <v>T Natarajan</v>
+        <v>Abdul Samad</v>
       </c>
       <c r="V9" t="str">
-        <v>Delhi Capitals</v>
+        <v>Lucknow Super Giants</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
       </c>
       <c r="X9">
         <v>0</v>
@@ -1344,22 +1594,28 @@
         <v/>
       </c>
       <c r="Z9" t="str">
-        <v>Khaleel Ahmed</v>
+        <v>Ayush Mhatre</v>
       </c>
       <c r="AA9" t="str">
         <v>Chennai Super Kings</v>
       </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD9" t="str">
         <v/>
       </c>
       <c r="AE9" t="str">
-        <v>Jofra Archer</v>
+        <v>Lungi Ngidi</v>
       </c>
       <c r="AF9" t="str">
-        <v>Rajasthan Royals</v>
+        <v>Delhi Capitals</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
       </c>
       <c r="AH9">
         <v>0</v>
@@ -1368,10 +1624,13 @@
         <v/>
       </c>
       <c r="AJ9" t="str">
-        <v>Digvesh Rathi</v>
+        <v>Prashant Veer</v>
       </c>
       <c r="AK9" t="str">
-        <v>Lucknow Super Giants</v>
+        <v>Chennai Super Kings</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
       </c>
       <c r="AM9">
         <v>0</v>
@@ -1380,10 +1639,13 @@
         <v/>
       </c>
       <c r="AO9" t="str">
-        <v>Prasidh Krishna</v>
+        <v>Mohammed Siraj</v>
       </c>
       <c r="AP9" t="str">
         <v>Gujarat Titans</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -1391,11 +1653,14 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Prithvi Shaw</v>
+        <v>Ashutosh Sharma</v>
       </c>
       <c r="B10" t="str">
         <v>Delhi Capitals</v>
       </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
       <c r="D10">
         <v>0</v>
       </c>
@@ -1403,61 +1668,73 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>Virat Kohli (C)</v>
+        <v>Phil Salt</v>
       </c>
       <c r="G10" t="str">
         <v>Royal Challengers Bengaluru</v>
       </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
       <c r="I10">
-        <v>145</v>
+        <v>48</v>
       </c>
       <c r="J10" t="str">
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>Matheesha Pathirana</v>
+        <v>Mitchell Marsh</v>
       </c>
       <c r="L10" t="str">
+        <v>Lucknow Super Giants</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v>Finn Allen</v>
+      </c>
+      <c r="Q10" t="str">
         <v>Kolkata Knight Riders</v>
       </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="str">
-        <v/>
-      </c>
-      <c r="P10" t="str">
-        <v>Rashid Khan</v>
-      </c>
-      <c r="Q10" t="str">
-        <v>Gujarat Titans</v>
+      <c r="R10">
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="T10" t="str">
         <v/>
       </c>
       <c r="U10" t="str">
-        <v>Rinku Singh</v>
+        <v>Ruturaj Gaikwad</v>
       </c>
       <c r="V10" t="str">
-        <v>Kolkata Knight Riders</v>
+        <v>Chennai Super Kings</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y10" t="str">
         <v/>
       </c>
       <c r="Z10" t="str">
-        <v>Marco Jansen</v>
+        <v>Abishek Porel</v>
       </c>
       <c r="AA10" t="str">
-        <v>Punjab Kings</v>
+        <v>Delhi Capitals</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -1466,34 +1743,43 @@
         <v/>
       </c>
       <c r="AE10" t="str">
-        <v>Quinton de Kock</v>
+        <v>Rohit Sharma</v>
       </c>
       <c r="AF10" t="str">
         <v>Mumbai Indians</v>
       </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
       <c r="AH10">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="AI10" t="str">
         <v/>
       </c>
       <c r="AJ10" t="str">
-        <v>MS Dhoni</v>
+        <v>Yashasvi Jaiswal</v>
       </c>
       <c r="AK10" t="str">
-        <v>Chennai Super Kings</v>
+        <v>Rajasthan Royals</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AN10" t="str">
         <v/>
       </c>
       <c r="AO10" t="str">
-        <v>Harshit Rana</v>
+        <v>Prasidh Krishna</v>
       </c>
       <c r="AP10" t="str">
-        <v>Kolkata Knight Riders</v>
+        <v>Gujarat Titans</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -1501,31 +1787,37 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Ishant Sharma</v>
+        <v>Vaibhav Sooryavanshi</v>
       </c>
       <c r="B11" t="str">
-        <v>Gujarat Titans</v>
+        <v>Rajasthan Royals</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>Phil Salt</v>
+        <v>Harshal Patel</v>
       </c>
       <c r="G11" t="str">
-        <v>Royal Challengers Bengaluru</v>
+        <v>Sunrisers Hyderabad</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="J11" t="str">
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>Mitchell Marsh</v>
+        <v>Ayush Badoni</v>
       </c>
       <c r="L11" t="str">
         <v>Lucknow Super Giants</v>
@@ -1540,13 +1832,16 @@
         <v/>
       </c>
       <c r="P11" t="str">
-        <v>Nehal Wadhera</v>
+        <v>Dhruv Jurel</v>
       </c>
       <c r="Q11" t="str">
-        <v>Punjab Kings</v>
+        <v>Rajasthan Royals</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="T11" t="str">
         <v/>
@@ -1557,53 +1852,68 @@
       <c r="V11" t="str">
         <v>Mumbai Indians</v>
       </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
       <c r="X11">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="Y11" t="str">
         <v/>
       </c>
       <c r="Z11" t="str">
-        <v>Ayush Mhatre</v>
+        <v>Riyan Parag</v>
       </c>
       <c r="AA11" t="str">
-        <v>Chennai Super Kings</v>
+        <v>Rajasthan Royals</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AD11" t="str">
         <v/>
       </c>
       <c r="AE11" t="str">
-        <v>Kagiso Rabada</v>
+        <v>Jofra Archer</v>
       </c>
       <c r="AF11" t="str">
-        <v>Gujarat Titans</v>
+        <v>Rajasthan Royals</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="AI11" t="str">
         <v/>
       </c>
       <c r="AJ11" t="str">
-        <v>Prashant Veer</v>
+        <v>Rajat Patidar</v>
       </c>
       <c r="AK11" t="str">
-        <v>Chennai Super Kings</v>
+        <v>Royal Challengers Bengaluru</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AN11" t="str">
         <v/>
       </c>
       <c r="AO11" t="str">
-        <v>Washington Sundar</v>
+        <v>Harshit Rana</v>
       </c>
       <c r="AP11" t="str">
-        <v>Gujarat Titans</v>
+        <v>Kolkata Knight Riders</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -1611,76 +1921,91 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>David Miller</v>
+        <v>Ishan Kishan</v>
       </c>
       <c r="B12" t="str">
-        <v>Delhi Capitals</v>
+        <v>Sunrisers Hyderabad</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>Harshal Patel</v>
+        <v>Trent Boult</v>
       </c>
       <c r="G12" t="str">
-        <v>Sunrisers Hyderabad</v>
+        <v>Mumbai Indians</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J12" t="str">
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>Ayush Badoni</v>
+        <v>Ravindra Jadeja</v>
       </c>
       <c r="L12" t="str">
-        <v>Lucknow Super Giants</v>
+        <v>Rajasthan Royals</v>
       </c>
       <c r="M12">
         <v>0</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="O12" t="str">
         <v/>
       </c>
       <c r="P12" t="str">
-        <v>Tim David</v>
+        <v>Sherfane Rutherford</v>
       </c>
       <c r="Q12" t="str">
-        <v>Royal Challengers Bengaluru</v>
+        <v>Mumbai Indians</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="T12" t="str">
         <v/>
       </c>
       <c r="U12" t="str">
-        <v>Rachin Ravindra</v>
+        <v>Sunil Narine</v>
       </c>
       <c r="V12" t="str">
         <v>Kolkata Knight Riders</v>
       </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
       <c r="X12">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="Y12" t="str">
         <v/>
       </c>
       <c r="Z12" t="str">
-        <v>Abishek Porel</v>
+        <v>Khaleel Ahmed</v>
       </c>
       <c r="AA12" t="str">
-        <v>Delhi Capitals</v>
+        <v>Chennai Super Kings</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AD12" t="str">
         <v/>
@@ -1691,43 +2016,55 @@
       <c r="AF12" t="str">
         <v>Rajasthan Royals</v>
       </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
       <c r="AH12">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AI12" t="str">
         <v/>
       </c>
       <c r="AJ12" t="str">
-        <v>Rajat Patidar</v>
+        <v>Nitish Kumar Reddy</v>
       </c>
       <c r="AK12" t="str">
-        <v>Royal Challengers Bengaluru</v>
+        <v>Sunrisers Hyderabad</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="AN12" t="str">
         <v/>
       </c>
       <c r="AO12" t="str">
-        <v>Abhishek Sharma</v>
+        <v>Washington Sundar</v>
       </c>
       <c r="AP12" t="str">
-        <v>Sunrisers Hyderabad</v>
+        <v>Gujarat Titans</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
       </c>
       <c r="AR12">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Ashutosh Sharma</v>
+        <v>Varun Chakravarthy</v>
       </c>
       <c r="B13" t="str">
-        <v>Delhi Capitals</v>
+        <v>Kolkata Knight Riders</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -1738,6 +2075,9 @@
       <c r="G13" t="str">
         <v>Royal Challengers Bengaluru</v>
       </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
       <c r="I13">
         <v>54</v>
       </c>
@@ -1760,25 +2100,31 @@
         <v/>
       </c>
       <c r="P13" t="str">
-        <v>Jitesh Sharma</v>
+        <v>Jasprit Bumrah</v>
       </c>
       <c r="Q13" t="str">
-        <v>Royal Challengers Bengaluru</v>
+        <v>Mumbai Indians</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T13" t="str">
         <v/>
       </c>
       <c r="U13" t="str">
-        <v>Abdul Samad</v>
+        <v>Rinku Singh</v>
       </c>
       <c r="V13" t="str">
-        <v>Lucknow Super Giants</v>
+        <v>Kolkata Knight Riders</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="Y13" t="str">
         <v/>
@@ -1789,6 +2135,9 @@
       <c r="AA13" t="str">
         <v>Sunrisers Hyderabad</v>
       </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
       <c r="AC13">
         <v>23</v>
       </c>
@@ -1796,37 +2145,46 @@
         <v/>
       </c>
       <c r="AE13" t="str">
-        <v>Lungi Ngidi</v>
+        <v>Suryakumar Yadav</v>
       </c>
       <c r="AF13" t="str">
-        <v>Delhi Capitals</v>
+        <v>Mumbai Indians</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI13" t="str">
         <v/>
       </c>
       <c r="AJ13" t="str">
-        <v>Nitish Kumar Reddy</v>
+        <v>Angkrish Raghuvanshi</v>
       </c>
       <c r="AK13" t="str">
+        <v>Kolkata Knight Riders</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>105</v>
+      </c>
+      <c r="AN13" t="str">
+        <v/>
+      </c>
+      <c r="AO13" t="str">
+        <v>Abhishek Sharma</v>
+      </c>
+      <c r="AP13" t="str">
         <v>Sunrisers Hyderabad</v>
       </c>
-      <c r="AM13">
-        <v>15</v>
-      </c>
-      <c r="AN13" t="str">
-        <v/>
-      </c>
-      <c r="AO13" t="str">
-        <v>Krunal Pandya</v>
-      </c>
-      <c r="AP13" t="str">
-        <v>Royal Challengers Bengaluru</v>
+      <c r="AQ13">
+        <v>0</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
@@ -1836,8 +2194,11 @@
       <c r="B14" t="str">
         <v/>
       </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
       <c r="D14">
-        <v>166</v>
+        <v>332</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -1848,8 +2209,11 @@
       <c r="G14" t="str">
         <v/>
       </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
       <c r="I14">
-        <v>249</v>
+        <v>396</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -1864,7 +2228,7 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <v>71</v>
+        <v>192</v>
       </c>
       <c r="O14" t="str">
         <v/>
@@ -1875,8 +2239,11 @@
       <c r="Q14" t="str">
         <v/>
       </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
       <c r="S14">
-        <v>44</v>
+        <v>221</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -1887,8 +2254,11 @@
       <c r="V14" t="str">
         <v/>
       </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
       <c r="X14">
-        <v>0</v>
+        <v>372</v>
       </c>
       <c r="Y14" t="str">
         <v/>
@@ -1899,8 +2269,11 @@
       <c r="AA14" t="str">
         <v/>
       </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
       <c r="AC14">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="AD14" t="str">
         <v/>
@@ -1911,8 +2284,11 @@
       <c r="AF14" t="str">
         <v/>
       </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
       <c r="AH14">
-        <v>0</v>
+        <v>438</v>
       </c>
       <c r="AI14" t="str">
         <v/>
@@ -1923,8 +2299,11 @@
       <c r="AK14" t="str">
         <v/>
       </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
       <c r="AM14">
-        <v>88</v>
+        <v>265</v>
       </c>
       <c r="AN14" t="str">
         <v/>
@@ -1935,12 +2314,14 @@
       <c r="AP14" t="str">
         <v/>
       </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
       <c r="AR14">
-        <v>17</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:AR14"/>
   </ignoredErrors>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ipl26\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A9EBFC-D456-4EE2-8D50-9C1FB57B558D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01F7BCD-A1FD-4C65-A0B1-A4259791D67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Teams" sheetId="1" r:id="rId1"/>
@@ -1096,7 +1096,7 @@
         <v>0</v>
       </c>
       <c r="S3" s="1">
-        <v>59</v>
+        <v>219</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>1</v>
@@ -1117,16 +1117,16 @@
         <v>1</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="AB3" s="1">
         <v>0</v>
       </c>
       <c r="AC3" s="1">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="AD3" s="1" t="s">
         <v>1</v>
@@ -1251,16 +1251,16 @@
         <v>1</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="AB4" s="1">
         <v>0</v>
       </c>
       <c r="AC4" s="1">
-        <v>28</v>
+        <v>148</v>
       </c>
       <c r="AD4" s="1" t="s">
         <v>1</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>1</v>
@@ -1385,16 +1385,16 @@
         <v>1</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AB5" s="1">
         <v>0</v>
       </c>
       <c r="AC5" s="1">
-        <v>148</v>
+        <v>96</v>
       </c>
       <c r="AD5" s="1" t="s">
         <v>1</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="AM5" s="1">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="AN5" s="1" t="s">
         <v>1</v>
@@ -1439,7 +1439,7 @@
         <v>0</v>
       </c>
       <c r="AR5" s="1">
-        <v>80</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
@@ -1677,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="AH7" s="1">
-        <v>44</v>
+        <v>177</v>
       </c>
       <c r="AI7" s="1" t="s">
         <v>1</v>
@@ -1736,7 +1736,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>25</v>
+        <v>168</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>1</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="1">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>1</v>
@@ -1811,7 +1811,7 @@
         <v>0</v>
       </c>
       <c r="AH8" s="1">
-        <v>72</v>
+        <v>224</v>
       </c>
       <c r="AI8" s="1" t="s">
         <v>1</v>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="AC9" s="1">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="AD9" s="1" t="s">
         <v>1</v>
@@ -2079,7 +2079,7 @@
         <v>0</v>
       </c>
       <c r="AH10" s="1">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="AI10" s="1" t="s">
         <v>1</v>
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="AR10" s="1">
-        <v>18</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
@@ -2257,7 +2257,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="1">
-        <v>118</v>
+        <v>189</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>1</v>
@@ -2287,7 +2287,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="1">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>1</v>
@@ -2436,7 +2436,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="1">
-        <v>64</v>
+        <v>144</v>
       </c>
       <c r="T13" s="1" t="s">
         <v>1</v>
@@ -2481,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="AH13" s="1">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="AI13" s="1" t="s">
         <v>1</v>
@@ -2511,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="AR13" s="1">
-        <v>134</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.3">
@@ -2525,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="1">
-        <v>475</v>
+        <v>546</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>1</v>
@@ -2540,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="1">
-        <v>584</v>
+        <v>773</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>1</v>
@@ -2555,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="1">
-        <v>531</v>
+        <v>623</v>
       </c>
       <c r="O14" s="1" t="s">
         <v>1</v>
@@ -2570,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="1">
-        <v>454</v>
+        <v>694</v>
       </c>
       <c r="T14" s="1" t="s">
         <v>1</v>
@@ -2600,7 +2600,7 @@
         <v>0</v>
       </c>
       <c r="AC14" s="1">
-        <v>810</v>
+        <v>890</v>
       </c>
       <c r="AD14" s="1" t="s">
         <v>1</v>
@@ -2615,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="AH14" s="1">
-        <v>910</v>
+        <v>1259</v>
       </c>
       <c r="AI14" s="1" t="s">
         <v>1</v>
@@ -2630,7 +2630,7 @@
         <v>0</v>
       </c>
       <c r="AM14" s="1">
-        <v>869</v>
+        <v>982</v>
       </c>
       <c r="AN14" s="1" t="s">
         <v>1</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="AR14" s="1">
-        <v>658</v>
+        <v>780</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ipl26\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0700913F-D003-4958-839D-60F94282E261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A0C8F4-EDFC-415D-90A2-D508B0C71EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1051,7 +1051,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="1">
-        <v>278</v>
+        <v>454</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>123</v>
@@ -1096,7 +1096,7 @@
         <v>0</v>
       </c>
       <c r="S3" s="1">
-        <v>241</v>
+        <v>402</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>123</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>123</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="AC4" s="1">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="AD4" s="1" t="s">
         <v>123</v>
@@ -1364,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="S5" s="1">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="T5" s="1" t="s">
         <v>123</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="AM5" s="1">
-        <v>193</v>
+        <v>312</v>
       </c>
       <c r="AN5" s="1" t="s">
         <v>123</v>
@@ -1468,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>123</v>
@@ -1617,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="1">
-        <v>126</v>
+        <v>194</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>123</v>
@@ -1692,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="AM7" s="1">
-        <v>358</v>
+        <v>387</v>
       </c>
       <c r="AN7" s="1" t="s">
         <v>123</v>
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="1">
-        <v>207</v>
+        <v>291</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>123</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="1">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="T9" s="1" t="s">
         <v>123</v>
@@ -1945,7 +1945,7 @@
         <v>0</v>
       </c>
       <c r="AH9" s="1">
-        <v>294</v>
+        <v>384</v>
       </c>
       <c r="AI9" s="1" t="s">
         <v>123</v>
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="AR10" s="1">
-        <v>74</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
@@ -2138,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>123</v>
@@ -2168,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="1">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="T11" s="1" t="s">
         <v>123</v>
@@ -2272,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>123</v>
@@ -2347,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="AH12" s="1">
-        <v>213</v>
+        <v>287</v>
       </c>
       <c r="AI12" s="1" t="s">
         <v>123</v>
@@ -2525,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="1">
-        <v>841</v>
+        <v>1017</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>123</v>
@@ -2540,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="1">
-        <v>1225</v>
+        <v>1437</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>123</v>
@@ -2555,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="1">
-        <v>1258</v>
+        <v>1326</v>
       </c>
       <c r="O14" s="1" t="s">
         <v>123</v>
@@ -2570,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="1">
-        <v>1131</v>
+        <v>1422</v>
       </c>
       <c r="T14" s="1" t="s">
         <v>123</v>
@@ -2600,7 +2600,7 @@
         <v>0</v>
       </c>
       <c r="AC14" s="1">
-        <v>1004</v>
+        <v>1011</v>
       </c>
       <c r="AD14" s="1" t="s">
         <v>123</v>
@@ -2615,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="AH14" s="1">
-        <v>1576</v>
+        <v>1740</v>
       </c>
       <c r="AI14" s="1" t="s">
         <v>123</v>
@@ -2630,7 +2630,7 @@
         <v>0</v>
       </c>
       <c r="AM14" s="1">
-        <v>1906</v>
+        <v>2054</v>
       </c>
       <c r="AN14" s="1" t="s">
         <v>123</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="AR14" s="1">
-        <v>1648</v>
+        <v>1737</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ipl26\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A0C8F4-EDFC-415D-90A2-D508B0C71EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841ED367-2D6A-4685-9FE9-7A5E5551E061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1066,22 +1066,22 @@
         <v>0</v>
       </c>
       <c r="I3" s="1">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>123</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>111</v>
+        <v>16</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M3" s="1">
         <v>0</v>
       </c>
       <c r="N3" s="1">
-        <v>269</v>
+        <v>145</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>123</v>
@@ -1102,31 +1102,31 @@
         <v>123</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="W3" s="1">
         <v>0</v>
       </c>
       <c r="X3" s="1">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Y3" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AB3" s="1">
         <v>0</v>
       </c>
       <c r="AC3" s="1">
-        <v>139</v>
+        <v>12</v>
       </c>
       <c r="AD3" s="1" t="s">
         <v>123</v>
@@ -1156,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="AM3" s="1">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="AN3" s="1" t="s">
         <v>123</v>
@@ -1206,16 +1206,16 @@
         <v>123</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>48</v>
+        <v>111</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M4" s="1">
         <v>0</v>
       </c>
       <c r="N4" s="1">
-        <v>65</v>
+        <v>334</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>123</v>
@@ -1236,31 +1236,31 @@
         <v>123</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="W4" s="1">
         <v>0</v>
       </c>
       <c r="X4" s="1">
+        <v>184</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="1">
         <v>154</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB4" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="1">
-        <v>137</v>
       </c>
       <c r="AD4" s="1" t="s">
         <v>123</v>
@@ -1281,31 +1281,31 @@
         <v>123</v>
       </c>
       <c r="AJ4" s="1" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="AK4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="1">
+        <v>163</v>
+      </c>
+      <c r="AN4" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AL4" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM4" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN4" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO4" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP4" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="AQ4" s="1">
         <v>0</v>
       </c>
       <c r="AR4" s="1">
-        <v>0</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.3">
@@ -1340,16 +1340,16 @@
         <v>123</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M5" s="1">
         <v>0</v>
       </c>
       <c r="N5" s="1">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>123</v>
@@ -1370,31 +1370,31 @@
         <v>123</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="W5" s="1">
         <v>0</v>
       </c>
       <c r="X5" s="1">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AB5" s="1">
         <v>0</v>
       </c>
       <c r="AC5" s="1">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="AD5" s="1" t="s">
         <v>123</v>
@@ -1415,31 +1415,31 @@
         <v>123</v>
       </c>
       <c r="AJ5" s="1" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="AK5" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="AL5" s="1">
         <v>0</v>
       </c>
       <c r="AM5" s="1">
-        <v>312</v>
+        <v>0</v>
       </c>
       <c r="AN5" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO5" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="AP5" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AQ5" s="1">
         <v>0</v>
       </c>
       <c r="AR5" s="1">
-        <v>122</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
@@ -1474,10 +1474,10 @@
         <v>123</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
@@ -1498,37 +1498,37 @@
         <v>0</v>
       </c>
       <c r="S6" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T6" s="1" t="s">
         <v>123</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="W6" s="1">
         <v>0</v>
       </c>
       <c r="X6" s="1">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="Y6" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="AA6" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AB6" s="1">
         <v>0</v>
       </c>
       <c r="AC6" s="1">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="AD6" s="1" t="s">
         <v>123</v>
@@ -1549,22 +1549,22 @@
         <v>123</v>
       </c>
       <c r="AJ6" s="1" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="AK6" s="1" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="AL6" s="1">
         <v>0</v>
       </c>
       <c r="AM6" s="1">
-        <v>97</v>
+        <v>312</v>
       </c>
       <c r="AN6" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO6" s="1" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="AP6" s="1" t="s">
         <v>23</v>
@@ -1573,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="AR6" s="1">
-        <v>203</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
@@ -1608,16 +1608,16 @@
         <v>123</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="M7" s="1">
         <v>0</v>
       </c>
       <c r="N7" s="1">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>123</v>
@@ -1638,81 +1638,81 @@
         <v>123</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="W7" s="1">
         <v>0</v>
       </c>
       <c r="X7" s="1">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="Y7" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="AA7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>142</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE7" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AF7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AB7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF7" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="AG7" s="1">
         <v>0</v>
       </c>
       <c r="AH7" s="1">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="AI7" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="AK7" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="AL7" s="1">
         <v>0</v>
       </c>
       <c r="AM7" s="1">
-        <v>387</v>
+        <v>97</v>
       </c>
       <c r="AN7" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="AP7" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AQ7" s="1">
         <v>0</v>
       </c>
       <c r="AR7" s="1">
-        <v>125</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>24</v>
@@ -1721,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="1">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>123</v>
@@ -1736,22 +1736,22 @@
         <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="M8" s="1">
         <v>0</v>
       </c>
       <c r="N8" s="1">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>123</v>
@@ -1772,40 +1772,40 @@
         <v>123</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="W8" s="1">
         <v>0</v>
       </c>
       <c r="X8" s="1">
-        <v>168</v>
+        <v>235</v>
       </c>
       <c r="Y8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>31</v>
+        <v>105</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AB8" s="1">
         <v>0</v>
       </c>
       <c r="AC8" s="1">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="AF8" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AG8" s="1">
         <v>0</v>
@@ -1817,39 +1817,39 @@
         <v>123</v>
       </c>
       <c r="AJ8" s="1" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="AK8" s="1" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="AL8" s="1">
         <v>0</v>
       </c>
       <c r="AM8" s="1">
-        <v>104</v>
+        <v>387</v>
       </c>
       <c r="AN8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="AP8" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AQ8" s="1">
         <v>0</v>
       </c>
       <c r="AR8" s="1">
-        <v>173</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1">
         <v>0</v>
@@ -1876,7 +1876,7 @@
         <v>123</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>54</v>
@@ -1885,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="1">
-        <v>132</v>
+        <v>180</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>123</v>
@@ -1906,61 +1906,61 @@
         <v>123</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="V9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="W9" s="1">
+        <v>0</v>
+      </c>
+      <c r="X9" s="1">
+        <v>108</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>287</v>
+      </c>
+      <c r="AD9" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE9" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="W9" s="1">
-        <v>0</v>
-      </c>
-      <c r="X9" s="1">
-        <v>111</v>
-      </c>
-      <c r="Y9" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z9" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="1">
-        <v>74</v>
-      </c>
-      <c r="AD9" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE9" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="AF9" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="AG9" s="1">
         <v>0</v>
       </c>
       <c r="AH9" s="1">
-        <v>384</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AJ9" s="1" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AK9" s="1" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="AL9" s="1">
         <v>0</v>
       </c>
       <c r="AM9" s="1">
-        <v>282</v>
+        <v>104</v>
       </c>
       <c r="AN9" s="1" t="s">
         <v>123</v>
@@ -1980,10 +1980,10 @@
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="1">
         <v>0</v>
@@ -2010,16 +2010,16 @@
         <v>123</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="M10" s="1">
         <v>0</v>
       </c>
       <c r="N10" s="1">
-        <v>34</v>
+        <v>132</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>123</v>
@@ -2040,61 +2040,61 @@
         <v>123</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="W10" s="1">
         <v>0</v>
       </c>
       <c r="X10" s="1">
-        <v>212</v>
+        <v>168</v>
       </c>
       <c r="Y10" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="AA10" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AB10" s="1">
         <v>0</v>
       </c>
       <c r="AC10" s="1">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="AD10" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="AF10" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AG10" s="1">
         <v>0</v>
       </c>
       <c r="AH10" s="1">
-        <v>201</v>
+        <v>384</v>
       </c>
       <c r="AI10" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AJ10" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="AK10" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AL10" s="1">
         <v>0</v>
       </c>
       <c r="AM10" s="1">
-        <v>229</v>
+        <v>294</v>
       </c>
       <c r="AN10" s="1" t="s">
         <v>123</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C11" s="1">
         <v>0</v>
       </c>
       <c r="D11" s="1">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>123</v>
@@ -2144,16 +2144,16 @@
         <v>123</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M11" s="1">
         <v>0</v>
       </c>
       <c r="N11" s="1">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>123</v>
@@ -2174,61 +2174,61 @@
         <v>123</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W11" s="1">
         <v>0</v>
       </c>
       <c r="X11" s="1">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="Y11" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="AA11" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AB11" s="1">
         <v>0</v>
       </c>
       <c r="AC11" s="1">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="AD11" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AF11" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG11" s="1">
         <v>0</v>
       </c>
       <c r="AH11" s="1">
-        <v>248</v>
+        <v>201</v>
       </c>
       <c r="AI11" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AJ11" s="1" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="AK11" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AL11" s="1">
         <v>0</v>
       </c>
       <c r="AM11" s="1">
-        <v>306</v>
+        <v>229</v>
       </c>
       <c r="AN11" s="1" t="s">
         <v>123</v>
@@ -2243,21 +2243,21 @@
         <v>0</v>
       </c>
       <c r="AR11" s="1">
-        <v>166</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C12" s="1">
         <v>0</v>
       </c>
       <c r="D12" s="1">
-        <v>140</v>
+        <v>296</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>123</v>
@@ -2308,16 +2308,16 @@
         <v>123</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="W12" s="1">
         <v>0</v>
       </c>
       <c r="X12" s="1">
-        <v>176</v>
+        <v>212</v>
       </c>
       <c r="Y12" s="1" t="s">
         <v>123</v>
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="AC12" s="1">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AD12" s="1" t="s">
         <v>123</v>
@@ -2353,16 +2353,16 @@
         <v>123</v>
       </c>
       <c r="AJ12" s="1" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="AK12" s="1" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="AL12" s="1">
         <v>0</v>
       </c>
       <c r="AM12" s="1">
-        <v>42</v>
+        <v>306</v>
       </c>
       <c r="AN12" s="1" t="s">
         <v>123</v>
@@ -2377,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="AR12" s="1">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.3">
@@ -2436,7 +2436,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="1">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="T13" s="1" t="s">
         <v>123</v>
@@ -2466,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="AC13" s="1">
-        <v>142</v>
+        <v>218</v>
       </c>
       <c r="AD13" s="1" t="s">
         <v>123</v>
@@ -2481,22 +2481,22 @@
         <v>0</v>
       </c>
       <c r="AH13" s="1">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AI13" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AJ13" s="1" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="AK13" s="1" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="AL13" s="1">
         <v>0</v>
       </c>
       <c r="AM13" s="1">
-        <v>159</v>
+        <v>42</v>
       </c>
       <c r="AN13" s="1" t="s">
         <v>123</v>
@@ -2525,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="1">
-        <v>1017</v>
+        <v>1078</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>123</v>
@@ -2540,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="1">
-        <v>1437</v>
+        <v>1447</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>123</v>
@@ -2555,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="1">
-        <v>1326</v>
+        <v>1600</v>
       </c>
       <c r="O14" s="1" t="s">
         <v>123</v>
@@ -2570,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="1">
-        <v>1422</v>
+        <v>1450</v>
       </c>
       <c r="T14" s="1" t="s">
         <v>123</v>
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="X14" s="1">
-        <v>1355</v>
+        <v>1511</v>
       </c>
       <c r="Y14" s="1" t="s">
         <v>123</v>
@@ -2600,7 +2600,7 @@
         <v>0</v>
       </c>
       <c r="AC14" s="1">
-        <v>1011</v>
+        <v>1356</v>
       </c>
       <c r="AD14" s="1" t="s">
         <v>123</v>
@@ -2615,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="AH14" s="1">
-        <v>1740</v>
+        <v>1753</v>
       </c>
       <c r="AI14" s="1" t="s">
         <v>123</v>
@@ -2630,7 +2630,7 @@
         <v>0</v>
       </c>
       <c r="AM14" s="1">
-        <v>2054</v>
+        <v>2078</v>
       </c>
       <c r="AN14" s="1" t="s">
         <v>123</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="AR14" s="1">
-        <v>1737</v>
+        <v>2025</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ipl26\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841ED367-2D6A-4685-9FE9-7A5E5551E061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9425C5E-1E47-4BCA-8DE7-4B8C6573A380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="1">
-        <v>145</v>
+        <v>275</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>123</v>
@@ -1117,16 +1117,16 @@
         <v>123</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AB3" s="1">
         <v>0</v>
       </c>
       <c r="AC3" s="1">
-        <v>12</v>
+        <v>261</v>
       </c>
       <c r="AD3" s="1" t="s">
         <v>123</v>
@@ -1156,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="AM3" s="1">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="AN3" s="1" t="s">
         <v>123</v>
@@ -1236,31 +1236,31 @@
         <v>123</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="W4" s="1">
         <v>0</v>
       </c>
       <c r="X4" s="1">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AB4" s="1">
         <v>0</v>
       </c>
       <c r="AC4" s="1">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AD4" s="1" t="s">
         <v>123</v>
@@ -1290,36 +1290,36 @@
         <v>0</v>
       </c>
       <c r="AM4" s="1">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AN4" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO4" s="1" t="s">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="AP4" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="AQ4" s="1">
         <v>0</v>
       </c>
       <c r="AR4" s="1">
-        <v>177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
       </c>
       <c r="D5" s="1">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>123</v>
@@ -1349,7 +1349,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="1">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>123</v>
@@ -1370,31 +1370,31 @@
         <v>123</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="W5" s="1">
         <v>0</v>
       </c>
       <c r="X5" s="1">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="Y5" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AB5" s="1">
         <v>0</v>
       </c>
       <c r="AC5" s="1">
-        <v>159</v>
+        <v>217</v>
       </c>
       <c r="AD5" s="1" t="s">
         <v>123</v>
@@ -1430,24 +1430,24 @@
         <v>123</v>
       </c>
       <c r="AO5" s="1" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AP5" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="AQ5" s="1">
         <v>0</v>
       </c>
       <c r="AR5" s="1">
-        <v>0</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1">
         <v>0</v>
@@ -1498,7 +1498,7 @@
         <v>0</v>
       </c>
       <c r="S6" s="1">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="T6" s="1" t="s">
         <v>123</v>
@@ -1564,30 +1564,30 @@
         <v>123</v>
       </c>
       <c r="AO6" s="1" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="AP6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ6" s="1">
         <v>0</v>
       </c>
       <c r="AR6" s="1">
-        <v>122</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1">
         <v>0</v>
       </c>
       <c r="D7" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>123</v>
@@ -1668,16 +1668,16 @@
         <v>123</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>115</v>
+        <v>52</v>
       </c>
       <c r="AF7" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AG7" s="1">
         <v>0</v>
       </c>
       <c r="AH7" s="1">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="1" t="s">
         <v>123</v>
@@ -1698,7 +1698,7 @@
         <v>123</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="AP7" s="1" t="s">
         <v>23</v>
@@ -1707,21 +1707,21 @@
         <v>0</v>
       </c>
       <c r="AR7" s="1">
-        <v>203</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1">
         <v>24</v>
-      </c>
-      <c r="C8" s="1">
-        <v>0</v>
-      </c>
-      <c r="D8" s="1">
-        <v>144</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>123</v>
@@ -1802,10 +1802,10 @@
         <v>123</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="AF8" s="1" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="AG8" s="1">
         <v>0</v>
@@ -1832,16 +1832,16 @@
         <v>123</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="AP8" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AQ8" s="1">
         <v>0</v>
       </c>
       <c r="AR8" s="1">
-        <v>289</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.3">
@@ -1936,16 +1936,16 @@
         <v>123</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="AF9" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AG9" s="1">
         <v>0</v>
       </c>
       <c r="AH9" s="1">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="AI9" s="1" t="s">
         <v>123</v>
@@ -1966,16 +1966,16 @@
         <v>123</v>
       </c>
       <c r="AO9" s="1" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="AP9" s="1" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="AQ9" s="1">
         <v>0</v>
       </c>
       <c r="AR9" s="1">
-        <v>147</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
@@ -2064,7 +2064,7 @@
         <v>0</v>
       </c>
       <c r="AC10" s="1">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AD10" s="1" t="s">
         <v>123</v>
@@ -2100,16 +2100,16 @@
         <v>123</v>
       </c>
       <c r="AO10" s="1" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="AP10" s="1" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="AQ10" s="1">
         <v>0</v>
       </c>
       <c r="AR10" s="1">
-        <v>163</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="1">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>123</v>
@@ -2189,16 +2189,16 @@
         <v>123</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="AA11" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB11" s="1">
         <v>0</v>
       </c>
       <c r="AC11" s="1">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="AD11" s="1" t="s">
         <v>123</v>
@@ -2234,16 +2234,16 @@
         <v>123</v>
       </c>
       <c r="AO11" s="1" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="AP11" s="1" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="AQ11" s="1">
         <v>0</v>
       </c>
       <c r="AR11" s="1">
-        <v>282</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.3">
@@ -2323,16 +2323,16 @@
         <v>123</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB12" s="1">
         <v>0</v>
       </c>
       <c r="AC12" s="1">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="AD12" s="1" t="s">
         <v>123</v>
@@ -2368,16 +2368,16 @@
         <v>123</v>
       </c>
       <c r="AO12" s="1" t="s">
-        <v>120</v>
+        <v>35</v>
       </c>
       <c r="AP12" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AQ12" s="1">
         <v>0</v>
       </c>
       <c r="AR12" s="1">
-        <v>201</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.3">
@@ -2525,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="1">
-        <v>1078</v>
+        <v>1150</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>123</v>
@@ -2555,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="1">
-        <v>1600</v>
+        <v>1772</v>
       </c>
       <c r="O14" s="1" t="s">
         <v>123</v>
@@ -2570,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="1">
-        <v>1450</v>
+        <v>1478</v>
       </c>
       <c r="T14" s="1" t="s">
         <v>123</v>
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="X14" s="1">
-        <v>1511</v>
+        <v>1508</v>
       </c>
       <c r="Y14" s="1" t="s">
         <v>123</v>
@@ -2600,7 +2600,7 @@
         <v>0</v>
       </c>
       <c r="AC14" s="1">
-        <v>1356</v>
+        <v>1607</v>
       </c>
       <c r="AD14" s="1" t="s">
         <v>123</v>
@@ -2615,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="AH14" s="1">
-        <v>1753</v>
+        <v>1766</v>
       </c>
       <c r="AI14" s="1" t="s">
         <v>123</v>
@@ -2630,7 +2630,7 @@
         <v>0</v>
       </c>
       <c r="AM14" s="1">
-        <v>2078</v>
+        <v>2117</v>
       </c>
       <c r="AN14" s="1" t="s">
         <v>123</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="AR14" s="1">
-        <v>2025</v>
+        <v>2105</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ipl26\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30FF90BC-9D18-417A-B42B-D40EEE3EB64C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0EEC387-F32A-4301-9CBB-795D9BF9831C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3000" yWindow="3000" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Teams" sheetId="1" r:id="rId1"/>
@@ -1151,7 +1151,7 @@
         <v>0</v>
       </c>
       <c r="AH3">
-        <v>242</v>
+        <v>281</v>
       </c>
       <c r="AI3" t="s">
         <v>123</v>
@@ -1240,7 +1240,7 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="T4" t="s">
         <v>123</v>
@@ -1285,7 +1285,7 @@
         <v>0</v>
       </c>
       <c r="AH4">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="AI4" t="s">
         <v>123</v>
@@ -1419,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="AH5">
-        <v>137</v>
+        <v>208</v>
       </c>
       <c r="AI5" t="s">
         <v>123</v>
@@ -1568,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>312</v>
+        <v>439</v>
       </c>
       <c r="AN6" t="s">
         <v>123</v>
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>86</v>
+        <v>235</v>
       </c>
       <c r="T7" t="s">
         <v>123</v>
@@ -1880,7 +1880,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>291</v>
+        <v>381</v>
       </c>
       <c r="J9" t="s">
         <v>123</v>
@@ -1910,7 +1910,7 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="T9" t="s">
         <v>123</v>
@@ -2014,7 +2014,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="J10" t="s">
         <v>123</v>
@@ -2148,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="J11" t="s">
         <v>123</v>
@@ -2178,7 +2178,7 @@
         <v>0</v>
       </c>
       <c r="S11">
-        <v>211</v>
+        <v>287</v>
       </c>
       <c r="T11" t="s">
         <v>123</v>
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="X11">
-        <v>111</v>
+        <v>247</v>
       </c>
       <c r="Y11" t="s">
         <v>123</v>
@@ -2253,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="AR11">
-        <v>163</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.3">
@@ -2282,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>140</v>
+        <v>294</v>
       </c>
       <c r="J12" t="s">
         <v>123</v>
@@ -2327,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <v>212</v>
+        <v>291</v>
       </c>
       <c r="Y12" t="s">
         <v>123</v>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="I14">
         <f>SUM(I3:I13)</f>
-        <v>1478</v>
+        <v>1792</v>
       </c>
       <c r="J14" t="s">
         <v>123</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="S14">
         <f>SUM(S3:S13)</f>
-        <v>1504</v>
+        <v>1765</v>
       </c>
       <c r="T14" t="s">
         <v>123</v>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="X14">
         <f>SUM(X3:X13)</f>
-        <v>1594</v>
+        <v>1809</v>
       </c>
       <c r="Y14" t="s">
         <v>123</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AH14">
         <f>SUM(AH3:AH13)</f>
-        <v>1828</v>
+        <v>1951</v>
       </c>
       <c r="AI14" t="s">
         <v>123</v>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="AM14">
         <f>SUM(AM3:AM13)</f>
-        <v>2314</v>
+        <v>2441</v>
       </c>
       <c r="AN14" t="s">
         <v>123</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AR14">
         <f>SUM(AR3:AR13)</f>
-        <v>2460</v>
+        <v>2512</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ipl26\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50892927-91B2-432B-845E-0DE70E476D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE742CC-8446-46AF-88CC-051601248765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3348" yWindow="3348" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2592" yWindow="2028" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Teams" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="125">
   <si>
     <t>Aizen</t>
   </si>
@@ -403,6 +403,9 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>Navdeep Saini</t>
   </si>
 </sst>
 </file>
@@ -780,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR14"/>
+  <dimension ref="A1:AR15"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
@@ -1113,31 +1116,31 @@
         <v>123</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="W3" s="1">
         <v>0</v>
       </c>
       <c r="X3" s="1">
-        <v>300</v>
+        <v>268</v>
       </c>
       <c r="Y3" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AB3" s="1">
         <v>0</v>
       </c>
       <c r="AC3" s="1">
-        <v>159</v>
+        <v>217</v>
       </c>
       <c r="AD3" s="1" t="s">
         <v>123</v>
@@ -1173,21 +1176,21 @@
         <v>123</v>
       </c>
       <c r="AO3" s="1" t="s">
-        <v>55</v>
+        <v>124</v>
       </c>
       <c r="AP3" s="1" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="AQ3" s="1">
         <v>0</v>
       </c>
       <c r="AR3" s="1">
-        <v>238</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>29</v>
@@ -1196,22 +1199,22 @@
         <v>0</v>
       </c>
       <c r="D4" s="1">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>121</v>
+        <v>37</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="H4" s="1">
         <v>0</v>
       </c>
       <c r="I4" s="1">
-        <v>470</v>
+        <v>160</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>123</v>
@@ -1262,16 +1265,16 @@
         <v>123</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AB4" s="1">
         <v>0</v>
       </c>
       <c r="AC4" s="1">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="AD4" s="1" t="s">
         <v>123</v>
@@ -1292,60 +1295,60 @@
         <v>123</v>
       </c>
       <c r="AJ4" s="1" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="AK4" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AL4" s="1">
         <v>0</v>
       </c>
       <c r="AM4" s="1">
-        <v>512</v>
+        <v>165</v>
       </c>
       <c r="AN4" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO4" s="1" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="AP4" s="1" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="AQ4" s="1">
         <v>0</v>
       </c>
       <c r="AR4" s="1">
-        <v>260</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
       </c>
       <c r="D5" s="1">
+        <v>171</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
       <c r="I5" s="1">
-        <v>103</v>
+        <v>470</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>123</v>
@@ -1366,16 +1369,16 @@
         <v>123</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="R5" s="1">
         <v>0</v>
       </c>
       <c r="S5" s="1">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="T5" s="1" t="s">
         <v>123</v>
@@ -1396,90 +1399,90 @@
         <v>123</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="AB5" s="1">
         <v>0</v>
       </c>
       <c r="AC5" s="1">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="AD5" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="AF5" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AG5" s="1">
         <v>0</v>
       </c>
       <c r="AH5" s="1">
-        <v>125</v>
+        <v>243</v>
       </c>
       <c r="AI5" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AJ5" s="1" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="AK5" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AL5" s="1">
         <v>0</v>
       </c>
       <c r="AM5" s="1">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="AN5" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO5" s="1" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AP5" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="AQ5" s="1">
         <v>0</v>
       </c>
       <c r="AR5" s="1">
-        <v>0</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1">
         <v>0</v>
       </c>
       <c r="D6" s="1">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>241</v>
+        <v>103</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>123</v>
@@ -1500,37 +1503,37 @@
         <v>123</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="R6" s="1">
         <v>0</v>
       </c>
       <c r="S6" s="1">
-        <v>235</v>
+        <v>132</v>
       </c>
       <c r="T6" s="1" t="s">
         <v>123</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="W6" s="1">
         <v>0</v>
       </c>
       <c r="X6" s="1">
-        <v>181</v>
+        <v>300</v>
       </c>
       <c r="Y6" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="AA6" s="1" t="s">
         <v>17</v>
@@ -1539,60 +1542,60 @@
         <v>0</v>
       </c>
       <c r="AC6" s="1">
-        <v>170</v>
+        <v>351</v>
       </c>
       <c r="AD6" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="AF6" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AG6" s="1">
         <v>0</v>
       </c>
       <c r="AH6" s="1">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="AI6" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AJ6" s="1" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="AK6" s="1" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="AL6" s="1">
         <v>0</v>
       </c>
       <c r="AM6" s="1">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="AN6" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO6" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="AP6" s="1" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="AQ6" s="1">
         <v>0</v>
       </c>
       <c r="AR6" s="1">
-        <v>256</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1">
         <v>0</v>
@@ -1604,16 +1607,16 @@
         <v>123</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
       </c>
       <c r="I7" s="1">
-        <v>61</v>
+        <v>241</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>123</v>
@@ -1634,52 +1637,52 @@
         <v>123</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="R7" s="1">
         <v>0</v>
       </c>
       <c r="S7" s="1">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="T7" s="1" t="s">
         <v>123</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="W7" s="1">
         <v>0</v>
       </c>
       <c r="X7" s="1">
-        <v>270</v>
+        <v>181</v>
       </c>
       <c r="Y7" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AB7" s="1">
         <v>0</v>
       </c>
       <c r="AC7" s="1">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="AD7" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="AF7" s="1" t="s">
         <v>15</v>
@@ -1688,7 +1691,7 @@
         <v>0</v>
       </c>
       <c r="AH7" s="1">
-        <v>208</v>
+        <v>145</v>
       </c>
       <c r="AI7" s="1" t="s">
         <v>123</v>
@@ -1723,31 +1726,31 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C8" s="1">
         <v>0</v>
       </c>
       <c r="D8" s="1">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>123</v>
@@ -1768,61 +1771,61 @@
         <v>123</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="R8" s="1">
         <v>0</v>
       </c>
       <c r="S8" s="1">
-        <v>132</v>
+        <v>187</v>
       </c>
       <c r="T8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="W8" s="1">
         <v>0</v>
       </c>
       <c r="X8" s="1">
-        <v>38</v>
+        <v>270</v>
       </c>
       <c r="Y8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AB8" s="1">
         <v>0</v>
       </c>
       <c r="AC8" s="1">
-        <v>351</v>
+        <v>20</v>
       </c>
       <c r="AD8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="AF8" s="1" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="AG8" s="1">
         <v>0</v>
       </c>
       <c r="AH8" s="1">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AI8" s="1" t="s">
         <v>123</v>
@@ -1843,16 +1846,16 @@
         <v>123</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="AP8" s="1" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AQ8" s="1">
         <v>0</v>
       </c>
       <c r="AR8" s="1">
-        <v>186</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.3">
@@ -1872,16 +1875,16 @@
         <v>123</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
       </c>
       <c r="I9" s="1">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>123</v>
@@ -1902,55 +1905,55 @@
         <v>123</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="Q9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9" s="1">
+        <v>240</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="W9" s="1">
+        <v>0</v>
+      </c>
+      <c r="X9" s="1">
+        <v>38</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>84</v>
+      </c>
+      <c r="AD9" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF9" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="R9" s="1">
-        <v>0</v>
-      </c>
-      <c r="S9" s="1">
-        <v>160</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="V9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W9" s="1">
-        <v>0</v>
-      </c>
-      <c r="X9" s="1">
-        <v>235</v>
-      </c>
-      <c r="Y9" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z9" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE9" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AF9" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="AG9" s="1">
         <v>0</v>
@@ -1977,7 +1980,7 @@
         <v>123</v>
       </c>
       <c r="AO9" s="1" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="AP9" s="1" t="s">
         <v>23</v>
@@ -1986,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="AR9" s="1">
-        <v>254</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
@@ -2036,16 +2039,16 @@
         <v>123</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="R10" s="1">
         <v>0</v>
       </c>
       <c r="S10" s="1">
-        <v>187</v>
+        <v>115</v>
       </c>
       <c r="T10" s="1" t="s">
         <v>123</v>
@@ -2075,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="AC10" s="1">
-        <v>287</v>
+        <v>415</v>
       </c>
       <c r="AD10" s="1" t="s">
         <v>123</v>
@@ -2111,16 +2114,16 @@
         <v>123</v>
       </c>
       <c r="AO10" s="1" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="AP10" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AQ10" s="1">
         <v>0</v>
       </c>
       <c r="AR10" s="1">
-        <v>299</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
@@ -2164,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="1">
-        <v>142</v>
+        <v>190</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>123</v>
@@ -2200,16 +2203,16 @@
         <v>123</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="AA11" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AB11" s="1">
         <v>0</v>
       </c>
       <c r="AC11" s="1">
-        <v>20</v>
+        <v>211</v>
       </c>
       <c r="AD11" s="1" t="s">
         <v>123</v>
@@ -2245,16 +2248,16 @@
         <v>123</v>
       </c>
       <c r="AO11" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="AP11" s="1" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="AQ11" s="1">
         <v>0</v>
       </c>
       <c r="AR11" s="1">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.3">
@@ -2328,22 +2331,22 @@
         <v>0</v>
       </c>
       <c r="X12" s="1">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="Y12" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AB12" s="1">
         <v>0</v>
       </c>
       <c r="AC12" s="1">
-        <v>84</v>
+        <v>284</v>
       </c>
       <c r="AD12" s="1" t="s">
         <v>123</v>
@@ -2379,16 +2382,16 @@
         <v>123</v>
       </c>
       <c r="AO12" s="1" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="AP12" s="1" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="AQ12" s="1">
         <v>0</v>
       </c>
       <c r="AR12" s="1">
-        <v>282</v>
+        <v>303</v>
       </c>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.3">
@@ -2462,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="X13" s="1">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="Y13" s="1" t="s">
         <v>123</v>
@@ -2492,7 +2495,7 @@
         <v>0</v>
       </c>
       <c r="AH13" s="1">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="AI13" s="1" t="s">
         <v>123</v>
@@ -2513,150 +2516,284 @@
         <v>123</v>
       </c>
       <c r="AO13" s="1" t="s">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="AP13" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AQ13" s="1">
         <v>0</v>
       </c>
       <c r="AR13" s="1">
-        <v>422</v>
+        <v>442</v>
       </c>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="X14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AA14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AC14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AD14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AG14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AH14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AI14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AK14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AM14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AN14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO14" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="1">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="15" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C14" s="1">
-        <v>0</v>
-      </c>
-      <c r="D14" s="1">
+      <c r="B15" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1">
         <v>1369</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F14" s="1" t="s">
+      <c r="E15" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1">
-        <v>2090</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K14" s="1" t="s">
+      <c r="G15" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>2102</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="L14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="M14" s="1">
-        <v>0</v>
-      </c>
-      <c r="N14" s="1">
-        <v>2557</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P14" s="1" t="s">
+      <c r="L15" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1">
+        <v>2605</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="P15" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="Q14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="R14" s="1">
-        <v>0</v>
-      </c>
-      <c r="S14" s="1">
-        <v>2043</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U14" s="1" t="s">
+      <c r="Q15" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="R15" s="1">
+        <v>0</v>
+      </c>
+      <c r="S15" s="1">
+        <v>2068</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="U15" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="V14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="W14" s="1">
-        <v>0</v>
-      </c>
-      <c r="X14" s="1">
-        <v>1990</v>
-      </c>
-      <c r="Y14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z14" s="1" t="s">
+      <c r="V15" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="W15" s="1">
+        <v>0</v>
+      </c>
+      <c r="X15" s="1">
+        <v>2053</v>
+      </c>
+      <c r="Y15" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z15" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AA14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="1">
-        <v>1871</v>
-      </c>
-      <c r="AD14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE14" s="1" t="s">
+      <c r="AA15" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="1">
+        <v>2193</v>
+      </c>
+      <c r="AD15" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE15" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AF14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AG14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="1">
-        <v>2051</v>
-      </c>
-      <c r="AI14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ14" s="1" t="s">
+      <c r="AF15" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AG15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="1">
+        <v>2315</v>
+      </c>
+      <c r="AI15" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ15" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AK14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AL14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM14" s="1">
+      <c r="AK15" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="1">
         <v>2691</v>
       </c>
-      <c r="AN14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO14" s="1" t="s">
+      <c r="AN15" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO15" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AP14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AQ14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AR14" s="1">
-        <v>2739</v>
+      <c r="AP15" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AQ15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR15" s="1">
+        <v>2909</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ipl26\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE742CC-8446-46AF-88CC-051601248765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABFCF89-94BE-4F14-8D7F-580675DB7926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2592" yWindow="2028" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3288" yWindow="2724" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Teams" sheetId="1" r:id="rId1"/>
@@ -1116,46 +1116,46 @@
         <v>123</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="W3" s="1">
         <v>0</v>
       </c>
       <c r="X3" s="1">
-        <v>268</v>
+        <v>185</v>
       </c>
       <c r="Y3" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB3" s="1">
         <v>0</v>
       </c>
       <c r="AC3" s="1">
-        <v>217</v>
+        <v>95</v>
       </c>
       <c r="AD3" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AG3" s="1">
         <v>0</v>
       </c>
       <c r="AH3" s="1">
-        <v>124</v>
+        <v>281</v>
       </c>
       <c r="AI3" s="1" t="s">
         <v>123</v>
@@ -1190,31 +1190,31 @@
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1">
         <v>0</v>
       </c>
       <c r="D4" s="1">
+        <v>171</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="H4" s="1">
         <v>0</v>
       </c>
       <c r="I4" s="1">
-        <v>160</v>
+        <v>470</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>123</v>
@@ -1250,37 +1250,37 @@
         <v>123</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="W4" s="1">
         <v>0</v>
       </c>
       <c r="X4" s="1">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="Y4" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AB4" s="1">
         <v>0</v>
       </c>
       <c r="AC4" s="1">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="AD4" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="AF4" s="1" t="s">
         <v>15</v>
@@ -1289,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="AH4" s="1">
-        <v>281</v>
+        <v>220</v>
       </c>
       <c r="AI4" s="1" t="s">
         <v>123</v>
@@ -1324,31 +1324,31 @@
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
       </c>
       <c r="D5" s="1">
-        <v>171</v>
+        <v>114</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>121</v>
+        <v>47</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
       <c r="I5" s="1">
-        <v>470</v>
+        <v>103</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>123</v>
@@ -1369,61 +1369,61 @@
         <v>123</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="Q5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="1">
+        <v>0</v>
+      </c>
+      <c r="S5" s="1">
+        <v>132</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="V5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="R5" s="1">
-        <v>0</v>
-      </c>
-      <c r="S5" s="1">
-        <v>0</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="V5" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="W5" s="1">
         <v>0</v>
       </c>
       <c r="X5" s="1">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="AB5" s="1">
         <v>0</v>
       </c>
       <c r="AC5" s="1">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="AD5" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="AF5" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AG5" s="1">
         <v>0</v>
       </c>
       <c r="AH5" s="1">
-        <v>243</v>
+        <v>145</v>
       </c>
       <c r="AI5" s="1" t="s">
         <v>123</v>
@@ -1473,16 +1473,16 @@
         <v>123</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>123</v>
@@ -1503,7 +1503,7 @@
         <v>123</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="Q6" s="1" t="s">
         <v>40</v>
@@ -1512,28 +1512,28 @@
         <v>0</v>
       </c>
       <c r="S6" s="1">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="T6" s="1" t="s">
         <v>123</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="W6" s="1">
         <v>0</v>
       </c>
       <c r="X6" s="1">
-        <v>300</v>
+        <v>328</v>
       </c>
       <c r="Y6" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="AA6" s="1" t="s">
         <v>17</v>
@@ -1542,13 +1542,13 @@
         <v>0</v>
       </c>
       <c r="AC6" s="1">
-        <v>351</v>
+        <v>170</v>
       </c>
       <c r="AD6" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="AF6" s="1" t="s">
         <v>15</v>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="AH6" s="1">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AI6" s="1" t="s">
         <v>123</v>
@@ -1607,16 +1607,16 @@
         <v>123</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
       </c>
       <c r="I7" s="1">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>123</v>
@@ -1637,61 +1637,61 @@
         <v>123</v>
       </c>
       <c r="P7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1">
         <v>39</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="T7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="W7" s="1">
+        <v>0</v>
+      </c>
+      <c r="X7" s="1">
+        <v>118</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>351</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="R7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1">
-        <v>160</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="V7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="W7" s="1">
-        <v>0</v>
-      </c>
-      <c r="X7" s="1">
-        <v>181</v>
-      </c>
-      <c r="Y7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z7" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF7" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="AG7" s="1">
         <v>0</v>
       </c>
       <c r="AH7" s="1">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="1" t="s">
         <v>123</v>
@@ -1726,31 +1726,31 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1">
         <v>0</v>
       </c>
       <c r="D8" s="1">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>61</v>
+        <v>160</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>123</v>
@@ -1786,22 +1786,22 @@
         <v>123</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="W8" s="1">
         <v>0</v>
       </c>
       <c r="X8" s="1">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="Y8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="AA8" s="1" t="s">
         <v>24</v>
@@ -1810,22 +1810,22 @@
         <v>0</v>
       </c>
       <c r="AC8" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>32</v>
+        <v>115</v>
       </c>
       <c r="AF8" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AG8" s="1">
         <v>0</v>
       </c>
       <c r="AH8" s="1">
-        <v>210</v>
+        <v>265</v>
       </c>
       <c r="AI8" s="1" t="s">
         <v>123</v>
@@ -1860,10 +1860,10 @@
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1">
         <v>0</v>
@@ -1875,16 +1875,16 @@
         <v>123</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
       </c>
       <c r="I9" s="1">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>123</v>
@@ -1920,46 +1920,46 @@
         <v>123</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="W9" s="1">
         <v>0</v>
       </c>
       <c r="X9" s="1">
-        <v>38</v>
+        <v>181</v>
       </c>
       <c r="Y9" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="AA9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>20</v>
+      </c>
+      <c r="AD9" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AB9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="1">
-        <v>84</v>
-      </c>
-      <c r="AD9" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF9" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="AG9" s="1">
         <v>0</v>
       </c>
       <c r="AH9" s="1">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="AI9" s="1" t="s">
         <v>123</v>
@@ -1989,21 +1989,21 @@
         <v>0</v>
       </c>
       <c r="AR9" s="1">
-        <v>186</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" s="1">
         <v>0</v>
       </c>
       <c r="D10" s="1">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>123</v>
@@ -2054,16 +2054,16 @@
         <v>123</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="W10" s="1">
         <v>0</v>
       </c>
       <c r="X10" s="1">
-        <v>138</v>
+        <v>38</v>
       </c>
       <c r="Y10" s="1" t="s">
         <v>123</v>
@@ -2084,16 +2084,16 @@
         <v>123</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AF10" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG10" s="1">
         <v>0</v>
       </c>
       <c r="AH10" s="1">
-        <v>265</v>
+        <v>381</v>
       </c>
       <c r="AI10" s="1" t="s">
         <v>123</v>
@@ -2123,21 +2123,21 @@
         <v>0</v>
       </c>
       <c r="AR10" s="1">
-        <v>254</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1">
         <v>0</v>
       </c>
       <c r="D11" s="1">
-        <v>45</v>
+        <v>311</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>123</v>
@@ -2188,16 +2188,16 @@
         <v>123</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="W11" s="1">
         <v>0</v>
       </c>
       <c r="X11" s="1">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="Y11" s="1" t="s">
         <v>123</v>
@@ -2316,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="1">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="T12" s="1" t="s">
         <v>123</v>
@@ -2376,7 +2376,7 @@
         <v>0</v>
       </c>
       <c r="AM12" s="1">
-        <v>345</v>
+        <v>509</v>
       </c>
       <c r="AN12" s="1" t="s">
         <v>123</v>
@@ -2420,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>123</v>
@@ -2435,7 +2435,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="1">
-        <v>406</v>
+        <v>504</v>
       </c>
       <c r="O13" s="1" t="s">
         <v>123</v>
@@ -2510,7 +2510,7 @@
         <v>0</v>
       </c>
       <c r="AM13" s="1">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="AN13" s="1" t="s">
         <v>123</v>
@@ -2659,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="AR14" s="1">
-        <v>422</v>
+        <v>479</v>
       </c>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.3">
@@ -2673,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="1">
-        <v>1369</v>
+        <v>1608</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>123</v>
@@ -2688,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="1">
-        <v>2102</v>
+        <v>2148</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>123</v>
@@ -2703,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="1">
-        <v>2605</v>
+        <v>2703</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>123</v>
@@ -2718,7 +2718,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="1">
-        <v>2068</v>
+        <v>2159</v>
       </c>
       <c r="T15" s="1" t="s">
         <v>123</v>
@@ -2733,7 +2733,7 @@
         <v>0</v>
       </c>
       <c r="X15" s="1">
-        <v>2053</v>
+        <v>2124</v>
       </c>
       <c r="Y15" s="1" t="s">
         <v>123</v>
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="AC15" s="1">
-        <v>2193</v>
+        <v>2204</v>
       </c>
       <c r="AD15" s="1" t="s">
         <v>123</v>
@@ -2763,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="AH15" s="1">
-        <v>2315</v>
+        <v>2500</v>
       </c>
       <c r="AI15" s="1" t="s">
         <v>123</v>
@@ -2778,7 +2778,7 @@
         <v>0</v>
       </c>
       <c r="AM15" s="1">
-        <v>2691</v>
+        <v>2875</v>
       </c>
       <c r="AN15" s="1" t="s">
         <v>123</v>
@@ -2793,7 +2793,7 @@
         <v>0</v>
       </c>
       <c r="AR15" s="1">
-        <v>2909</v>
+        <v>3101</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ipl26\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABFCF89-94BE-4F14-8D7F-580675DB7926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D87F42-8B56-4213-926C-0601296A892C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3288" yWindow="2724" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -441,8 +441,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -787,2013 +786,2021 @@
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="G1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K1" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P1" s="1" t="s">
+      <c r="L1" t="s">
+        <v>123</v>
+      </c>
+      <c r="M1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N1" t="s">
+        <v>123</v>
+      </c>
+      <c r="O1" t="s">
+        <v>123</v>
+      </c>
+      <c r="P1" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U1" s="1" t="s">
+      <c r="Q1" t="s">
+        <v>123</v>
+      </c>
+      <c r="R1" t="s">
+        <v>123</v>
+      </c>
+      <c r="S1" t="s">
+        <v>123</v>
+      </c>
+      <c r="T1" t="s">
+        <v>123</v>
+      </c>
+      <c r="U1" t="s">
         <v>4</v>
       </c>
-      <c r="V1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z1" s="1" t="s">
+      <c r="V1" t="s">
+        <v>123</v>
+      </c>
+      <c r="W1" t="s">
+        <v>123</v>
+      </c>
+      <c r="X1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z1" t="s">
         <v>5</v>
       </c>
-      <c r="AA1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AA1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE1" t="s">
         <v>6</v>
       </c>
-      <c r="AF1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AF1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ1" t="s">
         <v>7</v>
       </c>
-      <c r="AK1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AK1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO1" t="s">
         <v>8</v>
       </c>
-      <c r="AP1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AP1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AR1" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="E2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F2" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="J2" t="s">
+        <v>123</v>
+      </c>
+      <c r="K2" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P2" s="1" t="s">
+      <c r="O2" t="s">
+        <v>123</v>
+      </c>
+      <c r="P2" t="s">
         <v>9</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" t="s">
         <v>10</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" t="s">
         <v>11</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U2" s="1" t="s">
+      <c r="T2" t="s">
+        <v>123</v>
+      </c>
+      <c r="U2" t="s">
         <v>9</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="V2" t="s">
         <v>10</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="W2" t="s">
         <v>12</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="X2" t="s">
         <v>11</v>
       </c>
-      <c r="Y2" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z2" s="1" t="s">
+      <c r="Y2" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z2" t="s">
         <v>9</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AA2" t="s">
         <v>10</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AB2" t="s">
         <v>12</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AC2" t="s">
         <v>11</v>
       </c>
-      <c r="AD2" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AD2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE2" t="s">
         <v>9</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AF2" t="s">
         <v>10</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AG2" t="s">
         <v>12</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AH2" t="s">
         <v>11</v>
       </c>
-      <c r="AI2" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AI2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ2" t="s">
         <v>9</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AK2" t="s">
         <v>10</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AL2" t="s">
         <v>12</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AM2" t="s">
         <v>11</v>
       </c>
-      <c r="AN2" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO2" s="1" t="s">
+      <c r="AN2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO2" t="s">
         <v>9</v>
       </c>
-      <c r="AP2" s="1" t="s">
+      <c r="AP2" t="s">
         <v>10</v>
       </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="AQ2" t="s">
         <v>12</v>
       </c>
-      <c r="AR2" s="1" t="s">
+      <c r="AR2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="1">
-        <v>0</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <v>456</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="E3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="1">
-        <v>0</v>
-      </c>
-      <c r="I3" s="1">
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
         <v>34</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="J3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K3" t="s">
         <v>16</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" t="s">
         <v>17</v>
       </c>
-      <c r="M3" s="1">
-        <v>0</v>
-      </c>
-      <c r="N3" s="1">
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
         <v>367</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P3" s="1" t="s">
+      <c r="O3" t="s">
+        <v>123</v>
+      </c>
+      <c r="P3" t="s">
         <v>49</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="Q3" t="s">
         <v>17</v>
       </c>
-      <c r="R3" s="1">
-        <v>0</v>
-      </c>
-      <c r="S3" s="1">
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
         <v>119</v>
       </c>
-      <c r="T3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U3" s="1" t="s">
+      <c r="T3" t="s">
+        <v>123</v>
+      </c>
+      <c r="U3" t="s">
         <v>86</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="V3" t="s">
         <v>29</v>
       </c>
-      <c r="W3" s="1">
-        <v>0</v>
-      </c>
-      <c r="X3" s="1">
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
         <v>185</v>
       </c>
-      <c r="Y3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z3" s="1" t="s">
+      <c r="Y3" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z3" t="s">
         <v>70</v>
       </c>
-      <c r="AA3" s="1" t="s">
+      <c r="AA3" t="s">
         <v>23</v>
       </c>
-      <c r="AB3" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="1">
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
         <v>95</v>
       </c>
-      <c r="AD3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE3" s="1" t="s">
+      <c r="AD3" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE3" t="s">
         <v>22</v>
       </c>
-      <c r="AF3" s="1" t="s">
+      <c r="AF3" t="s">
         <v>15</v>
       </c>
-      <c r="AG3" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="1">
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
         <v>281</v>
       </c>
-      <c r="AI3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ3" s="1" t="s">
+      <c r="AI3" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ3" t="s">
         <v>44</v>
       </c>
-      <c r="AK3" s="1" t="s">
+      <c r="AK3" t="s">
         <v>24</v>
       </c>
-      <c r="AL3" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM3" s="1">
-        <v>181</v>
-      </c>
-      <c r="AN3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO3" s="1" t="s">
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>307</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO3" t="s">
         <v>124</v>
       </c>
-      <c r="AP3" s="1" t="s">
+      <c r="AP3" t="s">
         <v>29</v>
       </c>
-      <c r="AQ3" s="1">
-        <v>0</v>
-      </c>
-      <c r="AR3" s="1">
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="1">
-        <v>0</v>
-      </c>
-      <c r="D4" s="1">
-        <v>171</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>237</v>
+      </c>
+      <c r="E4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F4" t="s">
         <v>121</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>40</v>
       </c>
-      <c r="H4" s="1">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1">
-        <v>470</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K4" s="1" t="s">
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>515</v>
+      </c>
+      <c r="J4" t="s">
+        <v>123</v>
+      </c>
+      <c r="K4" t="s">
         <v>48</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" t="s">
         <v>17</v>
       </c>
-      <c r="M4" s="1">
-        <v>0</v>
-      </c>
-      <c r="N4" s="1">
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
         <v>243</v>
       </c>
-      <c r="O4" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P4" s="1" t="s">
+      <c r="O4" t="s">
+        <v>123</v>
+      </c>
+      <c r="P4" t="s">
         <v>59</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="Q4" t="s">
         <v>34</v>
       </c>
-      <c r="R4" s="1">
-        <v>0</v>
-      </c>
-      <c r="S4" s="1">
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <v>417</v>
       </c>
-      <c r="T4" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U4" s="1" t="s">
+      <c r="T4" t="s">
+        <v>123</v>
+      </c>
+      <c r="U4" t="s">
         <v>50</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="V4" t="s">
         <v>21</v>
       </c>
-      <c r="W4" s="1">
-        <v>0</v>
-      </c>
-      <c r="X4" s="1">
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
         <v>268</v>
       </c>
-      <c r="Y4" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z4" s="1" t="s">
+      <c r="Y4" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z4" t="s">
         <v>42</v>
       </c>
-      <c r="AA4" s="1" t="s">
+      <c r="AA4" t="s">
         <v>24</v>
       </c>
-      <c r="AB4" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="1">
-        <v>217</v>
-      </c>
-      <c r="AD4" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE4" s="1" t="s">
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>319</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE4" t="s">
         <v>88</v>
       </c>
-      <c r="AF4" s="1" t="s">
+      <c r="AF4" t="s">
         <v>15</v>
       </c>
-      <c r="AG4" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="1">
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
         <v>220</v>
       </c>
-      <c r="AI4" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ4" s="1" t="s">
+      <c r="AI4" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ4" t="s">
         <v>63</v>
       </c>
-      <c r="AK4" s="1" t="s">
+      <c r="AK4" t="s">
         <v>24</v>
       </c>
-      <c r="AL4" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM4" s="1">
-        <v>165</v>
-      </c>
-      <c r="AN4" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO4" s="1" t="s">
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>253</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO4" t="s">
         <v>90</v>
       </c>
-      <c r="AP4" s="1" t="s">
+      <c r="AP4" t="s">
         <v>29</v>
       </c>
-      <c r="AQ4" s="1">
-        <v>0</v>
-      </c>
-      <c r="AR4" s="1">
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="1">
-        <v>0</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
         <v>114</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="E5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F5" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="1">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1">
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>103</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K5" s="1" t="s">
+      <c r="J5" t="s">
+        <v>123</v>
+      </c>
+      <c r="K5" t="s">
         <v>111</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="L5" t="s">
         <v>13</v>
       </c>
-      <c r="M5" s="1">
-        <v>0</v>
-      </c>
-      <c r="N5" s="1">
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
         <v>408</v>
       </c>
-      <c r="O5" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P5" s="1" t="s">
+      <c r="O5" t="s">
+        <v>123</v>
+      </c>
+      <c r="P5" t="s">
         <v>112</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="Q5" t="s">
         <v>40</v>
       </c>
-      <c r="R5" s="1">
-        <v>0</v>
-      </c>
-      <c r="S5" s="1">
-        <v>132</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U5" s="1" t="s">
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>160</v>
+      </c>
+      <c r="T5" t="s">
+        <v>123</v>
+      </c>
+      <c r="U5" t="s">
         <v>104</v>
       </c>
-      <c r="V5" s="1" t="s">
+      <c r="V5" t="s">
         <v>29</v>
       </c>
-      <c r="W5" s="1">
-        <v>0</v>
-      </c>
-      <c r="X5" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z5" s="1" t="s">
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z5" t="s">
         <v>61</v>
       </c>
-      <c r="AA5" s="1" t="s">
+      <c r="AA5" t="s">
         <v>34</v>
       </c>
-      <c r="AB5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="1">
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
         <v>189</v>
       </c>
-      <c r="AD5" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE5" s="1" t="s">
+      <c r="AD5" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE5" t="s">
         <v>43</v>
       </c>
-      <c r="AF5" s="1" t="s">
+      <c r="AF5" t="s">
         <v>15</v>
       </c>
-      <c r="AG5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="1">
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
         <v>145</v>
       </c>
-      <c r="AI5" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ5" s="1" t="s">
+      <c r="AI5" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ5" t="s">
         <v>89</v>
       </c>
-      <c r="AK5" s="1" t="s">
+      <c r="AK5" t="s">
         <v>17</v>
       </c>
-      <c r="AL5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN5" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO5" s="1" t="s">
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO5" t="s">
         <v>45</v>
       </c>
-      <c r="AP5" s="1" t="s">
+      <c r="AP5" t="s">
         <v>17</v>
       </c>
-      <c r="AQ5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AR5" s="1">
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
         <v>256</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="1">
-        <v>0</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" t="s">
         <v>66</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1">
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>61</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K6" s="1" t="s">
+      <c r="J6" t="s">
+        <v>123</v>
+      </c>
+      <c r="K6" t="s">
         <v>76</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="L6" t="s">
         <v>21</v>
       </c>
-      <c r="M6" s="1">
-        <v>0</v>
-      </c>
-      <c r="N6" s="1">
-        <v>0</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P6" s="1" t="s">
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>123</v>
+      </c>
+      <c r="P6" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="1" t="s">
+      <c r="Q6" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="1">
-        <v>0</v>
-      </c>
-      <c r="S6" s="1">
-        <v>160</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U6" s="1" t="s">
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>180</v>
+      </c>
+      <c r="T6" t="s">
+        <v>123</v>
+      </c>
+      <c r="U6" t="s">
         <v>41</v>
       </c>
-      <c r="V6" s="1" t="s">
+      <c r="V6" t="s">
         <v>29</v>
       </c>
-      <c r="W6" s="1">
-        <v>0</v>
-      </c>
-      <c r="X6" s="1">
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
         <v>328</v>
       </c>
-      <c r="Y6" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z6" s="1" t="s">
+      <c r="Y6" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z6" t="s">
         <v>79</v>
       </c>
-      <c r="AA6" s="1" t="s">
+      <c r="AA6" t="s">
         <v>17</v>
       </c>
-      <c r="AB6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="1">
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
         <v>170</v>
       </c>
-      <c r="AD6" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE6" s="1" t="s">
+      <c r="AD6" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE6" t="s">
         <v>32</v>
       </c>
-      <c r="AF6" s="1" t="s">
+      <c r="AF6" t="s">
         <v>15</v>
       </c>
-      <c r="AG6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="1">
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
         <v>210</v>
       </c>
-      <c r="AI6" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ6" s="1" t="s">
+      <c r="AI6" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ6" t="s">
         <v>107</v>
       </c>
-      <c r="AK6" s="1" t="s">
+      <c r="AK6" t="s">
         <v>40</v>
       </c>
-      <c r="AL6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM6" s="1">
-        <v>512</v>
-      </c>
-      <c r="AN6" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO6" s="1" t="s">
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>530</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO6" t="s">
         <v>55</v>
       </c>
-      <c r="AP6" s="1" t="s">
+      <c r="AP6" t="s">
         <v>54</v>
       </c>
-      <c r="AQ6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AR6" s="1">
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
         <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="1">
-        <v>0</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F7" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K7" s="1" t="s">
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
+        <v>123</v>
+      </c>
+      <c r="K7" t="s">
         <v>84</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="L7" t="s">
         <v>29</v>
       </c>
-      <c r="M7" s="1">
-        <v>0</v>
-      </c>
-      <c r="N7" s="1">
-        <v>0</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P7" s="1" t="s">
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>123</v>
+      </c>
+      <c r="P7" t="s">
         <v>68</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="Q7" t="s">
         <v>29</v>
       </c>
-      <c r="R7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1">
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>39</v>
       </c>
-      <c r="T7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U7" s="1" t="s">
+      <c r="T7" t="s">
+        <v>123</v>
+      </c>
+      <c r="U7" t="s">
         <v>30</v>
       </c>
-      <c r="V7" s="1" t="s">
+      <c r="V7" t="s">
         <v>17</v>
       </c>
-      <c r="W7" s="1">
-        <v>0</v>
-      </c>
-      <c r="X7" s="1">
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
         <v>118</v>
       </c>
-      <c r="Y7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z7" s="1" t="s">
+      <c r="Y7" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z7" t="s">
         <v>96</v>
       </c>
-      <c r="AA7" s="1" t="s">
+      <c r="AA7" t="s">
         <v>17</v>
       </c>
-      <c r="AB7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="1">
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
         <v>351</v>
       </c>
-      <c r="AD7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE7" s="1" t="s">
+      <c r="AD7" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE7" t="s">
         <v>52</v>
       </c>
-      <c r="AF7" s="1" t="s">
+      <c r="AF7" t="s">
         <v>40</v>
       </c>
-      <c r="AG7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ7" s="1" t="s">
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ7" t="s">
         <v>53</v>
       </c>
-      <c r="AK7" s="1" t="s">
+      <c r="AK7" t="s">
         <v>54</v>
       </c>
-      <c r="AL7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM7" s="1">
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
         <v>88</v>
       </c>
-      <c r="AN7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO7" s="1" t="s">
+      <c r="AN7" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO7" t="s">
         <v>120</v>
       </c>
-      <c r="AP7" s="1" t="s">
+      <c r="AP7" t="s">
         <v>24</v>
       </c>
-      <c r="AQ7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AR7" s="1">
-        <v>239</v>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>361</v>
       </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>83</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="1">
-        <v>0</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F8" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1">
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
         <v>160</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K8" s="1" t="s">
+      <c r="J8" t="s">
+        <v>123</v>
+      </c>
+      <c r="K8" t="s">
         <v>38</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" t="s">
         <v>34</v>
       </c>
-      <c r="M8" s="1">
-        <v>0</v>
-      </c>
-      <c r="N8" s="1">
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
         <v>269</v>
       </c>
-      <c r="O8" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P8" s="1" t="s">
+      <c r="O8" t="s">
+        <v>123</v>
+      </c>
+      <c r="P8" t="s">
         <v>28</v>
       </c>
-      <c r="Q8" s="1" t="s">
+      <c r="Q8" t="s">
         <v>29</v>
       </c>
-      <c r="R8" s="1">
-        <v>0</v>
-      </c>
-      <c r="S8" s="1">
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <v>187</v>
       </c>
-      <c r="T8" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U8" s="1" t="s">
+      <c r="T8" t="s">
+        <v>123</v>
+      </c>
+      <c r="U8" t="s">
         <v>69</v>
       </c>
-      <c r="V8" s="1" t="s">
+      <c r="V8" t="s">
         <v>54</v>
       </c>
-      <c r="W8" s="1">
-        <v>0</v>
-      </c>
-      <c r="X8" s="1">
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
         <v>300</v>
       </c>
-      <c r="Y8" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z8" s="1" t="s">
+      <c r="Y8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z8" t="s">
         <v>105</v>
       </c>
-      <c r="AA8" s="1" t="s">
+      <c r="AA8" t="s">
         <v>24</v>
       </c>
-      <c r="AB8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE8" s="1" t="s">
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE8" t="s">
         <v>115</v>
       </c>
-      <c r="AF8" s="1" t="s">
+      <c r="AF8" t="s">
         <v>24</v>
       </c>
-      <c r="AG8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="1">
-        <v>265</v>
-      </c>
-      <c r="AI8" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ8" s="1" t="s">
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>346</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ8" t="s">
         <v>98</v>
       </c>
-      <c r="AK8" s="1" t="s">
+      <c r="AK8" t="s">
         <v>17</v>
       </c>
-      <c r="AL8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM8" s="1">
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
         <v>97</v>
       </c>
-      <c r="AN8" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO8" s="1" t="s">
+      <c r="AN8" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO8" t="s">
         <v>64</v>
       </c>
-      <c r="AP8" s="1" t="s">
+      <c r="AP8" t="s">
         <v>54</v>
       </c>
-      <c r="AQ8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AR8" s="1">
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
         <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>91</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="1">
-        <v>0</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F9" s="1" t="s">
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>123</v>
+      </c>
+      <c r="F9" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1">
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
         <v>285</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K9" s="1" t="s">
+      <c r="J9" t="s">
+        <v>123</v>
+      </c>
+      <c r="K9" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="L9" t="s">
         <v>54</v>
       </c>
-      <c r="M9" s="1">
-        <v>0</v>
-      </c>
-      <c r="N9" s="1">
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
         <v>280</v>
       </c>
-      <c r="O9" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P9" s="1" t="s">
+      <c r="O9" t="s">
+        <v>123</v>
+      </c>
+      <c r="P9" t="s">
         <v>77</v>
       </c>
-      <c r="Q9" s="1" t="s">
+      <c r="Q9" t="s">
         <v>15</v>
       </c>
-      <c r="R9" s="1">
-        <v>0</v>
-      </c>
-      <c r="S9" s="1">
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
         <v>240</v>
       </c>
-      <c r="T9" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U9" s="1" t="s">
+      <c r="T9" t="s">
+        <v>123</v>
+      </c>
+      <c r="U9" t="s">
         <v>78</v>
       </c>
-      <c r="V9" s="1" t="s">
+      <c r="V9" t="s">
         <v>24</v>
       </c>
-      <c r="W9" s="1">
-        <v>0</v>
-      </c>
-      <c r="X9" s="1">
-        <v>181</v>
-      </c>
-      <c r="Y9" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z9" s="1" t="s">
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>205</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z9" t="s">
         <v>51</v>
       </c>
-      <c r="AA9" s="1" t="s">
+      <c r="AA9" t="s">
         <v>24</v>
       </c>
-      <c r="AB9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="1">
-        <v>20</v>
-      </c>
-      <c r="AD9" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE9" s="1" t="s">
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>24</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE9" t="s">
         <v>62</v>
       </c>
-      <c r="AF9" s="1" t="s">
+      <c r="AF9" t="s">
         <v>23</v>
       </c>
-      <c r="AG9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="1">
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
         <v>171</v>
       </c>
-      <c r="AI9" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ9" s="1" t="s">
+      <c r="AI9" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ9" t="s">
         <v>33</v>
       </c>
-      <c r="AK9" s="1" t="s">
+      <c r="AK9" t="s">
         <v>34</v>
       </c>
-      <c r="AL9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM9" s="1">
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
         <v>392</v>
       </c>
-      <c r="AN9" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO9" s="1" t="s">
+      <c r="AN9" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO9" t="s">
         <v>73</v>
       </c>
-      <c r="AP9" s="1" t="s">
+      <c r="AP9" t="s">
         <v>23</v>
       </c>
-      <c r="AQ9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AR9" s="1">
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
         <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>109</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="1">
-        <v>0</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
         <v>45</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F10" s="1" t="s">
+      <c r="E10" t="s">
+        <v>123</v>
+      </c>
+      <c r="F10" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1">
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
         <v>69</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K10" s="1" t="s">
+      <c r="J10" t="s">
+        <v>123</v>
+      </c>
+      <c r="K10" t="s">
         <v>102</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="L10" t="s">
         <v>54</v>
       </c>
-      <c r="M10" s="1">
-        <v>0</v>
-      </c>
-      <c r="N10" s="1">
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
         <v>219</v>
       </c>
-      <c r="O10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P10" s="1" t="s">
+      <c r="O10" t="s">
+        <v>123</v>
+      </c>
+      <c r="P10" t="s">
         <v>18</v>
       </c>
-      <c r="Q10" s="1" t="s">
+      <c r="Q10" t="s">
         <v>15</v>
       </c>
-      <c r="R10" s="1">
-        <v>0</v>
-      </c>
-      <c r="S10" s="1">
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
         <v>115</v>
       </c>
-      <c r="T10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U10" s="1" t="s">
+      <c r="T10" t="s">
+        <v>123</v>
+      </c>
+      <c r="U10" t="s">
         <v>60</v>
       </c>
-      <c r="V10" s="1" t="s">
+      <c r="V10" t="s">
         <v>13</v>
       </c>
-      <c r="W10" s="1">
-        <v>0</v>
-      </c>
-      <c r="X10" s="1">
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
         <v>38</v>
       </c>
-      <c r="Y10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z10" s="1" t="s">
+      <c r="Y10" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z10" t="s">
         <v>31</v>
       </c>
-      <c r="AA10" s="1" t="s">
+      <c r="AA10" t="s">
         <v>21</v>
       </c>
-      <c r="AB10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="1">
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
         <v>415</v>
       </c>
-      <c r="AD10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE10" s="1" t="s">
+      <c r="AD10" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE10" t="s">
         <v>97</v>
       </c>
-      <c r="AF10" s="1" t="s">
+      <c r="AF10" t="s">
         <v>23</v>
       </c>
-      <c r="AG10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="1">
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
         <v>381</v>
       </c>
-      <c r="AI10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ10" s="1" t="s">
+      <c r="AI10" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ10" t="s">
         <v>81</v>
       </c>
-      <c r="AK10" s="1" t="s">
+      <c r="AK10" t="s">
         <v>54</v>
       </c>
-      <c r="AL10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM10" s="1">
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
         <v>166</v>
       </c>
-      <c r="AN10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO10" s="1" t="s">
+      <c r="AN10" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO10" t="s">
         <v>99</v>
       </c>
-      <c r="AP10" s="1" t="s">
+      <c r="AP10" t="s">
         <v>23</v>
       </c>
-      <c r="AQ10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AR10" s="1">
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
         <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="1">
-        <v>0</v>
-      </c>
-      <c r="D11" s="1">
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
         <v>311</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F11" s="1" t="s">
+      <c r="E11" t="s">
+        <v>123</v>
+      </c>
+      <c r="F11" t="s">
         <v>110</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" t="s">
         <v>40</v>
       </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1">
-        <v>365</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K11" s="1" t="s">
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>498</v>
+      </c>
+      <c r="J11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K11" t="s">
         <v>67</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="L11" t="s">
         <v>21</v>
       </c>
-      <c r="M11" s="1">
-        <v>0</v>
-      </c>
-      <c r="N11" s="1">
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
         <v>190</v>
       </c>
-      <c r="O11" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P11" s="1" t="s">
+      <c r="O11" t="s">
+        <v>123</v>
+      </c>
+      <c r="P11" t="s">
         <v>103</v>
       </c>
-      <c r="Q11" s="1" t="s">
+      <c r="Q11" t="s">
         <v>40</v>
       </c>
-      <c r="R11" s="1">
-        <v>0</v>
-      </c>
-      <c r="S11" s="1">
-        <v>323</v>
-      </c>
-      <c r="T11" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U11" s="1" t="s">
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>379</v>
+      </c>
+      <c r="T11" t="s">
+        <v>123</v>
+      </c>
+      <c r="U11" t="s">
         <v>113</v>
       </c>
-      <c r="V11" s="1" t="s">
+      <c r="V11" t="s">
         <v>54</v>
       </c>
-      <c r="W11" s="1">
-        <v>0</v>
-      </c>
-      <c r="X11" s="1">
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
         <v>138</v>
       </c>
-      <c r="Y11" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z11" s="1" t="s">
+      <c r="Y11" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z11" t="s">
         <v>87</v>
       </c>
-      <c r="AA11" s="1" t="s">
+      <c r="AA11" t="s">
         <v>21</v>
       </c>
-      <c r="AB11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="1">
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
         <v>211</v>
       </c>
-      <c r="AD11" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE11" s="1" t="s">
+      <c r="AD11" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE11" t="s">
         <v>106</v>
       </c>
-      <c r="AF11" s="1" t="s">
+      <c r="AF11" t="s">
         <v>34</v>
       </c>
-      <c r="AG11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="1">
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
         <v>392</v>
       </c>
-      <c r="AI11" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ11" s="1" t="s">
+      <c r="AI11" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ11" t="s">
         <v>116</v>
       </c>
-      <c r="AK11" s="1" t="s">
+      <c r="AK11" t="s">
         <v>13</v>
       </c>
-      <c r="AL11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM11" s="1">
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
         <v>384</v>
       </c>
-      <c r="AN11" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO11" s="1" t="s">
+      <c r="AN11" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO11" t="s">
         <v>108</v>
       </c>
-      <c r="AP11" s="1" t="s">
+      <c r="AP11" t="s">
         <v>13</v>
       </c>
-      <c r="AQ11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AR11" s="1">
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
         <v>299</v>
       </c>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>119</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="1">
-        <v>0</v>
-      </c>
-      <c r="D12" s="1">
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
         <v>495</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F12" s="1" t="s">
+      <c r="E12" t="s">
+        <v>123</v>
+      </c>
+      <c r="F12" t="s">
         <v>92</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1">
-        <v>325</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K12" s="1" t="s">
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>446</v>
+      </c>
+      <c r="J12" t="s">
+        <v>123</v>
+      </c>
+      <c r="K12" t="s">
         <v>93</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="L12" t="s">
         <v>54</v>
       </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
-      <c r="N12" s="1">
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
         <v>223</v>
       </c>
-      <c r="O12" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P12" s="1" t="s">
+      <c r="O12" t="s">
+        <v>123</v>
+      </c>
+      <c r="P12" t="s">
         <v>85</v>
       </c>
-      <c r="Q12" s="1" t="s">
+      <c r="Q12" t="s">
         <v>23</v>
       </c>
-      <c r="R12" s="1">
-        <v>0</v>
-      </c>
-      <c r="S12" s="1">
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
         <v>360</v>
       </c>
-      <c r="T12" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U12" s="1" t="s">
+      <c r="T12" t="s">
+        <v>123</v>
+      </c>
+      <c r="U12" t="s">
         <v>19</v>
       </c>
-      <c r="V12" s="1" t="s">
+      <c r="V12" t="s">
         <v>15</v>
       </c>
-      <c r="W12" s="1">
-        <v>0</v>
-      </c>
-      <c r="X12" s="1">
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
         <v>271</v>
       </c>
-      <c r="Y12" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z12" s="1" t="s">
+      <c r="Y12" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z12" t="s">
         <v>20</v>
       </c>
-      <c r="AA12" s="1" t="s">
+      <c r="AA12" t="s">
         <v>21</v>
       </c>
-      <c r="AB12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="1">
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
         <v>284</v>
       </c>
-      <c r="AD12" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE12" s="1" t="s">
+      <c r="AD12" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE12" t="s">
         <v>80</v>
       </c>
-      <c r="AF12" s="1" t="s">
+      <c r="AF12" t="s">
         <v>34</v>
       </c>
-      <c r="AG12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="1">
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
         <v>379</v>
       </c>
-      <c r="AI12" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ12" s="1" t="s">
+      <c r="AI12" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ12" t="s">
         <v>122</v>
       </c>
-      <c r="AK12" s="1" t="s">
+      <c r="AK12" t="s">
         <v>23</v>
       </c>
-      <c r="AL12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="1">
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
         <v>509</v>
       </c>
-      <c r="AN12" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO12" s="1" t="s">
+      <c r="AN12" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO12" t="s">
         <v>117</v>
       </c>
-      <c r="AP12" s="1" t="s">
+      <c r="AP12" t="s">
         <v>40</v>
       </c>
-      <c r="AQ12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AR12" s="1">
-        <v>303</v>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>369</v>
       </c>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="1">
-        <v>0</v>
-      </c>
-      <c r="D13" s="1">
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
         <v>16</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F13" s="1" t="s">
+      <c r="E13" t="s">
+        <v>123</v>
+      </c>
+      <c r="F13" t="s">
         <v>57</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1">
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>276</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K13" s="1" t="s">
+      <c r="J13" t="s">
+        <v>123</v>
+      </c>
+      <c r="K13" t="s">
         <v>27</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="L13" t="s">
         <v>23</v>
       </c>
-      <c r="M13" s="1">
-        <v>0</v>
-      </c>
-      <c r="N13" s="1">
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
         <v>504</v>
       </c>
-      <c r="O13" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P13" s="1" t="s">
+      <c r="O13" t="s">
+        <v>123</v>
+      </c>
+      <c r="P13" t="s">
         <v>94</v>
       </c>
-      <c r="Q13" s="1" t="s">
+      <c r="Q13" t="s">
         <v>21</v>
       </c>
-      <c r="R13" s="1">
-        <v>0</v>
-      </c>
-      <c r="S13" s="1">
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
         <v>67</v>
       </c>
-      <c r="T13" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U13" s="1" t="s">
+      <c r="T13" t="s">
+        <v>123</v>
+      </c>
+      <c r="U13" t="s">
         <v>95</v>
       </c>
-      <c r="V13" s="1" t="s">
+      <c r="V13" t="s">
         <v>15</v>
       </c>
-      <c r="W13" s="1">
-        <v>0</v>
-      </c>
-      <c r="X13" s="1">
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
         <v>297</v>
       </c>
-      <c r="Y13" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z13" s="1" t="s">
+      <c r="Y13" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z13" t="s">
         <v>114</v>
       </c>
-      <c r="AA13" s="1" t="s">
+      <c r="AA13" t="s">
         <v>13</v>
       </c>
-      <c r="AB13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="1">
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
         <v>252</v>
       </c>
-      <c r="AD13" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE13" s="1" t="s">
+      <c r="AD13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE13" t="s">
         <v>71</v>
       </c>
-      <c r="AF13" s="1" t="s">
+      <c r="AF13" t="s">
         <v>21</v>
       </c>
-      <c r="AG13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="1">
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
         <v>56</v>
       </c>
-      <c r="AI13" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ13" s="1" t="s">
+      <c r="AI13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ13" t="s">
         <v>72</v>
       </c>
-      <c r="AK13" s="1" t="s">
+      <c r="AK13" t="s">
         <v>29</v>
       </c>
-      <c r="AL13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM13" s="1">
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
         <v>381</v>
       </c>
-      <c r="AN13" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO13" s="1" t="s">
+      <c r="AN13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO13" t="s">
         <v>35</v>
       </c>
-      <c r="AP13" s="1" t="s">
+      <c r="AP13" t="s">
         <v>21</v>
       </c>
-      <c r="AQ13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AR13" s="1">
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
         <v>442</v>
       </c>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="V14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="W14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="X14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AC14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AD14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AF14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AG14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AH14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AI14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AK14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AL14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AM14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AN14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO14" s="1" t="s">
+      <c r="A14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C14" t="s">
+        <v>123</v>
+      </c>
+      <c r="D14" t="s">
+        <v>123</v>
+      </c>
+      <c r="E14" t="s">
+        <v>123</v>
+      </c>
+      <c r="F14" t="s">
+        <v>123</v>
+      </c>
+      <c r="G14" t="s">
+        <v>123</v>
+      </c>
+      <c r="H14" t="s">
+        <v>123</v>
+      </c>
+      <c r="I14" t="s">
+        <v>123</v>
+      </c>
+      <c r="J14" t="s">
+        <v>123</v>
+      </c>
+      <c r="K14" t="s">
+        <v>123</v>
+      </c>
+      <c r="L14" t="s">
+        <v>123</v>
+      </c>
+      <c r="M14" t="s">
+        <v>123</v>
+      </c>
+      <c r="N14" t="s">
+        <v>123</v>
+      </c>
+      <c r="O14" t="s">
+        <v>123</v>
+      </c>
+      <c r="P14" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>123</v>
+      </c>
+      <c r="R14" t="s">
+        <v>123</v>
+      </c>
+      <c r="S14" t="s">
+        <v>123</v>
+      </c>
+      <c r="T14" t="s">
+        <v>123</v>
+      </c>
+      <c r="U14" t="s">
+        <v>123</v>
+      </c>
+      <c r="V14" t="s">
+        <v>123</v>
+      </c>
+      <c r="W14" t="s">
+        <v>123</v>
+      </c>
+      <c r="X14" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO14" t="s">
         <v>82</v>
       </c>
-      <c r="AP14" s="1" t="s">
+      <c r="AP14" t="s">
         <v>23</v>
       </c>
-      <c r="AQ14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AR14" s="1">
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
         <v>479</v>
       </c>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>118</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C15" s="1">
-        <v>0</v>
-      </c>
-      <c r="D15" s="1">
-        <v>1608</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F15" s="1" t="s">
+      <c r="B15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <f>SUM(D3:D13)</f>
+        <v>1674</v>
+      </c>
+      <c r="E15" t="s">
+        <v>123</v>
+      </c>
+      <c r="F15" t="s">
         <v>118</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0</v>
-      </c>
-      <c r="I15" s="1">
+      <c r="G15" t="s">
+        <v>123</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <f>SUM(I3:I13)</f>
+        <v>2447</v>
+      </c>
+      <c r="J15" t="s">
+        <v>123</v>
+      </c>
+      <c r="K15" t="s">
+        <v>118</v>
+      </c>
+      <c r="L15" t="s">
+        <v>123</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>2703</v>
+      </c>
+      <c r="O15" t="s">
+        <v>123</v>
+      </c>
+      <c r="P15" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>123</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <f>SUM(S3:S13)</f>
+        <v>2263</v>
+      </c>
+      <c r="T15" t="s">
+        <v>123</v>
+      </c>
+      <c r="U15" t="s">
+        <v>118</v>
+      </c>
+      <c r="V15" t="s">
+        <v>123</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <f>SUM(X3:X13)</f>
         <v>2148</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K15" s="1" t="s">
+      <c r="Y15" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z15" t="s">
         <v>118</v>
       </c>
-      <c r="L15" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="M15" s="1">
-        <v>0</v>
-      </c>
-      <c r="N15" s="1">
-        <v>2703</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P15" s="1" t="s">
+      <c r="AA15" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <f>SUM(AC3:AC13)</f>
+        <v>2310</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE15" t="s">
         <v>118</v>
       </c>
-      <c r="Q15" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="R15" s="1">
-        <v>0</v>
-      </c>
-      <c r="S15" s="1">
-        <v>2159</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U15" s="1" t="s">
+      <c r="AF15" t="s">
+        <v>123</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <f>SUM(AH3:AH13)</f>
+        <v>2581</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ15" t="s">
         <v>118</v>
       </c>
-      <c r="V15" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="W15" s="1">
-        <v>0</v>
-      </c>
-      <c r="X15" s="1">
-        <v>2124</v>
-      </c>
-      <c r="Y15" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z15" s="1" t="s">
+      <c r="AK15" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <f>SUM(AM3:AM13)</f>
+        <v>3107</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO15" t="s">
         <v>118</v>
       </c>
-      <c r="AA15" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="1">
-        <v>2204</v>
-      </c>
-      <c r="AD15" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE15" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AF15" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AG15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="1">
-        <v>2500</v>
-      </c>
-      <c r="AI15" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ15" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AK15" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AL15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM15" s="1">
-        <v>2875</v>
-      </c>
-      <c r="AN15" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO15" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AP15" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AQ15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AR15" s="1">
-        <v>3101</v>
+      <c r="AP15" t="s">
+        <v>123</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <f>SUM(AR3:AR14)</f>
+        <v>3289</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ipl26\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B1E294-73E3-48FB-A79F-FBEB3D50A0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC36D3F-C665-4A8D-B124-D0174F83A081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3636" yWindow="3072" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1056,16 +1056,16 @@
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1">
         <v>0</v>
       </c>
       <c r="D3" s="1">
-        <v>456</v>
+        <v>0</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>123</v>
@@ -1161,45 +1161,45 @@
         <v>123</v>
       </c>
       <c r="AJ3" s="1" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="AL3" s="1">
         <v>0</v>
       </c>
       <c r="AM3" s="1">
-        <v>0</v>
+        <v>401</v>
       </c>
       <c r="AN3" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO3" s="1" t="s">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AP3" s="1" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="AQ3" s="1">
         <v>0</v>
       </c>
       <c r="AR3" s="1">
-        <v>361</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1">
         <v>0</v>
       </c>
       <c r="D4" s="1">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>123</v>
@@ -1235,99 +1235,99 @@
         <v>123</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="Q4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="1">
+        <v>0</v>
+      </c>
+      <c r="S4" s="1">
+        <v>180</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="W4" s="1">
+        <v>0</v>
+      </c>
+      <c r="X4" s="1">
+        <v>171</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>170</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R4" s="1">
-        <v>0</v>
-      </c>
-      <c r="S4" s="1">
-        <v>417</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W4" s="1">
-        <v>0</v>
-      </c>
-      <c r="X4" s="1">
-        <v>185</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB4" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="1">
-        <v>189</v>
-      </c>
-      <c r="AD4" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF4" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="AG4" s="1">
         <v>0</v>
       </c>
       <c r="AH4" s="1">
-        <v>0</v>
+        <v>432</v>
       </c>
       <c r="AI4" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AJ4" s="1" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="AK4" s="1" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="AL4" s="1">
         <v>0</v>
       </c>
       <c r="AM4" s="1">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="AN4" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO4" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="AP4" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AQ4" s="1">
         <v>0</v>
       </c>
       <c r="AR4" s="1">
-        <v>10</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
@@ -1339,16 +1339,16 @@
         <v>123</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
       <c r="I5" s="1">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>123</v>
@@ -1369,82 +1369,82 @@
         <v>123</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="Q5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="R5" s="1">
+        <v>0</v>
+      </c>
+      <c r="S5" s="1">
+        <v>137</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="W5" s="1">
+        <v>0</v>
+      </c>
+      <c r="X5" s="1">
+        <v>352</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>95</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="R5" s="1">
-        <v>0</v>
-      </c>
-      <c r="S5" s="1">
-        <v>180</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="V5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W5" s="1">
-        <v>0</v>
-      </c>
-      <c r="X5" s="1">
-        <v>328</v>
-      </c>
-      <c r="Y5" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z5" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="1">
-        <v>170</v>
-      </c>
-      <c r="AD5" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="AF5" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="AG5" s="1">
         <v>0</v>
       </c>
       <c r="AH5" s="1">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AJ5" s="1" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="AK5" s="1" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="AL5" s="1">
         <v>0</v>
       </c>
       <c r="AM5" s="1">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="AN5" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO5" s="1" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="AP5" s="1" t="s">
         <v>29</v>
@@ -1453,15 +1453,15 @@
         <v>0</v>
       </c>
       <c r="AR5" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1">
         <v>0</v>
@@ -1473,16 +1473,16 @@
         <v>123</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>123</v>
@@ -1503,96 +1503,96 @@
         <v>123</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="Q6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1">
+        <v>160</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W6" s="1">
+        <v>0</v>
+      </c>
+      <c r="X6" s="1">
+        <v>455</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z6" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R6" s="1">
-        <v>0</v>
-      </c>
-      <c r="S6" s="1">
-        <v>137</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="V6" s="1" t="s">
+      <c r="AB6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>423</v>
+      </c>
+      <c r="AD6" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="1">
+        <v>171</v>
+      </c>
+      <c r="AI6" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ6" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="W6" s="1">
-        <v>0</v>
-      </c>
-      <c r="X6" s="1">
-        <v>171</v>
-      </c>
-      <c r="Y6" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z6" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="1">
-        <v>95</v>
-      </c>
-      <c r="AD6" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE6" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AF6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="1">
-        <v>220</v>
-      </c>
-      <c r="AI6" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AK6" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="AL6" s="1">
         <v>0</v>
       </c>
       <c r="AM6" s="1">
-        <v>392</v>
+        <v>97</v>
       </c>
       <c r="AN6" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO6" s="1" t="s">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="AP6" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="AQ6" s="1">
         <v>0</v>
       </c>
       <c r="AR6" s="1">
-        <v>293</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>24</v>
@@ -1601,88 +1601,88 @@
         <v>0</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="G7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>285</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>313</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1">
+        <v>187</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="W7" s="1">
+        <v>0</v>
+      </c>
+      <c r="X7" s="1">
+        <v>59</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M7" s="1">
-        <v>0</v>
-      </c>
-      <c r="N7" s="1">
-        <v>269</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="R7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1">
-        <v>160</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="V7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="W7" s="1">
-        <v>0</v>
-      </c>
-      <c r="X7" s="1">
-        <v>300</v>
-      </c>
-      <c r="Y7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z7" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="AA7" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="AB7" s="1">
         <v>0</v>
       </c>
       <c r="AC7" s="1">
-        <v>423</v>
+        <v>0</v>
       </c>
       <c r="AD7" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="AF7" s="1" t="s">
         <v>15</v>
@@ -1691,7 +1691,7 @@
         <v>0</v>
       </c>
       <c r="AH7" s="1">
-        <v>145</v>
+        <v>220</v>
       </c>
       <c r="AI7" s="1" t="s">
         <v>123</v>
@@ -1712,111 +1712,111 @@
         <v>123</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>117</v>
+        <v>45</v>
       </c>
       <c r="AP7" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="AQ7" s="1">
         <v>0</v>
       </c>
       <c r="AR7" s="1">
-        <v>369</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1">
         <v>0</v>
       </c>
       <c r="D8" s="1">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>285</v>
+        <v>69</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>16</v>
+        <v>102</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="M8" s="1">
         <v>0</v>
       </c>
       <c r="N8" s="1">
-        <v>392</v>
+        <v>292</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="R8" s="1">
         <v>0</v>
       </c>
       <c r="S8" s="1">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="T8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>50</v>
+        <v>113</v>
       </c>
       <c r="V8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="W8" s="1">
+        <v>0</v>
+      </c>
+      <c r="X8" s="1">
+        <v>138</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W8" s="1">
-        <v>0</v>
-      </c>
-      <c r="X8" s="1">
-        <v>268</v>
-      </c>
-      <c r="Y8" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z8" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA8" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="AB8" s="1">
         <v>0</v>
       </c>
       <c r="AC8" s="1">
-        <v>0</v>
+        <v>332</v>
       </c>
       <c r="AD8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="AF8" s="1" t="s">
         <v>15</v>
@@ -1825,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="AH8" s="1">
-        <v>210</v>
+        <v>145</v>
       </c>
       <c r="AI8" s="1" t="s">
         <v>123</v>
@@ -1846,30 +1846,30 @@
         <v>123</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="AP8" s="1" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="AQ8" s="1">
         <v>0</v>
       </c>
       <c r="AR8" s="1">
-        <v>300</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1">
         <v>0</v>
       </c>
       <c r="D9" s="1">
-        <v>45</v>
+        <v>497</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>123</v>
@@ -1884,52 +1884,52 @@
         <v>0</v>
       </c>
       <c r="I9" s="1">
-        <v>160</v>
+        <v>204</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>123</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="M9" s="1">
         <v>0</v>
       </c>
       <c r="N9" s="1">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>123</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="R9" s="1">
         <v>0</v>
       </c>
       <c r="S9" s="1">
-        <v>187</v>
+        <v>240</v>
       </c>
       <c r="T9" s="1" t="s">
         <v>123</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W9" s="1">
         <v>0</v>
       </c>
       <c r="X9" s="1">
-        <v>59</v>
+        <v>271</v>
       </c>
       <c r="Y9" s="1" t="s">
         <v>123</v>
@@ -1950,16 +1950,16 @@
         <v>123</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>97</v>
+        <v>32</v>
       </c>
       <c r="AF9" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AG9" s="1">
         <v>0</v>
       </c>
       <c r="AH9" s="1">
-        <v>381</v>
+        <v>210</v>
       </c>
       <c r="AI9" s="1" t="s">
         <v>123</v>
@@ -1980,7 +1980,7 @@
         <v>123</v>
       </c>
       <c r="AO9" s="1" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="AP9" s="1" t="s">
         <v>23</v>
@@ -1989,57 +1989,57 @@
         <v>0</v>
       </c>
       <c r="AR9" s="1">
-        <v>275</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1">
         <v>0</v>
       </c>
       <c r="D10" s="1">
-        <v>237</v>
+        <v>388</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
       </c>
       <c r="I10" s="1">
-        <v>69</v>
+        <v>446</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>123</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="M10" s="1">
         <v>0</v>
       </c>
       <c r="N10" s="1">
-        <v>219</v>
+        <v>392</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>123</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="Q10" s="1" t="s">
         <v>15</v>
@@ -2048,22 +2048,22 @@
         <v>0</v>
       </c>
       <c r="S10" s="1">
-        <v>240</v>
+        <v>115</v>
       </c>
       <c r="T10" s="1" t="s">
         <v>123</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="W10" s="1">
         <v>0</v>
       </c>
       <c r="X10" s="1">
-        <v>138</v>
+        <v>297</v>
       </c>
       <c r="Y10" s="1" t="s">
         <v>123</v>
@@ -2078,22 +2078,22 @@
         <v>0</v>
       </c>
       <c r="AC10" s="1">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="AD10" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="AF10" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AG10" s="1">
         <v>0</v>
       </c>
       <c r="AH10" s="1">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="AI10" s="1" t="s">
         <v>123</v>
@@ -2114,21 +2114,21 @@
         <v>123</v>
       </c>
       <c r="AO10" s="1" t="s">
-        <v>108</v>
+        <v>35</v>
       </c>
       <c r="AP10" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AQ10" s="1">
         <v>0</v>
       </c>
       <c r="AR10" s="1">
-        <v>426</v>
+        <v>452</v>
       </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>29</v>
@@ -2137,67 +2137,67 @@
         <v>0</v>
       </c>
       <c r="D11" s="1">
-        <v>311</v>
+        <v>258</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
       </c>
       <c r="I11" s="1">
+        <v>120</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>376</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="R11" s="1">
+        <v>0</v>
+      </c>
+      <c r="S11" s="1">
         <v>446</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" s="1">
-        <v>0</v>
-      </c>
-      <c r="N11" s="1">
-        <v>190</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R11" s="1">
-        <v>0</v>
-      </c>
-      <c r="S11" s="1">
-        <v>115</v>
-      </c>
       <c r="T11" s="1" t="s">
         <v>123</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="W11" s="1">
         <v>0</v>
       </c>
       <c r="X11" s="1">
-        <v>271</v>
+        <v>205</v>
       </c>
       <c r="Y11" s="1" t="s">
         <v>123</v>
@@ -2212,7 +2212,7 @@
         <v>0</v>
       </c>
       <c r="AC11" s="1">
-        <v>211</v>
+        <v>288</v>
       </c>
       <c r="AD11" s="1" t="s">
         <v>123</v>
@@ -2227,7 +2227,7 @@
         <v>0</v>
       </c>
       <c r="AH11" s="1">
-        <v>379</v>
+        <v>451</v>
       </c>
       <c r="AI11" s="1" t="s">
         <v>123</v>
@@ -2248,30 +2248,30 @@
         <v>123</v>
       </c>
       <c r="AO11" s="1" t="s">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="AP11" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ11" s="1">
         <v>0</v>
       </c>
       <c r="AR11" s="1">
-        <v>442</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1">
         <v>0</v>
       </c>
       <c r="D12" s="1">
-        <v>497</v>
+        <v>550</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>123</v>
@@ -2292,16 +2292,16 @@
         <v>123</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="M12" s="1">
         <v>0</v>
       </c>
       <c r="N12" s="1">
-        <v>223</v>
+        <v>382</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>123</v>
@@ -2322,31 +2322,31 @@
         <v>123</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="W12" s="1">
         <v>0</v>
       </c>
       <c r="X12" s="1">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="Y12" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AB12" s="1">
         <v>0</v>
       </c>
       <c r="AC12" s="1">
-        <v>284</v>
+        <v>209</v>
       </c>
       <c r="AD12" s="1" t="s">
         <v>123</v>
@@ -2367,31 +2367,31 @@
         <v>123</v>
       </c>
       <c r="AJ12" s="1" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="AK12" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AL12" s="1">
         <v>0</v>
       </c>
       <c r="AM12" s="1">
-        <v>381</v>
+        <v>469</v>
       </c>
       <c r="AN12" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO12" s="1" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AP12" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AQ12" s="1">
         <v>0</v>
       </c>
       <c r="AR12" s="1">
-        <v>479</v>
+        <v>426</v>
       </c>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.3">
@@ -2420,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>123</v>
@@ -2441,31 +2441,31 @@
         <v>123</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="R13" s="1">
         <v>0</v>
       </c>
       <c r="S13" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T13" s="1" t="s">
         <v>123</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="W13" s="1">
         <v>0</v>
       </c>
       <c r="X13" s="1">
-        <v>205</v>
+        <v>430</v>
       </c>
       <c r="Y13" s="1" t="s">
         <v>123</v>
@@ -2495,7 +2495,7 @@
         <v>0</v>
       </c>
       <c r="AH13" s="1">
-        <v>56</v>
+        <v>127</v>
       </c>
       <c r="AI13" s="1" t="s">
         <v>123</v>
@@ -2516,16 +2516,16 @@
         <v>123</v>
       </c>
       <c r="AO13" s="1" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="AP13" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="AQ13" s="1">
         <v>0</v>
       </c>
       <c r="AR13" s="1">
-        <v>238</v>
+        <v>479</v>
       </c>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.3">
@@ -2659,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="AR14" s="1">
-        <v>260</v>
+        <v>268</v>
       </c>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.3">
@@ -2673,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="1">
-        <v>1676</v>
+        <v>1991</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>123</v>
@@ -2688,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="1">
-        <v>2447</v>
+        <v>2518</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>123</v>
@@ -2703,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="1">
-        <v>2882</v>
+        <v>3291</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>123</v>
@@ -2718,7 +2718,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="1">
-        <v>2281</v>
+        <v>2364</v>
       </c>
       <c r="T15" s="1" t="s">
         <v>123</v>
@@ -2733,7 +2733,7 @@
         <v>0</v>
       </c>
       <c r="X15" s="1">
-        <v>2222</v>
+        <v>2664</v>
       </c>
       <c r="Y15" s="1" t="s">
         <v>123</v>
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="AC15" s="1">
-        <v>2427</v>
+        <v>2589</v>
       </c>
       <c r="AD15" s="1" t="s">
         <v>123</v>
@@ -2763,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="AH15" s="1">
-        <v>2581</v>
+        <v>2764</v>
       </c>
       <c r="AI15" s="1" t="s">
         <v>123</v>
@@ -2778,7 +2778,7 @@
         <v>0</v>
       </c>
       <c r="AM15" s="1">
-        <v>3217</v>
+        <v>3349</v>
       </c>
       <c r="AN15" s="1" t="s">
         <v>123</v>
@@ -2793,7 +2793,7 @@
         <v>0</v>
       </c>
       <c r="AR15" s="1">
-        <v>3453</v>
+        <v>3556</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ipl26\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC36D3F-C665-4A8D-B124-D0174F83A081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD004E8-E96E-4BB9-AE3F-55985E91B31E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3636" yWindow="3072" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Teams" sheetId="1" r:id="rId1"/>
@@ -1131,16 +1131,16 @@
         <v>123</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB3" s="1">
         <v>0</v>
       </c>
       <c r="AC3" s="1">
-        <v>319</v>
+        <v>109</v>
       </c>
       <c r="AD3" s="1" t="s">
         <v>123</v>
@@ -1176,16 +1176,16 @@
         <v>123</v>
       </c>
       <c r="AO3" s="1" t="s">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AP3" s="1" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="AQ3" s="1">
         <v>0</v>
       </c>
       <c r="AR3" s="1">
-        <v>323</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.3">
@@ -1265,16 +1265,16 @@
         <v>123</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AB4" s="1">
         <v>0</v>
       </c>
       <c r="AC4" s="1">
-        <v>170</v>
+        <v>319</v>
       </c>
       <c r="AD4" s="1" t="s">
         <v>123</v>
@@ -1310,16 +1310,16 @@
         <v>123</v>
       </c>
       <c r="AO4" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AP4" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AQ4" s="1">
         <v>0</v>
       </c>
       <c r="AR4" s="1">
-        <v>361</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.3">
@@ -1384,67 +1384,67 @@
         <v>123</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="W5" s="1">
         <v>0</v>
       </c>
       <c r="X5" s="1">
-        <v>352</v>
+        <v>455</v>
       </c>
       <c r="Y5" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="AA5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>332</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AB5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="1">
-        <v>95</v>
-      </c>
-      <c r="AD5" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF5" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="AG5" s="1">
         <v>0</v>
       </c>
       <c r="AH5" s="1">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="AI5" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AJ5" s="1" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="AK5" s="1" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="AL5" s="1">
         <v>0</v>
       </c>
       <c r="AM5" s="1">
-        <v>123</v>
+        <v>469</v>
       </c>
       <c r="AN5" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO5" s="1" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="AP5" s="1" t="s">
         <v>29</v>
@@ -1453,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="AR5" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
@@ -1488,16 +1488,16 @@
         <v>123</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
       </c>
       <c r="N6" s="1">
-        <v>270</v>
+        <v>313</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>123</v>
@@ -1518,22 +1518,22 @@
         <v>123</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="W6" s="1">
         <v>0</v>
       </c>
       <c r="X6" s="1">
-        <v>455</v>
+        <v>59</v>
       </c>
       <c r="Y6" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="AA6" s="1" t="s">
         <v>17</v>
@@ -1542,22 +1542,22 @@
         <v>0</v>
       </c>
       <c r="AC6" s="1">
-        <v>423</v>
+        <v>170</v>
       </c>
       <c r="AD6" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="AF6" s="1" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="AG6" s="1">
         <v>0</v>
       </c>
       <c r="AH6" s="1">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="1" t="s">
         <v>123</v>
@@ -1578,16 +1578,16 @@
         <v>123</v>
       </c>
       <c r="AO6" s="1" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AP6" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="AQ6" s="1">
         <v>0</v>
       </c>
       <c r="AR6" s="1">
-        <v>0</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
@@ -1616,28 +1616,28 @@
         <v>0</v>
       </c>
       <c r="I7" s="1">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>123</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="M7" s="1">
         <v>0</v>
       </c>
       <c r="N7" s="1">
-        <v>313</v>
+        <v>270</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>123</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="Q7" s="1" t="s">
         <v>29</v>
@@ -1646,111 +1646,111 @@
         <v>0</v>
       </c>
       <c r="S7" s="1">
-        <v>187</v>
+        <v>66</v>
       </c>
       <c r="T7" s="1" t="s">
         <v>123</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="W7" s="1">
         <v>0</v>
       </c>
       <c r="X7" s="1">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="Y7" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AB7" s="1">
         <v>0</v>
       </c>
       <c r="AC7" s="1">
-        <v>0</v>
+        <v>423</v>
       </c>
       <c r="AD7" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="AF7" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AG7" s="1">
         <v>0</v>
       </c>
       <c r="AH7" s="1">
-        <v>220</v>
+        <v>553</v>
       </c>
       <c r="AI7" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="AK7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL7" s="1">
         <v>0</v>
       </c>
       <c r="AM7" s="1">
-        <v>253</v>
+        <v>539</v>
       </c>
       <c r="AN7" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="AP7" s="1" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="AQ7" s="1">
         <v>0</v>
       </c>
       <c r="AR7" s="1">
-        <v>293</v>
+        <v>369</v>
       </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C8" s="1">
         <v>0</v>
       </c>
       <c r="D8" s="1">
-        <v>237</v>
+        <v>550</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>123</v>
@@ -1771,46 +1771,46 @@
         <v>123</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="R8" s="1">
         <v>0</v>
       </c>
       <c r="S8" s="1">
-        <v>94</v>
+        <v>446</v>
       </c>
       <c r="T8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="W8" s="1">
         <v>0</v>
       </c>
       <c r="X8" s="1">
-        <v>138</v>
+        <v>334</v>
       </c>
       <c r="Y8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AB8" s="1">
         <v>0</v>
       </c>
       <c r="AC8" s="1">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="1" t="s">
         <v>123</v>
@@ -1825,87 +1825,87 @@
         <v>0</v>
       </c>
       <c r="AH8" s="1">
-        <v>145</v>
+        <v>348</v>
       </c>
       <c r="AI8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AJ8" s="1" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="AK8" s="1" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="AL8" s="1">
         <v>0</v>
       </c>
       <c r="AM8" s="1">
-        <v>166</v>
+        <v>253</v>
       </c>
       <c r="AN8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="AP8" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="AQ8" s="1">
         <v>0</v>
       </c>
       <c r="AR8" s="1">
-        <v>369</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1">
         <v>0</v>
       </c>
       <c r="D9" s="1">
-        <v>497</v>
+        <v>237</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
       </c>
       <c r="I9" s="1">
-        <v>204</v>
+        <v>69</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>123</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="M9" s="1">
         <v>0</v>
       </c>
       <c r="N9" s="1">
-        <v>227</v>
+        <v>382</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>123</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="Q9" s="1" t="s">
         <v>15</v>
@@ -1914,13 +1914,13 @@
         <v>0</v>
       </c>
       <c r="S9" s="1">
-        <v>240</v>
+        <v>177</v>
       </c>
       <c r="T9" s="1" t="s">
         <v>123</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="V9" s="1" t="s">
         <v>15</v>
@@ -1929,52 +1929,52 @@
         <v>0</v>
       </c>
       <c r="X9" s="1">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c r="Y9" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="AA9" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AB9" s="1">
         <v>0</v>
       </c>
       <c r="AC9" s="1">
-        <v>24</v>
+        <v>209</v>
       </c>
       <c r="AD9" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="AF9" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="AG9" s="1">
         <v>0</v>
       </c>
       <c r="AH9" s="1">
-        <v>210</v>
+        <v>451</v>
       </c>
       <c r="AI9" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AJ9" s="1" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="AK9" s="1" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="AL9" s="1">
         <v>0</v>
       </c>
       <c r="AM9" s="1">
-        <v>307</v>
+        <v>166</v>
       </c>
       <c r="AN9" s="1" t="s">
         <v>123</v>
@@ -1989,146 +1989,146 @@
         <v>0</v>
       </c>
       <c r="AR9" s="1">
-        <v>300</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1">
+        <v>497</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>204</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
+        <v>227</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="1">
-        <v>0</v>
-      </c>
-      <c r="D10" s="1">
-        <v>388</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1">
-        <v>446</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M10" s="1">
-        <v>0</v>
-      </c>
-      <c r="N10" s="1">
-        <v>392</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q10" s="1" t="s">
+      <c r="R10" s="1">
+        <v>0</v>
+      </c>
+      <c r="S10" s="1">
+        <v>187</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="W10" s="1">
+        <v>0</v>
+      </c>
+      <c r="X10" s="1">
+        <v>352</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>24</v>
+      </c>
+      <c r="AD10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE10" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R10" s="1">
-        <v>0</v>
-      </c>
-      <c r="S10" s="1">
-        <v>115</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U10" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="V10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="W10" s="1">
-        <v>0</v>
-      </c>
-      <c r="X10" s="1">
-        <v>297</v>
-      </c>
-      <c r="Y10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="1">
-        <v>432</v>
-      </c>
-      <c r="AD10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE10" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="AF10" s="1" t="s">
+      <c r="AG10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="1">
+        <v>267</v>
+      </c>
+      <c r="AI10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="1">
+        <v>307</v>
+      </c>
+      <c r="AN10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO10" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AG10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="1">
-        <v>381</v>
-      </c>
-      <c r="AI10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ10" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AK10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="AL10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM10" s="1">
-        <v>494</v>
-      </c>
-      <c r="AN10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AP10" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="AQ10" s="1">
         <v>0</v>
       </c>
       <c r="AR10" s="1">
-        <v>452</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>29</v>
@@ -2137,52 +2137,52 @@
         <v>0</v>
       </c>
       <c r="D11" s="1">
-        <v>258</v>
+        <v>388</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
       </c>
       <c r="I11" s="1">
-        <v>120</v>
+        <v>446</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>123</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="M11" s="1">
         <v>0</v>
       </c>
       <c r="N11" s="1">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>123</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="R11" s="1">
         <v>0</v>
       </c>
       <c r="S11" s="1">
-        <v>446</v>
+        <v>94</v>
       </c>
       <c r="T11" s="1" t="s">
         <v>123</v>
@@ -2203,7 +2203,7 @@
         <v>123</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="AA11" s="1" t="s">
         <v>21</v>
@@ -2212,66 +2212,66 @@
         <v>0</v>
       </c>
       <c r="AC11" s="1">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="AD11" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="AF11" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="AG11" s="1">
         <v>0</v>
       </c>
       <c r="AH11" s="1">
-        <v>451</v>
+        <v>241</v>
       </c>
       <c r="AI11" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AJ11" s="1" t="s">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="AK11" s="1" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AL11" s="1">
         <v>0</v>
       </c>
       <c r="AM11" s="1">
-        <v>509</v>
+        <v>123</v>
       </c>
       <c r="AN11" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO11" s="1" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="AP11" s="1" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AQ11" s="1">
         <v>0</v>
       </c>
       <c r="AR11" s="1">
-        <v>275</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1">
         <v>0</v>
       </c>
       <c r="D12" s="1">
-        <v>550</v>
+        <v>258</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>123</v>
@@ -2292,31 +2292,31 @@
         <v>123</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="M12" s="1">
         <v>0</v>
       </c>
       <c r="N12" s="1">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>123</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="R12" s="1">
         <v>0</v>
       </c>
       <c r="S12" s="1">
-        <v>360</v>
+        <v>245</v>
       </c>
       <c r="T12" s="1" t="s">
         <v>123</v>
@@ -2337,16 +2337,16 @@
         <v>123</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="AB12" s="1">
         <v>0</v>
       </c>
       <c r="AC12" s="1">
-        <v>209</v>
+        <v>288</v>
       </c>
       <c r="AD12" s="1" t="s">
         <v>123</v>
@@ -2367,16 +2367,16 @@
         <v>123</v>
       </c>
       <c r="AJ12" s="1" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="AK12" s="1" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="AL12" s="1">
         <v>0</v>
       </c>
       <c r="AM12" s="1">
-        <v>469</v>
+        <v>494</v>
       </c>
       <c r="AN12" s="1" t="s">
         <v>123</v>
@@ -2435,22 +2435,22 @@
         <v>0</v>
       </c>
       <c r="N13" s="1">
-        <v>504</v>
+        <v>517</v>
       </c>
       <c r="O13" s="1" t="s">
         <v>123</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R13" s="1">
         <v>0</v>
       </c>
       <c r="S13" s="1">
-        <v>66</v>
+        <v>380</v>
       </c>
       <c r="T13" s="1" t="s">
         <v>123</v>
@@ -2525,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="AR13" s="1">
-        <v>479</v>
+        <v>515</v>
       </c>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.3">
@@ -2688,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="1">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>123</v>
@@ -2703,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="1">
-        <v>3291</v>
+        <v>3304</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>123</v>
@@ -2718,7 +2718,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="1">
-        <v>2364</v>
+        <v>2451</v>
       </c>
       <c r="T15" s="1" t="s">
         <v>123</v>
@@ -2733,7 +2733,7 @@
         <v>0</v>
       </c>
       <c r="X15" s="1">
-        <v>2664</v>
+        <v>2727</v>
       </c>
       <c r="Y15" s="1" t="s">
         <v>123</v>
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="AC15" s="1">
-        <v>2589</v>
+        <v>2603</v>
       </c>
       <c r="AD15" s="1" t="s">
         <v>123</v>
@@ -2763,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="AH15" s="1">
-        <v>2764</v>
+        <v>3235</v>
       </c>
       <c r="AI15" s="1" t="s">
         <v>123</v>
@@ -2778,7 +2778,7 @@
         <v>0</v>
       </c>
       <c r="AM15" s="1">
-        <v>3349</v>
+        <v>3379</v>
       </c>
       <c r="AN15" s="1" t="s">
         <v>123</v>
@@ -2793,7 +2793,7 @@
         <v>0</v>
       </c>
       <c r="AR15" s="1">
-        <v>3556</v>
+        <v>3710</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ipl26\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD004E8-E96E-4BB9-AE3F-55985E91B31E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DE10C5-4E27-47A5-B2DD-EC39CB49B940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Teams" sheetId="1" r:id="rId1"/>
@@ -1056,7 +1056,7 @@
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>13</v>
@@ -1065,135 +1065,135 @@
         <v>0</v>
       </c>
       <c r="D3" s="1">
-        <v>0</v>
+        <v>552</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1">
-        <v>498</v>
+        <v>34</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>123</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="M3" s="1">
         <v>0</v>
       </c>
       <c r="N3" s="1">
-        <v>535</v>
+        <v>0</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>123</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="R3" s="1">
         <v>0</v>
       </c>
       <c r="S3" s="1">
-        <v>379</v>
+        <v>446</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>123</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="V3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="W3" s="1">
+        <v>0</v>
+      </c>
+      <c r="X3" s="1">
+        <v>213</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>376</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="1">
+        <v>360</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="1">
+        <v>256</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="AP3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="W3" s="1">
-        <v>0</v>
-      </c>
-      <c r="X3" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB3" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="1">
-        <v>109</v>
-      </c>
-      <c r="AD3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AF3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG3" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="1">
-        <v>281</v>
-      </c>
-      <c r="AI3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ3" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AL3" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM3" s="1">
-        <v>401</v>
-      </c>
-      <c r="AN3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AP3" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="AQ3" s="1">
         <v>0</v>
       </c>
       <c r="AR3" s="1">
-        <v>361</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1">
         <v>0</v>
@@ -1205,25 +1205,25 @@
         <v>123</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H4" s="1">
         <v>0</v>
       </c>
       <c r="I4" s="1">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>123</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="M4" s="1">
         <v>0</v>
@@ -1250,46 +1250,46 @@
         <v>123</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="W4" s="1">
         <v>0</v>
       </c>
       <c r="X4" s="1">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AB4" s="1">
         <v>0</v>
       </c>
       <c r="AC4" s="1">
-        <v>319</v>
+        <v>364</v>
       </c>
       <c r="AD4" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="AF4" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="AG4" s="1">
         <v>0</v>
       </c>
       <c r="AH4" s="1">
-        <v>432</v>
+        <v>281</v>
       </c>
       <c r="AI4" s="1" t="s">
         <v>123</v>
@@ -1310,24 +1310,24 @@
         <v>123</v>
       </c>
       <c r="AO4" s="1" t="s">
-        <v>124</v>
+        <v>45</v>
       </c>
       <c r="AP4" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="AQ4" s="1">
         <v>0</v>
       </c>
       <c r="AR4" s="1">
-        <v>10</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
@@ -1339,61 +1339,61 @@
         <v>123</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>69</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
+        <v>270</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="1">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1">
-        <v>61</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5" s="1">
-        <v>0</v>
-      </c>
-      <c r="N5" s="1">
-        <v>0</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="R5" s="1">
         <v>0</v>
       </c>
       <c r="S5" s="1">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="T5" s="1" t="s">
         <v>123</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="W5" s="1">
         <v>0</v>
       </c>
       <c r="X5" s="1">
-        <v>455</v>
+        <v>71</v>
       </c>
       <c r="Y5" s="1" t="s">
         <v>123</v>
@@ -1414,54 +1414,54 @@
         <v>123</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="AF5" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AG5" s="1">
         <v>0</v>
       </c>
       <c r="AH5" s="1">
-        <v>189</v>
+        <v>432</v>
       </c>
       <c r="AI5" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AJ5" s="1" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="AK5" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="AL5" s="1">
         <v>0</v>
       </c>
       <c r="AM5" s="1">
-        <v>469</v>
+        <v>97</v>
       </c>
       <c r="AN5" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO5" s="1" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="AP5" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="AQ5" s="1">
         <v>0</v>
       </c>
       <c r="AR5" s="1">
-        <v>0</v>
+        <v>705</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1">
         <v>0</v>
@@ -1473,76 +1473,76 @@
         <v>123</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>120</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>618</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1">
+        <v>187</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="W6" s="1">
+        <v>0</v>
+      </c>
+      <c r="X6" s="1">
+        <v>138</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z6" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M6" s="1">
-        <v>0</v>
-      </c>
-      <c r="N6" s="1">
-        <v>313</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="R6" s="1">
-        <v>0</v>
-      </c>
-      <c r="S6" s="1">
-        <v>160</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="V6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="W6" s="1">
-        <v>0</v>
-      </c>
-      <c r="X6" s="1">
-        <v>59</v>
-      </c>
-      <c r="Y6" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z6" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA6" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="AB6" s="1">
         <v>0</v>
       </c>
       <c r="AC6" s="1">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="AD6" s="1" t="s">
         <v>123</v>
@@ -1563,120 +1563,120 @@
         <v>123</v>
       </c>
       <c r="AJ6" s="1" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="AK6" s="1" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="AL6" s="1">
         <v>0</v>
       </c>
       <c r="AM6" s="1">
-        <v>97</v>
+        <v>166</v>
       </c>
       <c r="AN6" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO6" s="1" t="s">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="AP6" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="AQ6" s="1">
         <v>0</v>
       </c>
       <c r="AR6" s="1">
-        <v>293</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>446</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>382</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1">
+        <v>380</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="W7" s="1">
+        <v>0</v>
+      </c>
+      <c r="X7" s="1">
+        <v>430</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="1">
-        <v>0</v>
-      </c>
-      <c r="D7" s="1">
-        <v>45</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>287</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M7" s="1">
-        <v>0</v>
-      </c>
-      <c r="N7" s="1">
-        <v>270</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1">
-        <v>66</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="V7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="W7" s="1">
-        <v>0</v>
-      </c>
-      <c r="X7" s="1">
-        <v>138</v>
-      </c>
-      <c r="Y7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z7" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="AA7" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="AB7" s="1">
         <v>0</v>
       </c>
       <c r="AC7" s="1">
-        <v>423</v>
+        <v>24</v>
       </c>
       <c r="AD7" s="1" t="s">
         <v>123</v>
@@ -1697,16 +1697,16 @@
         <v>123</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="AK7" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL7" s="1">
         <v>0</v>
       </c>
       <c r="AM7" s="1">
-        <v>539</v>
+        <v>341</v>
       </c>
       <c r="AN7" s="1" t="s">
         <v>123</v>
@@ -1726,186 +1726,186 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1">
+        <v>239</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>204</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>227</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+      <c r="S8" s="1">
+        <v>66</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="W8" s="1">
+        <v>0</v>
+      </c>
+      <c r="X8" s="1">
+        <v>352</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>423</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE8" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="1">
-        <v>0</v>
-      </c>
-      <c r="D8" s="1">
-        <v>550</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1">
-        <v>120</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M8" s="1">
-        <v>0</v>
-      </c>
-      <c r="N8" s="1">
-        <v>292</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="R8" s="1">
-        <v>0</v>
-      </c>
-      <c r="S8" s="1">
-        <v>446</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="W8" s="1">
-        <v>0</v>
-      </c>
-      <c r="X8" s="1">
-        <v>334</v>
-      </c>
-      <c r="Y8" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z8" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF8" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="AG8" s="1">
         <v>0</v>
       </c>
       <c r="AH8" s="1">
-        <v>348</v>
+        <v>451</v>
       </c>
       <c r="AI8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AJ8" s="1" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="AK8" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AL8" s="1">
         <v>0</v>
       </c>
       <c r="AM8" s="1">
-        <v>253</v>
+        <v>510</v>
       </c>
       <c r="AN8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="AP8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ8" s="1">
         <v>0</v>
       </c>
       <c r="AR8" s="1">
-        <v>452</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1">
         <v>0</v>
       </c>
       <c r="D9" s="1">
-        <v>237</v>
+        <v>16</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
       </c>
       <c r="I9" s="1">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>123</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="M9" s="1">
         <v>0</v>
       </c>
       <c r="N9" s="1">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>123</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="Q9" s="1" t="s">
         <v>15</v>
@@ -1914,13 +1914,13 @@
         <v>0</v>
       </c>
       <c r="S9" s="1">
-        <v>177</v>
+        <v>245</v>
       </c>
       <c r="T9" s="1" t="s">
         <v>123</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="V9" s="1" t="s">
         <v>15</v>
@@ -1929,162 +1929,162 @@
         <v>0</v>
       </c>
       <c r="X9" s="1">
-        <v>297</v>
+        <v>334</v>
       </c>
       <c r="Y9" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="AA9" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="AB9" s="1">
         <v>0</v>
       </c>
       <c r="AC9" s="1">
-        <v>209</v>
+        <v>170</v>
       </c>
       <c r="AD9" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="AF9" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="AG9" s="1">
         <v>0</v>
       </c>
       <c r="AH9" s="1">
-        <v>451</v>
+        <v>127</v>
       </c>
       <c r="AI9" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AJ9" s="1" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="AK9" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="AL9" s="1">
         <v>0</v>
       </c>
       <c r="AM9" s="1">
-        <v>166</v>
+        <v>530</v>
       </c>
       <c r="AN9" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO9" s="1" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="AP9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ9" s="1">
         <v>0</v>
       </c>
       <c r="AR9" s="1">
-        <v>358</v>
+        <v>432</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1">
         <v>0</v>
       </c>
       <c r="D10" s="1">
-        <v>497</v>
+        <v>388</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>37</v>
+        <v>110</v>
       </c>
       <c r="G10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>498</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
+        <v>376</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R10" s="1">
+        <v>0</v>
+      </c>
+      <c r="S10" s="1">
+        <v>177</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="V10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1">
-        <v>204</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="L10" s="1" t="s">
+      <c r="W10" s="1">
+        <v>0</v>
+      </c>
+      <c r="X10" s="1">
+        <v>455</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M10" s="1">
-        <v>0</v>
-      </c>
-      <c r="N10" s="1">
-        <v>227</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R10" s="1">
-        <v>0</v>
-      </c>
-      <c r="S10" s="1">
-        <v>187</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U10" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="V10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="W10" s="1">
-        <v>0</v>
-      </c>
-      <c r="X10" s="1">
-        <v>352</v>
-      </c>
-      <c r="Y10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z10" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA10" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="AB10" s="1">
         <v>0</v>
       </c>
       <c r="AC10" s="1">
-        <v>24</v>
+        <v>288</v>
       </c>
       <c r="AD10" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="AF10" s="1" t="s">
         <v>15</v>
@@ -2093,28 +2093,28 @@
         <v>0</v>
       </c>
       <c r="AH10" s="1">
-        <v>267</v>
+        <v>241</v>
       </c>
       <c r="AI10" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AJ10" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="AK10" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AL10" s="1">
         <v>0</v>
       </c>
       <c r="AM10" s="1">
-        <v>307</v>
+        <v>469</v>
       </c>
       <c r="AN10" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO10" s="1" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="AP10" s="1" t="s">
         <v>23</v>
@@ -2123,27 +2123,27 @@
         <v>0</v>
       </c>
       <c r="AR10" s="1">
-        <v>335</v>
+        <v>515</v>
       </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C11" s="1">
         <v>0</v>
       </c>
       <c r="D11" s="1">
-        <v>388</v>
+        <v>550</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>40</v>
@@ -2152,22 +2152,22 @@
         <v>0</v>
       </c>
       <c r="I11" s="1">
-        <v>446</v>
+        <v>515</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>123</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="M11" s="1">
         <v>0</v>
       </c>
       <c r="N11" s="1">
-        <v>392</v>
+        <v>517</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>123</v>
@@ -2188,37 +2188,37 @@
         <v>123</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="W11" s="1">
         <v>0</v>
       </c>
       <c r="X11" s="1">
-        <v>205</v>
+        <v>286</v>
       </c>
       <c r="Y11" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="AA11" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AB11" s="1">
         <v>0</v>
       </c>
       <c r="AC11" s="1">
-        <v>432</v>
+        <v>209</v>
       </c>
       <c r="AD11" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="AF11" s="1" t="s">
         <v>15</v>
@@ -2227,28 +2227,28 @@
         <v>0</v>
       </c>
       <c r="AH11" s="1">
-        <v>241</v>
+        <v>348</v>
       </c>
       <c r="AI11" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AJ11" s="1" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="AK11" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="AL11" s="1">
         <v>0</v>
       </c>
       <c r="AM11" s="1">
-        <v>123</v>
+        <v>539</v>
       </c>
       <c r="AN11" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO11" s="1" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="AP11" s="1" t="s">
         <v>54</v>
@@ -2257,42 +2257,42 @@
         <v>0</v>
       </c>
       <c r="AR11" s="1">
-        <v>323</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C12" s="1">
         <v>0</v>
       </c>
       <c r="D12" s="1">
-        <v>258</v>
+        <v>73</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H12" s="1">
         <v>0</v>
       </c>
       <c r="I12" s="1">
-        <v>515</v>
+        <v>287</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>123</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>54</v>
@@ -2301,43 +2301,43 @@
         <v>0</v>
       </c>
       <c r="N12" s="1">
-        <v>376</v>
+        <v>313</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>123</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R12" s="1">
         <v>0</v>
       </c>
       <c r="S12" s="1">
-        <v>245</v>
+        <v>137</v>
       </c>
       <c r="T12" s="1" t="s">
         <v>123</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="W12" s="1">
         <v>0</v>
       </c>
       <c r="X12" s="1">
-        <v>286</v>
+        <v>171</v>
       </c>
       <c r="Y12" s="1" t="s">
         <v>123</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="AA12" s="1" t="s">
         <v>21</v>
@@ -2346,66 +2346,66 @@
         <v>0</v>
       </c>
       <c r="AC12" s="1">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="AD12" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AE12" s="1" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="AF12" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AG12" s="1">
         <v>0</v>
       </c>
       <c r="AH12" s="1">
-        <v>346</v>
+        <v>267</v>
       </c>
       <c r="AI12" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AJ12" s="1" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="AK12" s="1" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="AL12" s="1">
         <v>0</v>
       </c>
       <c r="AM12" s="1">
-        <v>494</v>
+        <v>123</v>
       </c>
       <c r="AN12" s="1" t="s">
         <v>123</v>
       </c>
       <c r="AO12" s="1" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="AP12" s="1" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="AQ12" s="1">
         <v>0</v>
       </c>
       <c r="AR12" s="1">
-        <v>426</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C13" s="1">
         <v>0</v>
       </c>
       <c r="D13" s="1">
-        <v>16</v>
+        <v>258</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>123</v>
@@ -2426,106 +2426,106 @@
         <v>123</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="L13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>292</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R13" s="1">
+        <v>0</v>
+      </c>
+      <c r="S13" s="1">
+        <v>379</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="W13" s="1">
+        <v>0</v>
+      </c>
+      <c r="X13" s="1">
+        <v>297</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M13" s="1">
-        <v>0</v>
-      </c>
-      <c r="N13" s="1">
-        <v>517</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q13" s="1" t="s">
+      <c r="AB13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="1">
+        <v>109</v>
+      </c>
+      <c r="AD13" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="R13" s="1">
-        <v>0</v>
-      </c>
-      <c r="S13" s="1">
-        <v>380</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="V13" s="1" t="s">
+      <c r="AG13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="1">
+        <v>189</v>
+      </c>
+      <c r="AI13" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="W13" s="1">
-        <v>0</v>
-      </c>
-      <c r="X13" s="1">
-        <v>430</v>
-      </c>
-      <c r="Y13" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z13" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="AA13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="1">
-        <v>297</v>
-      </c>
-      <c r="AD13" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE13" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AF13" s="1" t="s">
+      <c r="AL13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="1">
+        <v>401</v>
+      </c>
+      <c r="AN13" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AP13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AG13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="1">
-        <v>127</v>
-      </c>
-      <c r="AI13" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ13" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AK13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AL13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM13" s="1">
-        <v>530</v>
-      </c>
-      <c r="AN13" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO13" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AP13" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="AQ13" s="1">
         <v>0</v>
       </c>
       <c r="AR13" s="1">
-        <v>515</v>
+        <v>452</v>
       </c>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.3">
@@ -2650,16 +2650,16 @@
         <v>123</v>
       </c>
       <c r="AO14" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="AP14" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="AQ14" s="1">
         <v>0</v>
       </c>
       <c r="AR14" s="1">
-        <v>268</v>
+        <v>358</v>
       </c>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.3">
@@ -2673,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="1">
-        <v>1991</v>
+        <v>2076</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>123</v>
@@ -2703,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="1">
-        <v>3304</v>
+        <v>3387</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>123</v>
@@ -2733,7 +2733,7 @@
         <v>0</v>
       </c>
       <c r="X15" s="1">
-        <v>2727</v>
+        <v>2747</v>
       </c>
       <c r="Y15" s="1" t="s">
         <v>123</v>
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="AC15" s="1">
-        <v>2603</v>
+        <v>2727</v>
       </c>
       <c r="AD15" s="1" t="s">
         <v>123</v>
@@ -2763,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="AH15" s="1">
-        <v>3235</v>
+        <v>3249</v>
       </c>
       <c r="AI15" s="1" t="s">
         <v>123</v>
@@ -2778,7 +2778,7 @@
         <v>0</v>
       </c>
       <c r="AM15" s="1">
-        <v>3379</v>
+        <v>3432</v>
       </c>
       <c r="AN15" s="1" t="s">
         <v>123</v>
@@ -2793,7 +2793,7 @@
         <v>0</v>
       </c>
       <c r="AR15" s="1">
-        <v>3710</v>
+        <v>4060</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -932,7 +932,7 @@
         <v>0</v>
       </c>
       <c r="AR4">
-        <v>293</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5">
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>270</v>
+        <v>356</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -1512,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>392</v>
+        <v>611</v>
       </c>
       <c r="O9" t="str">
         <v/>
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="T9" t="str">
         <v/>
@@ -1542,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="Y9" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>177</v>
+        <v>243</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -1706,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="AH10">
-        <v>241</v>
+        <v>305</v>
       </c>
       <c r="AI10" t="str">
         <v/>
@@ -1840,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="AH11">
-        <v>348</v>
+        <v>421</v>
       </c>
       <c r="AI11" t="str">
         <v/>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="S12">
-        <v>137</v>
+        <v>194</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -1944,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <v>171</v>
+        <v>219</v>
       </c>
       <c r="Y12" t="str">
         <v/>
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="AH12">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="AI12" t="str">
         <v/>
@@ -2316,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <v>3613</v>
+        <v>3918</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -2331,7 +2331,7 @@
         <v>0</v>
       </c>
       <c r="S15">
-        <v>2481</v>
+        <v>2606</v>
       </c>
       <c r="T15" t="str">
         <v/>
@@ -2346,7 +2346,7 @@
         <v>0</v>
       </c>
       <c r="X15">
-        <v>2855</v>
+        <v>2898</v>
       </c>
       <c r="Y15" t="str">
         <v/>
@@ -2376,7 +2376,7 @@
         <v>0</v>
       </c>
       <c r="AH15">
-        <v>3467</v>
+        <v>3619</v>
       </c>
       <c r="AI15" t="str">
         <v/>
@@ -2406,7 +2406,7 @@
         <v>0</v>
       </c>
       <c r="AR15">
-        <v>4078</v>
+        <v>4075</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -857,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="T4" t="str">
         <v/>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="T5" t="str">
         <v/>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI6" t="str">
         <v/>
@@ -1259,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>380</v>
+        <v>460</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -1304,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="AH7">
-        <v>553</v>
+        <v>567</v>
       </c>
       <c r="AI7" t="str">
         <v/>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="AR7">
-        <v>369</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8">
@@ -1468,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="AR8">
-        <v>323</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9">
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>530</v>
+        <v>548</v>
       </c>
       <c r="AN9" t="str">
         <v/>
@@ -1631,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>498</v>
+        <v>546</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>515</v>
+        <v>674</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>517</v>
+        <v>568</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>539</v>
+        <v>595</v>
       </c>
       <c r="AN11" t="str">
         <v/>
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>287</v>
+        <v>487</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -2063,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="S13">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="AC13">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AD13" t="str">
         <v/>
@@ -2272,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="AR14">
-        <v>358</v>
+        <v>410</v>
       </c>
     </row>
     <row r="15">
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>2560</v>
+        <v>2967</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -2316,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <v>3918</v>
+        <v>3969</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -2331,7 +2331,7 @@
         <v>0</v>
       </c>
       <c r="S15">
-        <v>2606</v>
+        <v>2800</v>
       </c>
       <c r="T15" t="str">
         <v/>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="AC15">
-        <v>2781</v>
+        <v>2785</v>
       </c>
       <c r="AD15" t="str">
         <v/>
@@ -2376,7 +2376,7 @@
         <v>0</v>
       </c>
       <c r="AH15">
-        <v>3619</v>
+        <v>3665</v>
       </c>
       <c r="AI15" t="str">
         <v/>
@@ -2391,7 +2391,7 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>3552</v>
+        <v>3626</v>
       </c>
       <c r="AN15" t="str">
         <v/>
@@ -2406,7 +2406,7 @@
         <v>0</v>
       </c>
       <c r="AR15">
-        <v>4075</v>
+        <v>4227</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AR15"/>
+  <dimension ref="A1:AR46"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -678,13 +678,13 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>552</v>
+        <v>708</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>Harshal Patel</v>
+        <v>Harshal Patel (Out)</v>
       </c>
       <c r="G3" t="str">
         <v>Sunrisers Hyderabad</v>
@@ -699,7 +699,7 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>Azmatullah Omarzai</v>
+        <v>Azmatullah Omarzai (Out)</v>
       </c>
       <c r="L3" t="str">
         <v>Punjab Kings</v>
@@ -723,7 +723,7 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>476</v>
+        <v>587</v>
       </c>
       <c r="T3" t="str">
         <v/>
@@ -738,7 +738,7 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="Y3" t="str">
         <v/>
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="AC3">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="AD3" t="str">
         <v/>
@@ -768,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="AH3">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="AI3" t="str">
         <v/>
@@ -783,13 +783,13 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>256</v>
+        <v>348</v>
       </c>
       <c r="AN3" t="str">
         <v/>
       </c>
       <c r="AO3" t="str">
-        <v>Navdeep Saini</v>
+        <v>Navdeep Saini (Out)</v>
       </c>
       <c r="AP3" t="str">
         <v>Kolkata Knight Riders</v>
@@ -812,13 +812,13 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>Mitchell Starc</v>
+        <v>Mitchell Starc (Out)</v>
       </c>
       <c r="G4" t="str">
         <v>Delhi Capitals</v>
@@ -833,7 +833,7 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>Matheesha Pathirana</v>
+        <v>Matheesha Pathirana (Out)</v>
       </c>
       <c r="L4" t="str">
         <v>Kolkata Knight Riders</v>
@@ -863,7 +863,7 @@
         <v/>
       </c>
       <c r="U4" t="str">
-        <v>Rachin Ravindra</v>
+        <v>Rachin Ravindra (Out)</v>
       </c>
       <c r="V4" t="str">
         <v>Kolkata Knight Riders</v>
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="AC4">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="AD4" t="str">
         <v/>
@@ -908,7 +908,7 @@
         <v/>
       </c>
       <c r="AJ4" t="str">
-        <v>MS Dhoni</v>
+        <v>MS Dhoni (Out)</v>
       </c>
       <c r="AK4" t="str">
         <v>Chennai Super Kings</v>
@@ -952,7 +952,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>Trent Boult</v>
+        <v>Trent Boult (Out)</v>
       </c>
       <c r="G5" t="str">
         <v>Mumbai Indians</v>
@@ -982,7 +982,7 @@
         <v/>
       </c>
       <c r="P5" t="str">
-        <v>Jitesh Sharma</v>
+        <v>Jitesh Sharma (Out)</v>
       </c>
       <c r="Q5" t="str">
         <v>Royal Challengers Bengaluru</v>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="AC5">
-        <v>332</v>
+        <v>366</v>
       </c>
       <c r="AD5" t="str">
         <v/>
@@ -1036,13 +1036,13 @@
         <v>0</v>
       </c>
       <c r="AH5">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="AI5" t="str">
         <v/>
       </c>
       <c r="AJ5" t="str">
-        <v>Prashant Veer</v>
+        <v>Prashant Veer (Out)</v>
       </c>
       <c r="AK5" t="str">
         <v>Chennai Super Kings</v>
@@ -1066,12 +1066,12 @@
         <v>0</v>
       </c>
       <c r="AR5">
-        <v>705</v>
+        <v>832</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Prithvi Shaw</v>
+        <v>Prithvi Shaw (Out)</v>
       </c>
       <c r="B6" t="str">
         <v>Delhi Capitals</v>
@@ -1095,7 +1095,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -1110,13 +1110,13 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>618</v>
+        <v>689</v>
       </c>
       <c r="O6" t="str">
         <v/>
       </c>
       <c r="P6" t="str">
-        <v>Finn Allen</v>
+        <v>Finn Allen (Out)</v>
       </c>
       <c r="Q6" t="str">
         <v>Kolkata Knight Riders</v>
@@ -1161,7 +1161,7 @@
         <v/>
       </c>
       <c r="AE6" t="str">
-        <v>Jacob Bethell</v>
+        <v>Jacob Bethell (Out)</v>
       </c>
       <c r="AF6" t="str">
         <v>Royal Challengers Bengaluru</v>
@@ -1191,21 +1191,21 @@
         <v/>
       </c>
       <c r="AO6" t="str">
-        <v>Harshit Rana</v>
+        <v>Krunal Pandya</v>
       </c>
       <c r="AP6" t="str">
-        <v>Kolkata Knight Riders</v>
+        <v>Royal Challengers Bengaluru</v>
       </c>
       <c r="AQ6">
         <v>0</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>424</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Ishant Sharma</v>
+        <v>Ishant Sharma (Out)</v>
       </c>
       <c r="B7" t="str">
         <v>Gujarat Titans</v>
@@ -1244,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>499</v>
+        <v>515</v>
       </c>
       <c r="O7" t="str">
         <v/>
@@ -1280,7 +1280,7 @@
         <v/>
       </c>
       <c r="Z7" t="str">
-        <v>Auqib Nabi</v>
+        <v>Auqib Nabi (Out)</v>
       </c>
       <c r="AA7" t="str">
         <v>Delhi Capitals</v>
@@ -1289,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="AC7">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AD7" t="str">
         <v/>
@@ -1319,22 +1319,22 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>341</v>
+        <v>383</v>
       </c>
       <c r="AN7" t="str">
         <v/>
       </c>
       <c r="AO7" t="str">
-        <v>Krunal Pandya</v>
+        <v>Washington Sundar</v>
       </c>
       <c r="AP7" t="str">
-        <v>Royal Challengers Bengaluru</v>
+        <v>Gujarat Titans</v>
       </c>
       <c r="AQ7">
         <v>0</v>
       </c>
       <c r="AR7">
-        <v>424</v>
+        <v>368</v>
       </c>
     </row>
     <row r="8">
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -1363,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -1378,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>227</v>
+        <v>272</v>
       </c>
       <c r="O8" t="str">
         <v/>
@@ -1414,7 +1414,7 @@
         <v/>
       </c>
       <c r="Z8" t="str">
-        <v>Ayush Mhatre</v>
+        <v>Ayush Mhatre (Out)</v>
       </c>
       <c r="AA8" t="str">
         <v>Chennai Super Kings</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="AH8">
-        <v>613</v>
+        <v>713</v>
       </c>
       <c r="AI8" t="str">
         <v/>
@@ -1453,27 +1453,27 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>510</v>
+        <v>632</v>
       </c>
       <c r="AN8" t="str">
         <v/>
       </c>
       <c r="AO8" t="str">
-        <v>Washington Sundar</v>
+        <v>KL Rahul</v>
       </c>
       <c r="AP8" t="str">
-        <v>Gujarat Titans</v>
+        <v>Delhi Capitals</v>
       </c>
       <c r="AQ8">
         <v>0</v>
       </c>
       <c r="AR8">
-        <v>368</v>
+        <v>730</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Rahul Chahar</v>
+        <v>Rahul Chahar (Out)</v>
       </c>
       <c r="B9" t="str">
         <v>Chennai Super Kings</v>
@@ -1488,7 +1488,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Venkatesh Iyer</v>
+        <v>Venkatesh Iyer (Out)</v>
       </c>
       <c r="G9" t="str">
         <v>Royal Challengers Bengaluru</v>
@@ -1548,7 +1548,7 @@
         <v/>
       </c>
       <c r="Z9" t="str">
-        <v>Khaleel Ahmed</v>
+        <v>Khaleel Ahmed (Out)</v>
       </c>
       <c r="AA9" t="str">
         <v>Chennai Super Kings</v>
@@ -1572,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="AH9">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="AI9" t="str">
         <v/>
@@ -1593,16 +1593,16 @@
         <v/>
       </c>
       <c r="AO9" t="str">
-        <v>KL Rahul</v>
+        <v>Prasidh Krishna</v>
       </c>
       <c r="AP9" t="str">
-        <v>Delhi Capitals</v>
+        <v>Gujarat Titans</v>
       </c>
       <c r="AQ9">
         <v>0</v>
       </c>
       <c r="AR9">
-        <v>432</v>
+        <v>515</v>
       </c>
     </row>
     <row r="10">
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>455</v>
+        <v>552</v>
       </c>
       <c r="Y10" t="str">
         <v/>
@@ -1691,7 +1691,7 @@
         <v>0</v>
       </c>
       <c r="AC10">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="AD10" t="str">
         <v/>
@@ -1721,22 +1721,22 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>517</v>
+        <v>539</v>
       </c>
       <c r="AN10" t="str">
         <v/>
       </c>
       <c r="AO10" t="str">
-        <v>Prasidh Krishna</v>
+        <v>Avesh Khan</v>
       </c>
       <c r="AP10" t="str">
-        <v>Gujarat Titans</v>
+        <v>Lucknow Super Giants</v>
       </c>
       <c r="AQ10">
         <v>0</v>
       </c>
       <c r="AR10">
-        <v>515</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
@@ -1750,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>568</v>
+        <v>791</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -1786,7 +1786,7 @@
         <v/>
       </c>
       <c r="P11" t="str">
-        <v>Nehal Wadhera</v>
+        <v>Nehal Wadhera (Out)</v>
       </c>
       <c r="Q11" t="str">
         <v>Punjab Kings</v>
@@ -1795,7 +1795,7 @@
         <v>0</v>
       </c>
       <c r="S11">
-        <v>94</v>
+        <v>149</v>
       </c>
       <c r="T11" t="str">
         <v/>
@@ -1825,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="AC11">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="AD11" t="str">
         <v/>
@@ -1861,7 +1861,7 @@
         <v/>
       </c>
       <c r="AO11" t="str">
-        <v>Avesh Khan</v>
+        <v>Rishabh Pant</v>
       </c>
       <c r="AP11" t="str">
         <v>Lucknow Super Giants</v>
@@ -1870,12 +1870,12 @@
         <v>0</v>
       </c>
       <c r="AR11">
-        <v>268</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Ashutosh Sharma</v>
+        <v>Ashutosh Sharma (Out)</v>
       </c>
       <c r="B12" t="str">
         <v>Delhi Capitals</v>
@@ -1959,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="AC12">
-        <v>432</v>
+        <v>585</v>
       </c>
       <c r="AD12" t="str">
         <v/>
@@ -1995,16 +1995,16 @@
         <v/>
       </c>
       <c r="AO12" t="str">
-        <v>Rishabh Pant</v>
+        <v>Prabhsimran Singh</v>
       </c>
       <c r="AP12" t="str">
-        <v>Lucknow Super Giants</v>
+        <v>Punjab Kings</v>
       </c>
       <c r="AQ12">
         <v>0</v>
       </c>
       <c r="AR12">
-        <v>341</v>
+        <v>626</v>
       </c>
     </row>
     <row r="13">
@@ -2084,7 +2084,7 @@
         <v/>
       </c>
       <c r="Z13" t="str">
-        <v>Rahul Tewatia</v>
+        <v>Rahul Tewatia (Out)</v>
       </c>
       <c r="AA13" t="str">
         <v>Gujarat Titans</v>
@@ -2099,7 +2099,7 @@
         <v/>
       </c>
       <c r="AE13" t="str">
-        <v>Glenn Phillips</v>
+        <v>Glenn Phillips (Out)</v>
       </c>
       <c r="AF13" t="str">
         <v>Gujarat Titans</v>
@@ -2129,16 +2129,16 @@
         <v/>
       </c>
       <c r="AO13" t="str">
-        <v>Prabhsimran Singh</v>
+        <v/>
       </c>
       <c r="AP13" t="str">
-        <v>Punjab Kings</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
-      <c r="AR13">
-        <v>452</v>
+        <v/>
+      </c>
+      <c r="AQ13" t="str">
+        <v/>
+      </c>
+      <c r="AR13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -2188,16 +2188,16 @@
         <v/>
       </c>
       <c r="P14" t="str">
-        <v/>
+        <v>Cooper Connolly (New)</v>
       </c>
       <c r="Q14" t="str">
-        <v/>
+        <v>Punjab Kings</v>
       </c>
       <c r="R14" t="str">
         <v/>
       </c>
-      <c r="S14" t="str">
-        <v/>
+      <c r="S14">
+        <v>0</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -2263,155 +2263,4309 @@
         <v/>
       </c>
       <c r="AO14" t="str">
-        <v>Mohammed Siraj</v>
+        <v/>
       </c>
       <c r="AP14" t="str">
-        <v>Gujarat Titans</v>
-      </c>
-      <c r="AQ14">
-        <v>0</v>
-      </c>
-      <c r="AR14">
-        <v>410</v>
+        <v/>
+      </c>
+      <c r="AQ14" t="str">
+        <v/>
+      </c>
+      <c r="AR14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
+        <v/>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v>Jamie Overton (New)</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Chennai Super Kings</v>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str">
+        <v/>
+      </c>
+      <c r="T15" t="str">
+        <v/>
+      </c>
+      <c r="U15" t="str">
+        <v/>
+      </c>
+      <c r="V15" t="str">
+        <v/>
+      </c>
+      <c r="W15" t="str">
+        <v/>
+      </c>
+      <c r="X15" t="str">
+        <v/>
+      </c>
+      <c r="Y15" t="str">
+        <v/>
+      </c>
+      <c r="Z15" t="str">
+        <v/>
+      </c>
+      <c r="AA15" t="str">
+        <v/>
+      </c>
+      <c r="AB15" t="str">
+        <v/>
+      </c>
+      <c r="AC15" t="str">
+        <v/>
+      </c>
+      <c r="AD15" t="str">
+        <v/>
+      </c>
+      <c r="AE15" t="str">
+        <v/>
+      </c>
+      <c r="AF15" t="str">
+        <v/>
+      </c>
+      <c r="AG15" t="str">
+        <v/>
+      </c>
+      <c r="AH15" t="str">
+        <v/>
+      </c>
+      <c r="AI15" t="str">
+        <v/>
+      </c>
+      <c r="AJ15" t="str">
+        <v/>
+      </c>
+      <c r="AK15" t="str">
+        <v/>
+      </c>
+      <c r="AL15" t="str">
+        <v/>
+      </c>
+      <c r="AM15" t="str">
+        <v/>
+      </c>
+      <c r="AN15" t="str">
+        <v/>
+      </c>
+      <c r="AO15" t="str">
+        <v>Xavier Bartlett (New)</v>
+      </c>
+      <c r="AP15" t="str">
+        <v>Punjab Kings</v>
+      </c>
+      <c r="AQ15" t="str">
+        <v/>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v/>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
+        <v/>
+      </c>
+      <c r="S16" t="str">
+        <v/>
+      </c>
+      <c r="T16" t="str">
+        <v/>
+      </c>
+      <c r="U16" t="str">
+        <v/>
+      </c>
+      <c r="V16" t="str">
+        <v/>
+      </c>
+      <c r="W16" t="str">
+        <v/>
+      </c>
+      <c r="X16" t="str">
+        <v/>
+      </c>
+      <c r="Y16" t="str">
+        <v/>
+      </c>
+      <c r="Z16" t="str">
+        <v/>
+      </c>
+      <c r="AA16" t="str">
+        <v/>
+      </c>
+      <c r="AB16" t="str">
+        <v/>
+      </c>
+      <c r="AC16" t="str">
+        <v/>
+      </c>
+      <c r="AD16" t="str">
+        <v/>
+      </c>
+      <c r="AE16" t="str">
+        <v/>
+      </c>
+      <c r="AF16" t="str">
+        <v/>
+      </c>
+      <c r="AG16" t="str">
+        <v/>
+      </c>
+      <c r="AH16" t="str">
+        <v/>
+      </c>
+      <c r="AI16" t="str">
+        <v/>
+      </c>
+      <c r="AJ16" t="str">
+        <v/>
+      </c>
+      <c r="AK16" t="str">
+        <v/>
+      </c>
+      <c r="AL16" t="str">
+        <v/>
+      </c>
+      <c r="AM16" t="str">
+        <v/>
+      </c>
+      <c r="AN16" t="str">
+        <v/>
+      </c>
+      <c r="AO16" t="str">
+        <v/>
+      </c>
+      <c r="AP16" t="str">
+        <v/>
+      </c>
+      <c r="AQ16" t="str">
+        <v/>
+      </c>
+      <c r="AR16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v/>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v/>
+      </c>
+      <c r="S17" t="str">
+        <v/>
+      </c>
+      <c r="T17" t="str">
+        <v/>
+      </c>
+      <c r="U17" t="str">
+        <v>Sarfaraz Khan (New)</v>
+      </c>
+      <c r="V17" t="str">
+        <v>Chennai Super Kings</v>
+      </c>
+      <c r="W17" t="str">
+        <v/>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="str">
+        <v/>
+      </c>
+      <c r="Z17" t="str">
+        <v/>
+      </c>
+      <c r="AA17" t="str">
+        <v/>
+      </c>
+      <c r="AB17" t="str">
+        <v/>
+      </c>
+      <c r="AC17" t="str">
+        <v/>
+      </c>
+      <c r="AD17" t="str">
+        <v/>
+      </c>
+      <c r="AE17" t="str">
+        <v/>
+      </c>
+      <c r="AF17" t="str">
+        <v/>
+      </c>
+      <c r="AG17" t="str">
+        <v/>
+      </c>
+      <c r="AH17" t="str">
+        <v/>
+      </c>
+      <c r="AI17" t="str">
+        <v/>
+      </c>
+      <c r="AJ17" t="str">
+        <v/>
+      </c>
+      <c r="AK17" t="str">
+        <v/>
+      </c>
+      <c r="AL17" t="str">
+        <v/>
+      </c>
+      <c r="AM17" t="str">
+        <v/>
+      </c>
+      <c r="AN17" t="str">
+        <v/>
+      </c>
+      <c r="AO17" t="str">
+        <v/>
+      </c>
+      <c r="AP17" t="str">
+        <v/>
+      </c>
+      <c r="AQ17" t="str">
+        <v/>
+      </c>
+      <c r="AR17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v/>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
+        <v/>
+      </c>
+      <c r="S18" t="str">
+        <v/>
+      </c>
+      <c r="T18" t="str">
+        <v/>
+      </c>
+      <c r="U18" t="str">
+        <v/>
+      </c>
+      <c r="V18" t="str">
+        <v/>
+      </c>
+      <c r="W18" t="str">
+        <v/>
+      </c>
+      <c r="X18" t="str">
+        <v/>
+      </c>
+      <c r="Y18" t="str">
+        <v/>
+      </c>
+      <c r="Z18" t="str">
+        <v/>
+      </c>
+      <c r="AA18" t="str">
+        <v/>
+      </c>
+      <c r="AB18" t="str">
+        <v/>
+      </c>
+      <c r="AC18" t="str">
+        <v/>
+      </c>
+      <c r="AD18" t="str">
+        <v/>
+      </c>
+      <c r="AE18" t="str">
+        <v>AM Ghazanfar (New)</v>
+      </c>
+      <c r="AF18" t="str">
+        <v>Mumbai Indians</v>
+      </c>
+      <c r="AG18" t="str">
+        <v/>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="str">
+        <v/>
+      </c>
+      <c r="AJ18" t="str">
+        <v/>
+      </c>
+      <c r="AK18" t="str">
+        <v/>
+      </c>
+      <c r="AL18" t="str">
+        <v/>
+      </c>
+      <c r="AM18" t="str">
+        <v/>
+      </c>
+      <c r="AN18" t="str">
+        <v/>
+      </c>
+      <c r="AO18" t="str">
+        <v/>
+      </c>
+      <c r="AP18" t="str">
+        <v/>
+      </c>
+      <c r="AQ18" t="str">
+        <v/>
+      </c>
+      <c r="AR18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v/>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v>Anshul Kamboj (New)</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Chennai Super Kings</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
+        <v/>
+      </c>
+      <c r="S19" t="str">
+        <v/>
+      </c>
+      <c r="T19" t="str">
+        <v/>
+      </c>
+      <c r="U19" t="str">
+        <v/>
+      </c>
+      <c r="V19" t="str">
+        <v/>
+      </c>
+      <c r="W19" t="str">
+        <v/>
+      </c>
+      <c r="X19" t="str">
+        <v/>
+      </c>
+      <c r="Y19" t="str">
+        <v/>
+      </c>
+      <c r="Z19" t="str">
+        <v/>
+      </c>
+      <c r="AA19" t="str">
+        <v/>
+      </c>
+      <c r="AB19" t="str">
+        <v/>
+      </c>
+      <c r="AC19" t="str">
+        <v/>
+      </c>
+      <c r="AD19" t="str">
+        <v/>
+      </c>
+      <c r="AE19" t="str">
+        <v/>
+      </c>
+      <c r="AF19" t="str">
+        <v/>
+      </c>
+      <c r="AG19" t="str">
+        <v/>
+      </c>
+      <c r="AH19" t="str">
+        <v/>
+      </c>
+      <c r="AI19" t="str">
+        <v/>
+      </c>
+      <c r="AJ19" t="str">
+        <v/>
+      </c>
+      <c r="AK19" t="str">
+        <v/>
+      </c>
+      <c r="AL19" t="str">
+        <v/>
+      </c>
+      <c r="AM19" t="str">
+        <v/>
+      </c>
+      <c r="AN19" t="str">
+        <v/>
+      </c>
+      <c r="AO19" t="str">
+        <v/>
+      </c>
+      <c r="AP19" t="str">
+        <v/>
+      </c>
+      <c r="AQ19" t="str">
+        <v/>
+      </c>
+      <c r="AR19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v/>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v>Naman Dhir (New)</v>
+      </c>
+      <c r="Q20" t="str">
+        <v>Mumbai Indians</v>
+      </c>
+      <c r="R20" t="str">
+        <v/>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20" t="str">
+        <v/>
+      </c>
+      <c r="U20" t="str">
+        <v/>
+      </c>
+      <c r="V20" t="str">
+        <v/>
+      </c>
+      <c r="W20" t="str">
+        <v/>
+      </c>
+      <c r="X20" t="str">
+        <v/>
+      </c>
+      <c r="Y20" t="str">
+        <v/>
+      </c>
+      <c r="Z20" t="str">
+        <v/>
+      </c>
+      <c r="AA20" t="str">
+        <v/>
+      </c>
+      <c r="AB20" t="str">
+        <v/>
+      </c>
+      <c r="AC20" t="str">
+        <v/>
+      </c>
+      <c r="AD20" t="str">
+        <v/>
+      </c>
+      <c r="AE20" t="str">
+        <v/>
+      </c>
+      <c r="AF20" t="str">
+        <v/>
+      </c>
+      <c r="AG20" t="str">
+        <v/>
+      </c>
+      <c r="AH20" t="str">
+        <v/>
+      </c>
+      <c r="AI20" t="str">
+        <v/>
+      </c>
+      <c r="AJ20" t="str">
+        <v/>
+      </c>
+      <c r="AK20" t="str">
+        <v/>
+      </c>
+      <c r="AL20" t="str">
+        <v/>
+      </c>
+      <c r="AM20" t="str">
+        <v/>
+      </c>
+      <c r="AN20" t="str">
+        <v/>
+      </c>
+      <c r="AO20" t="str">
+        <v/>
+      </c>
+      <c r="AP20" t="str">
+        <v/>
+      </c>
+      <c r="AQ20" t="str">
+        <v/>
+      </c>
+      <c r="AR20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v/>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
+        <v/>
+      </c>
+      <c r="S21" t="str">
+        <v/>
+      </c>
+      <c r="T21" t="str">
+        <v/>
+      </c>
+      <c r="U21" t="str">
+        <v/>
+      </c>
+      <c r="V21" t="str">
+        <v/>
+      </c>
+      <c r="W21" t="str">
+        <v/>
+      </c>
+      <c r="X21" t="str">
+        <v/>
+      </c>
+      <c r="Y21" t="str">
+        <v/>
+      </c>
+      <c r="Z21" t="str">
+        <v>Mukesh Kumar (New)</v>
+      </c>
+      <c r="AA21" t="str">
+        <v>Delhi Capitals</v>
+      </c>
+      <c r="AB21" t="str">
+        <v/>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="str">
+        <v/>
+      </c>
+      <c r="AE21" t="str">
+        <v/>
+      </c>
+      <c r="AF21" t="str">
+        <v/>
+      </c>
+      <c r="AG21" t="str">
+        <v/>
+      </c>
+      <c r="AH21" t="str">
+        <v/>
+      </c>
+      <c r="AI21" t="str">
+        <v/>
+      </c>
+      <c r="AJ21" t="str">
+        <v/>
+      </c>
+      <c r="AK21" t="str">
+        <v/>
+      </c>
+      <c r="AL21" t="str">
+        <v/>
+      </c>
+      <c r="AM21" t="str">
+        <v/>
+      </c>
+      <c r="AN21" t="str">
+        <v/>
+      </c>
+      <c r="AO21" t="str">
+        <v/>
+      </c>
+      <c r="AP21" t="str">
+        <v/>
+      </c>
+      <c r="AQ21" t="str">
+        <v/>
+      </c>
+      <c r="AR21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Devdutt Padikkal (New)</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Royal Challengers Bengaluru</v>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <v/>
+      </c>
+      <c r="R22" t="str">
+        <v/>
+      </c>
+      <c r="S22" t="str">
+        <v/>
+      </c>
+      <c r="T22" t="str">
+        <v/>
+      </c>
+      <c r="U22" t="str">
+        <v/>
+      </c>
+      <c r="V22" t="str">
+        <v/>
+      </c>
+      <c r="W22" t="str">
+        <v/>
+      </c>
+      <c r="X22" t="str">
+        <v/>
+      </c>
+      <c r="Y22" t="str">
+        <v/>
+      </c>
+      <c r="Z22" t="str">
+        <v/>
+      </c>
+      <c r="AA22" t="str">
+        <v/>
+      </c>
+      <c r="AB22" t="str">
+        <v/>
+      </c>
+      <c r="AC22" t="str">
+        <v/>
+      </c>
+      <c r="AD22" t="str">
+        <v/>
+      </c>
+      <c r="AE22" t="str">
+        <v/>
+      </c>
+      <c r="AF22" t="str">
+        <v/>
+      </c>
+      <c r="AG22" t="str">
+        <v/>
+      </c>
+      <c r="AH22" t="str">
+        <v/>
+      </c>
+      <c r="AI22" t="str">
+        <v/>
+      </c>
+      <c r="AJ22" t="str">
+        <v/>
+      </c>
+      <c r="AK22" t="str">
+        <v/>
+      </c>
+      <c r="AL22" t="str">
+        <v/>
+      </c>
+      <c r="AM22" t="str">
+        <v/>
+      </c>
+      <c r="AN22" t="str">
+        <v/>
+      </c>
+      <c r="AO22" t="str">
+        <v/>
+      </c>
+      <c r="AP22" t="str">
+        <v/>
+      </c>
+      <c r="AQ22" t="str">
+        <v/>
+      </c>
+      <c r="AR22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v/>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <v/>
+      </c>
+      <c r="R23" t="str">
+        <v/>
+      </c>
+      <c r="S23" t="str">
+        <v/>
+      </c>
+      <c r="T23" t="str">
+        <v/>
+      </c>
+      <c r="U23" t="str">
+        <v/>
+      </c>
+      <c r="V23" t="str">
+        <v/>
+      </c>
+      <c r="W23" t="str">
+        <v/>
+      </c>
+      <c r="X23" t="str">
+        <v/>
+      </c>
+      <c r="Y23" t="str">
+        <v/>
+      </c>
+      <c r="Z23" t="str">
+        <v>Sameer Rizvi (New)</v>
+      </c>
+      <c r="AA23" t="str">
+        <v>Delhi Capitals</v>
+      </c>
+      <c r="AB23" t="str">
+        <v/>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="str">
+        <v/>
+      </c>
+      <c r="AE23" t="str">
+        <v/>
+      </c>
+      <c r="AF23" t="str">
+        <v/>
+      </c>
+      <c r="AG23" t="str">
+        <v/>
+      </c>
+      <c r="AH23" t="str">
+        <v/>
+      </c>
+      <c r="AI23" t="str">
+        <v/>
+      </c>
+      <c r="AJ23" t="str">
+        <v/>
+      </c>
+      <c r="AK23" t="str">
+        <v/>
+      </c>
+      <c r="AL23" t="str">
+        <v/>
+      </c>
+      <c r="AM23" t="str">
+        <v/>
+      </c>
+      <c r="AN23" t="str">
+        <v/>
+      </c>
+      <c r="AO23" t="str">
+        <v/>
+      </c>
+      <c r="AP23" t="str">
+        <v/>
+      </c>
+      <c r="AQ23" t="str">
+        <v/>
+      </c>
+      <c r="AR23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v/>
+      </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <v/>
+      </c>
+      <c r="R24" t="str">
+        <v/>
+      </c>
+      <c r="S24" t="str">
+        <v/>
+      </c>
+      <c r="T24" t="str">
+        <v/>
+      </c>
+      <c r="U24" t="str">
+        <v/>
+      </c>
+      <c r="V24" t="str">
+        <v/>
+      </c>
+      <c r="W24" t="str">
+        <v/>
+      </c>
+      <c r="X24" t="str">
+        <v/>
+      </c>
+      <c r="Y24" t="str">
+        <v/>
+      </c>
+      <c r="Z24" t="str">
+        <v>Romario Shepherd (New)</v>
+      </c>
+      <c r="AA24" t="str">
+        <v>Royal Challengers Bengaluru</v>
+      </c>
+      <c r="AB24" t="str">
+        <v/>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="str">
+        <v/>
+      </c>
+      <c r="AE24" t="str">
+        <v/>
+      </c>
+      <c r="AF24" t="str">
+        <v/>
+      </c>
+      <c r="AG24" t="str">
+        <v/>
+      </c>
+      <c r="AH24" t="str">
+        <v/>
+      </c>
+      <c r="AI24" t="str">
+        <v/>
+      </c>
+      <c r="AJ24" t="str">
+        <v/>
+      </c>
+      <c r="AK24" t="str">
+        <v/>
+      </c>
+      <c r="AL24" t="str">
+        <v/>
+      </c>
+      <c r="AM24" t="str">
+        <v/>
+      </c>
+      <c r="AN24" t="str">
+        <v/>
+      </c>
+      <c r="AO24" t="str">
+        <v/>
+      </c>
+      <c r="AP24" t="str">
+        <v/>
+      </c>
+      <c r="AQ24" t="str">
+        <v/>
+      </c>
+      <c r="AR24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v/>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+      <c r="Q25" t="str">
+        <v/>
+      </c>
+      <c r="R25" t="str">
+        <v/>
+      </c>
+      <c r="S25" t="str">
+        <v/>
+      </c>
+      <c r="T25" t="str">
+        <v/>
+      </c>
+      <c r="U25" t="str">
+        <v/>
+      </c>
+      <c r="V25" t="str">
+        <v/>
+      </c>
+      <c r="W25" t="str">
+        <v/>
+      </c>
+      <c r="X25" t="str">
+        <v/>
+      </c>
+      <c r="Y25" t="str">
+        <v/>
+      </c>
+      <c r="Z25" t="str">
+        <v>Harsh Dubey (New)</v>
+      </c>
+      <c r="AA25" t="str">
+        <v>Sunrisers Hyderabad</v>
+      </c>
+      <c r="AB25" t="str">
+        <v/>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="str">
+        <v/>
+      </c>
+      <c r="AE25" t="str">
+        <v/>
+      </c>
+      <c r="AF25" t="str">
+        <v/>
+      </c>
+      <c r="AG25" t="str">
+        <v/>
+      </c>
+      <c r="AH25" t="str">
+        <v/>
+      </c>
+      <c r="AI25" t="str">
+        <v/>
+      </c>
+      <c r="AJ25" t="str">
+        <v/>
+      </c>
+      <c r="AK25" t="str">
+        <v/>
+      </c>
+      <c r="AL25" t="str">
+        <v/>
+      </c>
+      <c r="AM25" t="str">
+        <v/>
+      </c>
+      <c r="AN25" t="str">
+        <v/>
+      </c>
+      <c r="AO25" t="str">
+        <v/>
+      </c>
+      <c r="AP25" t="str">
+        <v/>
+      </c>
+      <c r="AQ25" t="str">
+        <v/>
+      </c>
+      <c r="AR25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v/>
+      </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>Rasikh Dar Salam (New)</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Royal Challengers Bengaluru</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
+        <v/>
+      </c>
+      <c r="R26" t="str">
+        <v/>
+      </c>
+      <c r="S26" t="str">
+        <v/>
+      </c>
+      <c r="T26" t="str">
+        <v/>
+      </c>
+      <c r="U26" t="str">
+        <v/>
+      </c>
+      <c r="V26" t="str">
+        <v/>
+      </c>
+      <c r="W26" t="str">
+        <v/>
+      </c>
+      <c r="X26" t="str">
+        <v/>
+      </c>
+      <c r="Y26" t="str">
+        <v/>
+      </c>
+      <c r="Z26" t="str">
+        <v/>
+      </c>
+      <c r="AA26" t="str">
+        <v/>
+      </c>
+      <c r="AB26" t="str">
+        <v/>
+      </c>
+      <c r="AC26" t="str">
+        <v/>
+      </c>
+      <c r="AD26" t="str">
+        <v/>
+      </c>
+      <c r="AE26" t="str">
+        <v/>
+      </c>
+      <c r="AF26" t="str">
+        <v/>
+      </c>
+      <c r="AG26" t="str">
+        <v/>
+      </c>
+      <c r="AH26" t="str">
+        <v/>
+      </c>
+      <c r="AI26" t="str">
+        <v/>
+      </c>
+      <c r="AJ26" t="str">
+        <v/>
+      </c>
+      <c r="AK26" t="str">
+        <v/>
+      </c>
+      <c r="AL26" t="str">
+        <v/>
+      </c>
+      <c r="AM26" t="str">
+        <v/>
+      </c>
+      <c r="AN26" t="str">
+        <v/>
+      </c>
+      <c r="AO26" t="str">
+        <v/>
+      </c>
+      <c r="AP26" t="str">
+        <v/>
+      </c>
+      <c r="AQ26" t="str">
+        <v/>
+      </c>
+      <c r="AR26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v/>
+      </c>
+      <c r="B27" t="str">
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
+        <v/>
+      </c>
+      <c r="R27" t="str">
+        <v/>
+      </c>
+      <c r="S27" t="str">
+        <v/>
+      </c>
+      <c r="T27" t="str">
+        <v/>
+      </c>
+      <c r="U27" t="str">
+        <v/>
+      </c>
+      <c r="V27" t="str">
+        <v/>
+      </c>
+      <c r="W27" t="str">
+        <v/>
+      </c>
+      <c r="X27" t="str">
+        <v/>
+      </c>
+      <c r="Y27" t="str">
+        <v/>
+      </c>
+      <c r="Z27" t="str">
+        <v>Kartik Tyagi (New)</v>
+      </c>
+      <c r="AA27" t="str">
+        <v>Kolkata Knight Riders</v>
+      </c>
+      <c r="AB27" t="str">
+        <v/>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="str">
+        <v/>
+      </c>
+      <c r="AE27" t="str">
+        <v/>
+      </c>
+      <c r="AF27" t="str">
+        <v/>
+      </c>
+      <c r="AG27" t="str">
+        <v/>
+      </c>
+      <c r="AH27" t="str">
+        <v/>
+      </c>
+      <c r="AI27" t="str">
+        <v/>
+      </c>
+      <c r="AJ27" t="str">
+        <v/>
+      </c>
+      <c r="AK27" t="str">
+        <v/>
+      </c>
+      <c r="AL27" t="str">
+        <v/>
+      </c>
+      <c r="AM27" t="str">
+        <v/>
+      </c>
+      <c r="AN27" t="str">
+        <v/>
+      </c>
+      <c r="AO27" t="str">
+        <v/>
+      </c>
+      <c r="AP27" t="str">
+        <v/>
+      </c>
+      <c r="AQ27" t="str">
+        <v/>
+      </c>
+      <c r="AR27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v/>
+      </c>
+      <c r="B28" t="str">
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v>Eshan Malinga (New)</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Sunrisers Hyderabad</v>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28">
+        <v>86</v>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
+        <v/>
+      </c>
+      <c r="R28" t="str">
+        <v/>
+      </c>
+      <c r="S28" t="str">
+        <v/>
+      </c>
+      <c r="T28" t="str">
+        <v/>
+      </c>
+      <c r="U28" t="str">
+        <v/>
+      </c>
+      <c r="V28" t="str">
+        <v/>
+      </c>
+      <c r="W28" t="str">
+        <v/>
+      </c>
+      <c r="X28" t="str">
+        <v/>
+      </c>
+      <c r="Y28" t="str">
+        <v/>
+      </c>
+      <c r="Z28" t="str">
+        <v/>
+      </c>
+      <c r="AA28" t="str">
+        <v/>
+      </c>
+      <c r="AB28" t="str">
+        <v/>
+      </c>
+      <c r="AC28" t="str">
+        <v/>
+      </c>
+      <c r="AD28" t="str">
+        <v/>
+      </c>
+      <c r="AE28" t="str">
+        <v/>
+      </c>
+      <c r="AF28" t="str">
+        <v/>
+      </c>
+      <c r="AG28" t="str">
+        <v/>
+      </c>
+      <c r="AH28" t="str">
+        <v/>
+      </c>
+      <c r="AI28" t="str">
+        <v/>
+      </c>
+      <c r="AJ28" t="str">
+        <v/>
+      </c>
+      <c r="AK28" t="str">
+        <v/>
+      </c>
+      <c r="AL28" t="str">
+        <v/>
+      </c>
+      <c r="AM28" t="str">
+        <v/>
+      </c>
+      <c r="AN28" t="str">
+        <v/>
+      </c>
+      <c r="AO28" t="str">
+        <v/>
+      </c>
+      <c r="AP28" t="str">
+        <v/>
+      </c>
+      <c r="AQ28" t="str">
+        <v/>
+      </c>
+      <c r="AR28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v/>
+      </c>
+      <c r="B29" t="str">
+        <v/>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>Prince Yadav (New)</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Lucknow Super Giants</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+      <c r="Q29" t="str">
+        <v/>
+      </c>
+      <c r="R29" t="str">
+        <v/>
+      </c>
+      <c r="S29" t="str">
+        <v/>
+      </c>
+      <c r="T29" t="str">
+        <v/>
+      </c>
+      <c r="U29" t="str">
+        <v/>
+      </c>
+      <c r="V29" t="str">
+        <v/>
+      </c>
+      <c r="W29" t="str">
+        <v/>
+      </c>
+      <c r="X29" t="str">
+        <v/>
+      </c>
+      <c r="Y29" t="str">
+        <v/>
+      </c>
+      <c r="Z29" t="str">
+        <v/>
+      </c>
+      <c r="AA29" t="str">
+        <v/>
+      </c>
+      <c r="AB29" t="str">
+        <v/>
+      </c>
+      <c r="AC29" t="str">
+        <v/>
+      </c>
+      <c r="AD29" t="str">
+        <v/>
+      </c>
+      <c r="AE29" t="str">
+        <v/>
+      </c>
+      <c r="AF29" t="str">
+        <v/>
+      </c>
+      <c r="AG29" t="str">
+        <v/>
+      </c>
+      <c r="AH29" t="str">
+        <v/>
+      </c>
+      <c r="AI29" t="str">
+        <v/>
+      </c>
+      <c r="AJ29" t="str">
+        <v/>
+      </c>
+      <c r="AK29" t="str">
+        <v/>
+      </c>
+      <c r="AL29" t="str">
+        <v/>
+      </c>
+      <c r="AM29" t="str">
+        <v/>
+      </c>
+      <c r="AN29" t="str">
+        <v/>
+      </c>
+      <c r="AO29" t="str">
+        <v/>
+      </c>
+      <c r="AP29" t="str">
+        <v/>
+      </c>
+      <c r="AQ29" t="str">
+        <v/>
+      </c>
+      <c r="AR29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Pathum Nissanka (New)</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Delhi Capitals</v>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+      <c r="Q30" t="str">
+        <v/>
+      </c>
+      <c r="R30" t="str">
+        <v/>
+      </c>
+      <c r="S30" t="str">
+        <v/>
+      </c>
+      <c r="T30" t="str">
+        <v/>
+      </c>
+      <c r="U30" t="str">
+        <v/>
+      </c>
+      <c r="V30" t="str">
+        <v/>
+      </c>
+      <c r="W30" t="str">
+        <v/>
+      </c>
+      <c r="X30" t="str">
+        <v/>
+      </c>
+      <c r="Y30" t="str">
+        <v/>
+      </c>
+      <c r="Z30" t="str">
+        <v/>
+      </c>
+      <c r="AA30" t="str">
+        <v/>
+      </c>
+      <c r="AB30" t="str">
+        <v/>
+      </c>
+      <c r="AC30" t="str">
+        <v/>
+      </c>
+      <c r="AD30" t="str">
+        <v/>
+      </c>
+      <c r="AE30" t="str">
+        <v/>
+      </c>
+      <c r="AF30" t="str">
+        <v/>
+      </c>
+      <c r="AG30" t="str">
+        <v/>
+      </c>
+      <c r="AH30" t="str">
+        <v/>
+      </c>
+      <c r="AI30" t="str">
+        <v/>
+      </c>
+      <c r="AJ30" t="str">
+        <v/>
+      </c>
+      <c r="AK30" t="str">
+        <v/>
+      </c>
+      <c r="AL30" t="str">
+        <v/>
+      </c>
+      <c r="AM30" t="str">
+        <v/>
+      </c>
+      <c r="AN30" t="str">
+        <v/>
+      </c>
+      <c r="AO30" t="str">
+        <v/>
+      </c>
+      <c r="AP30" t="str">
+        <v/>
+      </c>
+      <c r="AQ30" t="str">
+        <v/>
+      </c>
+      <c r="AR30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Suyash Sharma (New)</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Royal Challengers Bengaluru</v>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+      <c r="Q31" t="str">
+        <v/>
+      </c>
+      <c r="R31" t="str">
+        <v/>
+      </c>
+      <c r="S31" t="str">
+        <v/>
+      </c>
+      <c r="T31" t="str">
+        <v/>
+      </c>
+      <c r="U31" t="str">
+        <v/>
+      </c>
+      <c r="V31" t="str">
+        <v/>
+      </c>
+      <c r="W31" t="str">
+        <v/>
+      </c>
+      <c r="X31" t="str">
+        <v/>
+      </c>
+      <c r="Y31" t="str">
+        <v/>
+      </c>
+      <c r="Z31" t="str">
+        <v/>
+      </c>
+      <c r="AA31" t="str">
+        <v/>
+      </c>
+      <c r="AB31" t="str">
+        <v/>
+      </c>
+      <c r="AC31" t="str">
+        <v/>
+      </c>
+      <c r="AD31" t="str">
+        <v/>
+      </c>
+      <c r="AE31" t="str">
+        <v/>
+      </c>
+      <c r="AF31" t="str">
+        <v/>
+      </c>
+      <c r="AG31" t="str">
+        <v/>
+      </c>
+      <c r="AH31" t="str">
+        <v/>
+      </c>
+      <c r="AI31" t="str">
+        <v/>
+      </c>
+      <c r="AJ31" t="str">
+        <v/>
+      </c>
+      <c r="AK31" t="str">
+        <v/>
+      </c>
+      <c r="AL31" t="str">
+        <v/>
+      </c>
+      <c r="AM31" t="str">
+        <v/>
+      </c>
+      <c r="AN31" t="str">
+        <v/>
+      </c>
+      <c r="AO31" t="str">
+        <v/>
+      </c>
+      <c r="AP31" t="str">
+        <v/>
+      </c>
+      <c r="AQ31" t="str">
+        <v/>
+      </c>
+      <c r="AR31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v/>
+      </c>
+      <c r="B32" t="str">
+        <v/>
+      </c>
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <v/>
+      </c>
+      <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <v/>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+      <c r="Q32" t="str">
+        <v/>
+      </c>
+      <c r="R32" t="str">
+        <v/>
+      </c>
+      <c r="S32" t="str">
+        <v/>
+      </c>
+      <c r="T32" t="str">
+        <v/>
+      </c>
+      <c r="U32" t="str">
+        <v/>
+      </c>
+      <c r="V32" t="str">
+        <v/>
+      </c>
+      <c r="W32" t="str">
+        <v/>
+      </c>
+      <c r="X32" t="str">
+        <v/>
+      </c>
+      <c r="Y32" t="str">
+        <v/>
+      </c>
+      <c r="Z32" t="str">
+        <v/>
+      </c>
+      <c r="AA32" t="str">
+        <v/>
+      </c>
+      <c r="AB32" t="str">
+        <v/>
+      </c>
+      <c r="AC32" t="str">
+        <v/>
+      </c>
+      <c r="AD32" t="str">
+        <v/>
+      </c>
+      <c r="AE32" t="str">
+        <v/>
+      </c>
+      <c r="AF32" t="str">
+        <v/>
+      </c>
+      <c r="AG32" t="str">
+        <v/>
+      </c>
+      <c r="AH32" t="str">
+        <v/>
+      </c>
+      <c r="AI32" t="str">
+        <v/>
+      </c>
+      <c r="AJ32" t="str">
+        <v>Akeal Hosein (New)</v>
+      </c>
+      <c r="AK32" t="str">
+        <v>Chennai Super Kings</v>
+      </c>
+      <c r="AL32" t="str">
+        <v/>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="str">
+        <v/>
+      </c>
+      <c r="AO32" t="str">
+        <v/>
+      </c>
+      <c r="AP32" t="str">
+        <v/>
+      </c>
+      <c r="AQ32" t="str">
+        <v/>
+      </c>
+      <c r="AR32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v/>
+      </c>
+      <c r="B33" t="str">
+        <v/>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+      <c r="Q33" t="str">
+        <v/>
+      </c>
+      <c r="R33" t="str">
+        <v/>
+      </c>
+      <c r="S33" t="str">
+        <v/>
+      </c>
+      <c r="T33" t="str">
+        <v/>
+      </c>
+      <c r="U33" t="str">
+        <v/>
+      </c>
+      <c r="V33" t="str">
+        <v/>
+      </c>
+      <c r="W33" t="str">
+        <v/>
+      </c>
+      <c r="X33" t="str">
+        <v/>
+      </c>
+      <c r="Y33" t="str">
+        <v/>
+      </c>
+      <c r="Z33" t="str">
+        <v/>
+      </c>
+      <c r="AA33" t="str">
+        <v/>
+      </c>
+      <c r="AB33" t="str">
+        <v/>
+      </c>
+      <c r="AC33" t="str">
+        <v/>
+      </c>
+      <c r="AD33" t="str">
+        <v/>
+      </c>
+      <c r="AE33" t="str">
+        <v/>
+      </c>
+      <c r="AF33" t="str">
+        <v/>
+      </c>
+      <c r="AG33" t="str">
+        <v/>
+      </c>
+      <c r="AH33" t="str">
+        <v/>
+      </c>
+      <c r="AI33" t="str">
+        <v/>
+      </c>
+      <c r="AJ33" t="str">
+        <v>Sakib Hussain (New)</v>
+      </c>
+      <c r="AK33" t="str">
+        <v>Sunrisers Hyderabad</v>
+      </c>
+      <c r="AL33" t="str">
+        <v/>
+      </c>
+      <c r="AM33">
+        <v>48</v>
+      </c>
+      <c r="AN33" t="str">
+        <v/>
+      </c>
+      <c r="AO33" t="str">
+        <v/>
+      </c>
+      <c r="AP33" t="str">
+        <v/>
+      </c>
+      <c r="AQ33" t="str">
+        <v/>
+      </c>
+      <c r="AR33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v/>
+      </c>
+      <c r="B34" t="str">
+        <v/>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v/>
+      </c>
+      <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+      <c r="Q34" t="str">
+        <v/>
+      </c>
+      <c r="R34" t="str">
+        <v/>
+      </c>
+      <c r="S34" t="str">
+        <v/>
+      </c>
+      <c r="T34" t="str">
+        <v/>
+      </c>
+      <c r="U34" t="str">
+        <v/>
+      </c>
+      <c r="V34" t="str">
+        <v/>
+      </c>
+      <c r="W34" t="str">
+        <v/>
+      </c>
+      <c r="X34" t="str">
+        <v/>
+      </c>
+      <c r="Y34" t="str">
+        <v/>
+      </c>
+      <c r="Z34" t="str">
+        <v/>
+      </c>
+      <c r="AA34" t="str">
+        <v/>
+      </c>
+      <c r="AB34" t="str">
+        <v/>
+      </c>
+      <c r="AC34" t="str">
+        <v/>
+      </c>
+      <c r="AD34" t="str">
+        <v/>
+      </c>
+      <c r="AE34" t="str">
+        <v>Jason Holder (New)</v>
+      </c>
+      <c r="AF34" t="str">
+        <v>Gujarat Titans</v>
+      </c>
+      <c r="AG34" t="str">
+        <v/>
+      </c>
+      <c r="AH34">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="str">
+        <v/>
+      </c>
+      <c r="AJ34" t="str">
+        <v/>
+      </c>
+      <c r="AK34" t="str">
+        <v/>
+      </c>
+      <c r="AL34" t="str">
+        <v/>
+      </c>
+      <c r="AM34" t="str">
+        <v/>
+      </c>
+      <c r="AN34" t="str">
+        <v/>
+      </c>
+      <c r="AO34" t="str">
+        <v/>
+      </c>
+      <c r="AP34" t="str">
+        <v/>
+      </c>
+      <c r="AQ34" t="str">
+        <v/>
+      </c>
+      <c r="AR34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v/>
+      </c>
+      <c r="B35" t="str">
+        <v/>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v/>
+      </c>
+      <c r="L35" t="str">
+        <v/>
+      </c>
+      <c r="M35" t="str">
+        <v/>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
+      <c r="P35" t="str">
+        <v>Nitish Rana (New)</v>
+      </c>
+      <c r="Q35" t="str">
+        <v>Delhi Capitals</v>
+      </c>
+      <c r="R35" t="str">
+        <v/>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35" t="str">
+        <v/>
+      </c>
+      <c r="U35" t="str">
+        <v/>
+      </c>
+      <c r="V35" t="str">
+        <v/>
+      </c>
+      <c r="W35" t="str">
+        <v/>
+      </c>
+      <c r="X35" t="str">
+        <v/>
+      </c>
+      <c r="Y35" t="str">
+        <v/>
+      </c>
+      <c r="Z35" t="str">
+        <v/>
+      </c>
+      <c r="AA35" t="str">
+        <v/>
+      </c>
+      <c r="AB35" t="str">
+        <v/>
+      </c>
+      <c r="AC35" t="str">
+        <v/>
+      </c>
+      <c r="AD35" t="str">
+        <v/>
+      </c>
+      <c r="AE35" t="str">
+        <v/>
+      </c>
+      <c r="AF35" t="str">
+        <v/>
+      </c>
+      <c r="AG35" t="str">
+        <v/>
+      </c>
+      <c r="AH35" t="str">
+        <v/>
+      </c>
+      <c r="AI35" t="str">
+        <v/>
+      </c>
+      <c r="AJ35" t="str">
+        <v/>
+      </c>
+      <c r="AK35" t="str">
+        <v/>
+      </c>
+      <c r="AL35" t="str">
+        <v/>
+      </c>
+      <c r="AM35" t="str">
+        <v/>
+      </c>
+      <c r="AN35" t="str">
+        <v/>
+      </c>
+      <c r="AO35" t="str">
+        <v/>
+      </c>
+      <c r="AP35" t="str">
+        <v/>
+      </c>
+      <c r="AQ35" t="str">
+        <v/>
+      </c>
+      <c r="AR35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v/>
+      </c>
+      <c r="B36" t="str">
+        <v/>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v>Nandre Burger (New)</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Rajasthan Royals</v>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36">
+        <v>16</v>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v/>
+      </c>
+      <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+      <c r="Q36" t="str">
+        <v/>
+      </c>
+      <c r="R36" t="str">
+        <v/>
+      </c>
+      <c r="S36" t="str">
+        <v/>
+      </c>
+      <c r="T36" t="str">
+        <v/>
+      </c>
+      <c r="U36" t="str">
+        <v/>
+      </c>
+      <c r="V36" t="str">
+        <v/>
+      </c>
+      <c r="W36" t="str">
+        <v/>
+      </c>
+      <c r="X36" t="str">
+        <v/>
+      </c>
+      <c r="Y36" t="str">
+        <v/>
+      </c>
+      <c r="Z36" t="str">
+        <v/>
+      </c>
+      <c r="AA36" t="str">
+        <v/>
+      </c>
+      <c r="AB36" t="str">
+        <v/>
+      </c>
+      <c r="AC36" t="str">
+        <v/>
+      </c>
+      <c r="AD36" t="str">
+        <v/>
+      </c>
+      <c r="AE36" t="str">
+        <v/>
+      </c>
+      <c r="AF36" t="str">
+        <v/>
+      </c>
+      <c r="AG36" t="str">
+        <v/>
+      </c>
+      <c r="AH36" t="str">
+        <v/>
+      </c>
+      <c r="AI36" t="str">
+        <v/>
+      </c>
+      <c r="AJ36" t="str">
+        <v/>
+      </c>
+      <c r="AK36" t="str">
+        <v/>
+      </c>
+      <c r="AL36" t="str">
+        <v/>
+      </c>
+      <c r="AM36" t="str">
+        <v/>
+      </c>
+      <c r="AN36" t="str">
+        <v/>
+      </c>
+      <c r="AO36" t="str">
+        <v/>
+      </c>
+      <c r="AP36" t="str">
+        <v/>
+      </c>
+      <c r="AQ36" t="str">
+        <v/>
+      </c>
+      <c r="AR36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Rovman Powell (New)</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Kolkata Knight Riders</v>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
+      <c r="L37" t="str">
+        <v/>
+      </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+      <c r="Q37" t="str">
+        <v/>
+      </c>
+      <c r="R37" t="str">
+        <v/>
+      </c>
+      <c r="S37" t="str">
+        <v/>
+      </c>
+      <c r="T37" t="str">
+        <v/>
+      </c>
+      <c r="U37" t="str">
+        <v/>
+      </c>
+      <c r="V37" t="str">
+        <v/>
+      </c>
+      <c r="W37" t="str">
+        <v/>
+      </c>
+      <c r="X37" t="str">
+        <v/>
+      </c>
+      <c r="Y37" t="str">
+        <v/>
+      </c>
+      <c r="Z37" t="str">
+        <v/>
+      </c>
+      <c r="AA37" t="str">
+        <v/>
+      </c>
+      <c r="AB37" t="str">
+        <v/>
+      </c>
+      <c r="AC37" t="str">
+        <v/>
+      </c>
+      <c r="AD37" t="str">
+        <v/>
+      </c>
+      <c r="AE37" t="str">
+        <v/>
+      </c>
+      <c r="AF37" t="str">
+        <v/>
+      </c>
+      <c r="AG37" t="str">
+        <v/>
+      </c>
+      <c r="AH37" t="str">
+        <v/>
+      </c>
+      <c r="AI37" t="str">
+        <v/>
+      </c>
+      <c r="AJ37" t="str">
+        <v/>
+      </c>
+      <c r="AK37" t="str">
+        <v/>
+      </c>
+      <c r="AL37" t="str">
+        <v/>
+      </c>
+      <c r="AM37" t="str">
+        <v/>
+      </c>
+      <c r="AN37" t="str">
+        <v/>
+      </c>
+      <c r="AO37" t="str">
+        <v/>
+      </c>
+      <c r="AP37" t="str">
+        <v/>
+      </c>
+      <c r="AQ37" t="str">
+        <v/>
+      </c>
+      <c r="AR37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v/>
+      </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
+      <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
+      <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+      <c r="P38" t="str">
+        <v>MST Costs</v>
+      </c>
+      <c r="Q38" t="str">
+        <v/>
+      </c>
+      <c r="R38" t="str">
+        <v/>
+      </c>
+      <c r="S38">
+        <v>-500</v>
+      </c>
+      <c r="T38" t="str">
+        <v/>
+      </c>
+      <c r="U38" t="str">
+        <v/>
+      </c>
+      <c r="V38" t="str">
+        <v/>
+      </c>
+      <c r="W38" t="str">
+        <v/>
+      </c>
+      <c r="X38" t="str">
+        <v/>
+      </c>
+      <c r="Y38" t="str">
+        <v/>
+      </c>
+      <c r="Z38" t="str">
+        <v/>
+      </c>
+      <c r="AA38" t="str">
+        <v/>
+      </c>
+      <c r="AB38" t="str">
+        <v/>
+      </c>
+      <c r="AC38" t="str">
+        <v/>
+      </c>
+      <c r="AD38" t="str">
+        <v/>
+      </c>
+      <c r="AE38" t="str">
+        <v/>
+      </c>
+      <c r="AF38" t="str">
+        <v/>
+      </c>
+      <c r="AG38" t="str">
+        <v/>
+      </c>
+      <c r="AH38" t="str">
+        <v/>
+      </c>
+      <c r="AI38" t="str">
+        <v/>
+      </c>
+      <c r="AJ38" t="str">
+        <v/>
+      </c>
+      <c r="AK38" t="str">
+        <v/>
+      </c>
+      <c r="AL38" t="str">
+        <v/>
+      </c>
+      <c r="AM38" t="str">
+        <v/>
+      </c>
+      <c r="AN38" t="str">
+        <v/>
+      </c>
+      <c r="AO38" t="str">
+        <v>Mohammed Siraj</v>
+      </c>
+      <c r="AP38" t="str">
+        <v>RCB</v>
+      </c>
+      <c r="AQ38" t="str">
+        <v/>
+      </c>
+      <c r="AR38">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v/>
+      </c>
+      <c r="B39" t="str">
+        <v/>
+      </c>
+      <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
+        <v/>
+      </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+      <c r="Q39" t="str">
+        <v/>
+      </c>
+      <c r="R39" t="str">
+        <v/>
+      </c>
+      <c r="S39" t="str">
+        <v/>
+      </c>
+      <c r="T39" t="str">
+        <v/>
+      </c>
+      <c r="U39" t="str">
+        <v/>
+      </c>
+      <c r="V39" t="str">
+        <v/>
+      </c>
+      <c r="W39" t="str">
+        <v/>
+      </c>
+      <c r="X39" t="str">
+        <v/>
+      </c>
+      <c r="Y39" t="str">
+        <v/>
+      </c>
+      <c r="Z39" t="str">
+        <v/>
+      </c>
+      <c r="AA39" t="str">
+        <v/>
+      </c>
+      <c r="AB39" t="str">
+        <v/>
+      </c>
+      <c r="AC39" t="str">
+        <v/>
+      </c>
+      <c r="AD39" t="str">
+        <v/>
+      </c>
+      <c r="AE39" t="str">
+        <v/>
+      </c>
+      <c r="AF39" t="str">
+        <v/>
+      </c>
+      <c r="AG39" t="str">
+        <v/>
+      </c>
+      <c r="AH39" t="str">
+        <v/>
+      </c>
+      <c r="AI39" t="str">
+        <v/>
+      </c>
+      <c r="AJ39" t="str">
+        <v/>
+      </c>
+      <c r="AK39" t="str">
+        <v/>
+      </c>
+      <c r="AL39" t="str">
+        <v/>
+      </c>
+      <c r="AM39" t="str">
+        <v/>
+      </c>
+      <c r="AN39" t="str">
+        <v/>
+      </c>
+      <c r="AO39" t="str">
+        <v>MST Costs</v>
+      </c>
+      <c r="AP39" t="str">
+        <v/>
+      </c>
+      <c r="AQ39" t="str">
+        <v/>
+      </c>
+      <c r="AR39">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v/>
+      </c>
+      <c r="B40" t="str">
+        <v/>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v/>
+      </c>
+      <c r="L40" t="str">
+        <v/>
+      </c>
+      <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+      <c r="Q40" t="str">
+        <v/>
+      </c>
+      <c r="R40" t="str">
+        <v/>
+      </c>
+      <c r="S40" t="str">
+        <v/>
+      </c>
+      <c r="T40" t="str">
+        <v/>
+      </c>
+      <c r="U40" t="str">
+        <v/>
+      </c>
+      <c r="V40" t="str">
+        <v/>
+      </c>
+      <c r="W40" t="str">
+        <v/>
+      </c>
+      <c r="X40" t="str">
+        <v/>
+      </c>
+      <c r="Y40" t="str">
+        <v/>
+      </c>
+      <c r="Z40" t="str">
+        <v/>
+      </c>
+      <c r="AA40" t="str">
+        <v/>
+      </c>
+      <c r="AB40" t="str">
+        <v/>
+      </c>
+      <c r="AC40" t="str">
+        <v/>
+      </c>
+      <c r="AD40" t="str">
+        <v/>
+      </c>
+      <c r="AE40" t="str">
+        <v>MST Costs</v>
+      </c>
+      <c r="AF40" t="str">
+        <v/>
+      </c>
+      <c r="AG40" t="str">
+        <v/>
+      </c>
+      <c r="AH40">
+        <v>-200</v>
+      </c>
+      <c r="AI40" t="str">
+        <v/>
+      </c>
+      <c r="AJ40" t="str">
+        <v/>
+      </c>
+      <c r="AK40" t="str">
+        <v/>
+      </c>
+      <c r="AL40" t="str">
+        <v/>
+      </c>
+      <c r="AM40" t="str">
+        <v/>
+      </c>
+      <c r="AN40" t="str">
+        <v/>
+      </c>
+      <c r="AO40" t="str">
+        <v/>
+      </c>
+      <c r="AP40" t="str">
+        <v/>
+      </c>
+      <c r="AQ40" t="str">
+        <v/>
+      </c>
+      <c r="AR40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v/>
+      </c>
+      <c r="B41" t="str">
+        <v/>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v>MST Costs</v>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41">
+        <v>-400</v>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <v/>
+      </c>
+      <c r="L41" t="str">
+        <v/>
+      </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+      <c r="Q41" t="str">
+        <v/>
+      </c>
+      <c r="R41" t="str">
+        <v/>
+      </c>
+      <c r="S41" t="str">
+        <v/>
+      </c>
+      <c r="T41" t="str">
+        <v/>
+      </c>
+      <c r="U41" t="str">
+        <v/>
+      </c>
+      <c r="V41" t="str">
+        <v/>
+      </c>
+      <c r="W41" t="str">
+        <v/>
+      </c>
+      <c r="X41" t="str">
+        <v/>
+      </c>
+      <c r="Y41" t="str">
+        <v/>
+      </c>
+      <c r="Z41" t="str">
+        <v/>
+      </c>
+      <c r="AA41" t="str">
+        <v/>
+      </c>
+      <c r="AB41" t="str">
+        <v/>
+      </c>
+      <c r="AC41" t="str">
+        <v/>
+      </c>
+      <c r="AD41" t="str">
+        <v/>
+      </c>
+      <c r="AE41" t="str">
+        <v/>
+      </c>
+      <c r="AF41" t="str">
+        <v/>
+      </c>
+      <c r="AG41" t="str">
+        <v/>
+      </c>
+      <c r="AH41" t="str">
+        <v/>
+      </c>
+      <c r="AI41" t="str">
+        <v/>
+      </c>
+      <c r="AJ41" t="str">
+        <v/>
+      </c>
+      <c r="AK41" t="str">
+        <v/>
+      </c>
+      <c r="AL41" t="str">
+        <v/>
+      </c>
+      <c r="AM41" t="str">
+        <v/>
+      </c>
+      <c r="AN41" t="str">
+        <v/>
+      </c>
+      <c r="AO41" t="str">
+        <v/>
+      </c>
+      <c r="AP41" t="str">
+        <v/>
+      </c>
+      <c r="AQ41" t="str">
+        <v/>
+      </c>
+      <c r="AR41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v/>
+      </c>
+      <c r="B42" t="str">
+        <v/>
+      </c>
+      <c r="C42" t="str">
+        <v/>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v/>
+      </c>
+      <c r="L42" t="str">
+        <v/>
+      </c>
+      <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+      <c r="Q42" t="str">
+        <v/>
+      </c>
+      <c r="R42" t="str">
+        <v/>
+      </c>
+      <c r="S42" t="str">
+        <v/>
+      </c>
+      <c r="T42" t="str">
+        <v/>
+      </c>
+      <c r="U42" t="str">
+        <v/>
+      </c>
+      <c r="V42" t="str">
+        <v/>
+      </c>
+      <c r="W42" t="str">
+        <v/>
+      </c>
+      <c r="X42" t="str">
+        <v/>
+      </c>
+      <c r="Y42" t="str">
+        <v/>
+      </c>
+      <c r="Z42" t="str">
+        <v>MST Costs</v>
+      </c>
+      <c r="AA42" t="str">
+        <v/>
+      </c>
+      <c r="AB42" t="str">
+        <v/>
+      </c>
+      <c r="AC42">
+        <v>-300</v>
+      </c>
+      <c r="AD42" t="str">
+        <v/>
+      </c>
+      <c r="AE42" t="str">
+        <v/>
+      </c>
+      <c r="AF42" t="str">
+        <v/>
+      </c>
+      <c r="AG42" t="str">
+        <v/>
+      </c>
+      <c r="AH42" t="str">
+        <v/>
+      </c>
+      <c r="AI42" t="str">
+        <v/>
+      </c>
+      <c r="AJ42" t="str">
+        <v/>
+      </c>
+      <c r="AK42" t="str">
+        <v/>
+      </c>
+      <c r="AL42" t="str">
+        <v/>
+      </c>
+      <c r="AM42" t="str">
+        <v/>
+      </c>
+      <c r="AN42" t="str">
+        <v/>
+      </c>
+      <c r="AO42" t="str">
+        <v/>
+      </c>
+      <c r="AP42" t="str">
+        <v/>
+      </c>
+      <c r="AQ42" t="str">
+        <v/>
+      </c>
+      <c r="AR42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v/>
+      </c>
+      <c r="B43" t="str">
+        <v/>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
+        <v/>
+      </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
+      <c r="Q43" t="str">
+        <v/>
+      </c>
+      <c r="R43" t="str">
+        <v/>
+      </c>
+      <c r="S43" t="str">
+        <v/>
+      </c>
+      <c r="T43" t="str">
+        <v/>
+      </c>
+      <c r="U43" t="str">
+        <v/>
+      </c>
+      <c r="V43" t="str">
+        <v/>
+      </c>
+      <c r="W43" t="str">
+        <v/>
+      </c>
+      <c r="X43" t="str">
+        <v/>
+      </c>
+      <c r="Y43" t="str">
+        <v/>
+      </c>
+      <c r="Z43" t="str">
+        <v/>
+      </c>
+      <c r="AA43" t="str">
+        <v/>
+      </c>
+      <c r="AB43" t="str">
+        <v/>
+      </c>
+      <c r="AC43" t="str">
+        <v/>
+      </c>
+      <c r="AD43" t="str">
+        <v/>
+      </c>
+      <c r="AE43" t="str">
+        <v/>
+      </c>
+      <c r="AF43" t="str">
+        <v/>
+      </c>
+      <c r="AG43" t="str">
+        <v/>
+      </c>
+      <c r="AH43" t="str">
+        <v/>
+      </c>
+      <c r="AI43" t="str">
+        <v/>
+      </c>
+      <c r="AJ43" t="str">
+        <v>MST Costs</v>
+      </c>
+      <c r="AK43" t="str">
+        <v/>
+      </c>
+      <c r="AL43" t="str">
+        <v/>
+      </c>
+      <c r="AM43">
+        <v>-100</v>
+      </c>
+      <c r="AN43" t="str">
+        <v/>
+      </c>
+      <c r="AO43" t="str">
+        <v/>
+      </c>
+      <c r="AP43" t="str">
+        <v/>
+      </c>
+      <c r="AQ43" t="str">
+        <v/>
+      </c>
+      <c r="AR43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>MST Costs</v>
+      </c>
+      <c r="B44" t="str">
+        <v/>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44">
+        <v>-200</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
+      <c r="L44" t="str">
+        <v/>
+      </c>
+      <c r="M44" t="str">
+        <v/>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
+      <c r="Q44" t="str">
+        <v/>
+      </c>
+      <c r="R44" t="str">
+        <v/>
+      </c>
+      <c r="S44" t="str">
+        <v/>
+      </c>
+      <c r="T44" t="str">
+        <v/>
+      </c>
+      <c r="U44" t="str">
+        <v/>
+      </c>
+      <c r="V44" t="str">
+        <v/>
+      </c>
+      <c r="W44" t="str">
+        <v/>
+      </c>
+      <c r="X44" t="str">
+        <v/>
+      </c>
+      <c r="Y44" t="str">
+        <v/>
+      </c>
+      <c r="Z44" t="str">
+        <v/>
+      </c>
+      <c r="AA44" t="str">
+        <v/>
+      </c>
+      <c r="AB44" t="str">
+        <v/>
+      </c>
+      <c r="AC44" t="str">
+        <v/>
+      </c>
+      <c r="AD44" t="str">
+        <v/>
+      </c>
+      <c r="AE44" t="str">
+        <v/>
+      </c>
+      <c r="AF44" t="str">
+        <v/>
+      </c>
+      <c r="AG44" t="str">
+        <v/>
+      </c>
+      <c r="AH44" t="str">
+        <v/>
+      </c>
+      <c r="AI44" t="str">
+        <v/>
+      </c>
+      <c r="AJ44" t="str">
+        <v/>
+      </c>
+      <c r="AK44" t="str">
+        <v/>
+      </c>
+      <c r="AL44" t="str">
+        <v/>
+      </c>
+      <c r="AM44" t="str">
+        <v/>
+      </c>
+      <c r="AN44" t="str">
+        <v/>
+      </c>
+      <c r="AO44" t="str">
+        <v/>
+      </c>
+      <c r="AP44" t="str">
+        <v/>
+      </c>
+      <c r="AQ44" t="str">
+        <v/>
+      </c>
+      <c r="AR44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
         <v>TOTAL</v>
       </c>
-      <c r="B15" t="str">
-        <v/>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>2094</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
+      <c r="B45" t="str">
+        <v/>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>2350</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
         <v>TOTAL</v>
       </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>2967</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>2610</v>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
         <v>TOTAL</v>
       </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>3969</v>
-      </c>
-      <c r="O15" t="str">
-        <v/>
-      </c>
-      <c r="P15" t="str">
+      <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>4187</v>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+      <c r="P45" t="str">
         <v>TOTAL</v>
       </c>
-      <c r="Q15" t="str">
-        <v/>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>2800</v>
-      </c>
-      <c r="T15" t="str">
-        <v/>
-      </c>
-      <c r="U15" t="str">
+      <c r="Q45" t="str">
+        <v/>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>2466</v>
+      </c>
+      <c r="T45" t="str">
+        <v/>
+      </c>
+      <c r="U45" t="str">
         <v>TOTAL</v>
       </c>
-      <c r="V15" t="str">
-        <v/>
-      </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>2898</v>
-      </c>
-      <c r="Y15" t="str">
-        <v/>
-      </c>
-      <c r="Z15" t="str">
+      <c r="V45" t="str">
+        <v/>
+      </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
+      <c r="X45">
+        <v>3003</v>
+      </c>
+      <c r="Y45" t="str">
+        <v/>
+      </c>
+      <c r="Z45" t="str">
         <v>TOTAL</v>
       </c>
-      <c r="AA15" t="str">
-        <v/>
-      </c>
-      <c r="AB15">
-        <v>0</v>
-      </c>
-      <c r="AC15">
-        <v>2785</v>
-      </c>
-      <c r="AD15" t="str">
-        <v/>
-      </c>
-      <c r="AE15" t="str">
+      <c r="AA45" t="str">
+        <v/>
+      </c>
+      <c r="AB45">
+        <v>0</v>
+      </c>
+      <c r="AC45">
+        <v>2723</v>
+      </c>
+      <c r="AD45" t="str">
+        <v/>
+      </c>
+      <c r="AE45" t="str">
         <v>TOTAL</v>
       </c>
-      <c r="AF15" t="str">
-        <v/>
-      </c>
-      <c r="AG15">
-        <v>0</v>
-      </c>
-      <c r="AH15">
-        <v>3665</v>
-      </c>
-      <c r="AI15" t="str">
-        <v/>
-      </c>
-      <c r="AJ15" t="str">
+      <c r="AF45" t="str">
+        <v/>
+      </c>
+      <c r="AG45">
+        <v>0</v>
+      </c>
+      <c r="AH45">
+        <v>3591</v>
+      </c>
+      <c r="AI45" t="str">
+        <v/>
+      </c>
+      <c r="AJ45" t="str">
         <v>TOTAL</v>
       </c>
-      <c r="AK15" t="str">
-        <v/>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>3626</v>
-      </c>
-      <c r="AN15" t="str">
-        <v/>
-      </c>
-      <c r="AO15" t="str">
+      <c r="AK45" t="str">
+        <v/>
+      </c>
+      <c r="AL45">
+        <v>0</v>
+      </c>
+      <c r="AM45">
+        <v>3852</v>
+      </c>
+      <c r="AN45" t="str">
+        <v/>
+      </c>
+      <c r="AO45" t="str">
+        <v/>
+      </c>
+      <c r="AP45" t="str">
+        <v/>
+      </c>
+      <c r="AQ45" t="str">
+        <v/>
+      </c>
+      <c r="AR45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v/>
+      </c>
+      <c r="B46" t="str">
+        <v/>
+      </c>
+      <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <v/>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+      <c r="P46" t="str">
+        <v/>
+      </c>
+      <c r="Q46" t="str">
+        <v/>
+      </c>
+      <c r="R46" t="str">
+        <v/>
+      </c>
+      <c r="S46" t="str">
+        <v/>
+      </c>
+      <c r="T46" t="str">
+        <v/>
+      </c>
+      <c r="U46" t="str">
+        <v/>
+      </c>
+      <c r="V46" t="str">
+        <v/>
+      </c>
+      <c r="W46" t="str">
+        <v/>
+      </c>
+      <c r="X46" t="str">
+        <v/>
+      </c>
+      <c r="Y46" t="str">
+        <v/>
+      </c>
+      <c r="Z46" t="str">
+        <v/>
+      </c>
+      <c r="AA46" t="str">
+        <v/>
+      </c>
+      <c r="AB46" t="str">
+        <v/>
+      </c>
+      <c r="AC46" t="str">
+        <v/>
+      </c>
+      <c r="AD46" t="str">
+        <v/>
+      </c>
+      <c r="AE46" t="str">
+        <v/>
+      </c>
+      <c r="AF46" t="str">
+        <v/>
+      </c>
+      <c r="AG46" t="str">
+        <v/>
+      </c>
+      <c r="AH46" t="str">
+        <v/>
+      </c>
+      <c r="AI46" t="str">
+        <v/>
+      </c>
+      <c r="AJ46" t="str">
+        <v/>
+      </c>
+      <c r="AK46" t="str">
+        <v/>
+      </c>
+      <c r="AL46" t="str">
+        <v/>
+      </c>
+      <c r="AM46" t="str">
+        <v/>
+      </c>
+      <c r="AN46" t="str">
+        <v/>
+      </c>
+      <c r="AO46" t="str">
         <v>TOTAL</v>
       </c>
-      <c r="AP15" t="str">
-        <v/>
-      </c>
-      <c r="AQ15">
-        <v>0</v>
-      </c>
-      <c r="AR15">
-        <v>4227</v>
+      <c r="AP46" t="str">
+        <v/>
+      </c>
+      <c r="AQ46">
+        <v>0</v>
+      </c>
+      <c r="AR46">
+        <v>4816</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AR15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AR46"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -1146,7 +1146,7 @@
         <v/>
       </c>
       <c r="Z6" t="str">
-        <v>Abishek Porel</v>
+        <v>Abishek Porel (Out)</v>
       </c>
       <c r="AA6" t="str">
         <v>Delhi Capitals</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -932,7 +932,7 @@
         <v>0</v>
       </c>
       <c r="AR4">
-        <v>302</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5">
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>356</v>
+        <v>404</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -1259,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -1304,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="AH7">
-        <v>567</v>
+        <v>703</v>
       </c>
       <c r="AI7" t="str">
         <v/>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="AR7">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="8">
@@ -1512,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>611</v>
+        <v>644</v>
       </c>
       <c r="O9" t="str">
         <v/>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>568</v>
+        <v>655</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>595</v>
+        <v>668</v>
       </c>
       <c r="AN11" t="str">
         <v/>
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>487</v>
+        <v>654</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="S12">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -1944,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <v>219</v>
+        <v>353</v>
       </c>
       <c r="Y12" t="str">
         <v/>
@@ -2316,7 +2316,7 @@
         <v/>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -2614,7 +2614,7 @@
         <v/>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="str">
         <v/>
@@ -2837,7 +2837,7 @@
         <v/>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -4669,7 +4669,7 @@
         <v/>
       </c>
       <c r="AM32">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AN32" t="str">
         <v/>
@@ -4922,7 +4922,7 @@
         <v/>
       </c>
       <c r="AH34">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AI34" t="str">
         <v/>
@@ -5488,7 +5488,7 @@
         <v/>
       </c>
       <c r="AR38">
-        <v>410</v>
+        <v>478</v>
       </c>
     </row>
     <row r="39">
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>2610</v>
+        <v>2807</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>4187</v>
+        <v>4393</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>2466</v>
+        <v>2486</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="X45">
-        <v>3003</v>
+        <v>3139</v>
       </c>
       <c r="Y45" t="str">
         <v/>
@@ -6396,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="AH45">
-        <v>3591</v>
+        <v>3781</v>
       </c>
       <c r="AI45" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>3852</v>
+        <v>3965</v>
       </c>
       <c r="AN45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>4816</v>
+        <v>4937</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="AN6" t="str">
         <v/>
@@ -1274,7 +1274,7 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>430</v>
+        <v>504</v>
       </c>
       <c r="Y7" t="str">
         <v/>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="T8" t="str">
         <v/>
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>448</v>
+        <v>489</v>
       </c>
       <c r="Y8" t="str">
         <v/>
@@ -1616,7 +1616,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>388</v>
+        <v>498</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -1646,7 +1646,7 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>378</v>
+        <v>455</v>
       </c>
       <c r="O10" t="str">
         <v/>
@@ -1810,7 +1810,7 @@
         <v>0</v>
       </c>
       <c r="X11">
-        <v>286</v>
+        <v>483</v>
       </c>
       <c r="Y11" t="str">
         <v/>
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="AR11">
-        <v>341</v>
+        <v>429</v>
       </c>
     </row>
     <row r="12">
@@ -1914,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="O12" t="str">
         <v/>
@@ -1989,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="AN12" t="str">
         <v/>
@@ -2018,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>258</v>
+        <v>342</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -2048,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>294</v>
+        <v>342</v>
       </c>
       <c r="O13" t="str">
         <v/>
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="AN13" t="str">
         <v/>
@@ -3969,7 +3969,7 @@
         <v/>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AD27" t="str">
         <v/>
@@ -4177,7 +4177,7 @@
         <v/>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J29" t="str">
         <v/>
@@ -5234,7 +5234,7 @@
         <v/>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>2350</v>
+        <v>2557</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>2807</v>
+        <v>2851</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>4393</v>
+        <v>4532</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>2486</v>
+        <v>2496</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="X45">
-        <v>3139</v>
+        <v>3451</v>
       </c>
       <c r="Y45" t="str">
         <v/>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AC45">
-        <v>2723</v>
+        <v>2777</v>
       </c>
       <c r="AD45" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>3965</v>
+        <v>4015</v>
       </c>
       <c r="AN45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>4937</v>
+        <v>5025</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -738,7 +738,7 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="Y3" t="str">
         <v/>
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="AC3">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="AD3" t="str">
         <v/>
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AN3" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>250</v>
+        <v>432</v>
       </c>
       <c r="T4" t="str">
         <v/>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="AR6">
-        <v>424</v>
+        <v>482</v>
       </c>
     </row>
     <row r="7">
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="AN7" t="str">
         <v/>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>246</v>
+        <v>281</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -1468,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="AR8">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="9">
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="AN9" t="str">
         <v/>
@@ -1631,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>546</v>
+        <v>694</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>674</v>
+        <v>721</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -2063,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="S13">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -3224,7 +3224,7 @@
         <v/>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -3433,7 +3433,7 @@
         <v/>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD23" t="str">
         <v/>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD24" t="str">
         <v/>
@@ -4430,7 +4430,7 @@
         <v/>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -5011,7 +5011,7 @@
         <v/>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T35" t="str">
         <v/>
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>2557</v>
+        <v>2790</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>2851</v>
+        <v>3046</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>2496</v>
+        <v>2687</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="X45">
-        <v>3451</v>
+        <v>3465</v>
       </c>
       <c r="Y45" t="str">
         <v/>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AC45">
-        <v>2777</v>
+        <v>2800</v>
       </c>
       <c r="AD45" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>4015</v>
+        <v>4022</v>
       </c>
       <c r="AN45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>5025</v>
+        <v>5088</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -3775,7 +3775,7 @@
         <v/>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J26" t="str">
         <v/>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>3046</v>
+        <v>3084</v>
       </c>
       <c r="J45" t="str">
         <v/>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -723,7 +723,7 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>587</v>
+        <v>619</v>
       </c>
       <c r="T3" t="str">
         <v/>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="AC5">
-        <v>366</v>
+        <v>406</v>
       </c>
       <c r="AD5" t="str">
         <v/>
@@ -1244,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="O7" t="str">
         <v/>
@@ -1363,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>212</v>
+        <v>328</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="AH8">
-        <v>713</v>
+        <v>765</v>
       </c>
       <c r="AI8" t="str">
         <v/>
@@ -1572,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="AH9">
-        <v>135</v>
+        <v>269</v>
       </c>
       <c r="AI9" t="str">
         <v/>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>552</v>
+        <v>623</v>
       </c>
       <c r="Y10" t="str">
         <v/>
@@ -1691,7 +1691,7 @@
         <v>0</v>
       </c>
       <c r="AC10">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="AD10" t="str">
         <v/>
@@ -1721,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>539</v>
+        <v>642</v>
       </c>
       <c r="AN10" t="str">
         <v/>
@@ -1750,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>791</v>
+        <v>892</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -1825,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="AC11">
-        <v>274</v>
+        <v>345</v>
       </c>
       <c r="AD11" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="AC12">
-        <v>585</v>
+        <v>641</v>
       </c>
       <c r="AD12" t="str">
         <v/>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="AR12">
-        <v>626</v>
+        <v>729</v>
       </c>
     </row>
     <row r="13">
@@ -2197,7 +2197,7 @@
         <v/>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -5115,7 +5115,7 @@
         <v/>
       </c>
       <c r="I36">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="J36" t="str">
         <v/>
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>2790</v>
+        <v>2891</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>3084</v>
+        <v>3244</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>4532</v>
+        <v>4544</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>2687</v>
+        <v>2791</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="X45">
-        <v>3465</v>
+        <v>3536</v>
       </c>
       <c r="Y45" t="str">
         <v/>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AC45">
-        <v>2800</v>
+        <v>2981</v>
       </c>
       <c r="AD45" t="str">
         <v/>
@@ -6396,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="AH45">
-        <v>3781</v>
+        <v>3967</v>
       </c>
       <c r="AI45" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>4022</v>
+        <v>4125</v>
       </c>
       <c r="AN45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>5088</v>
+        <v>5191</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -812,7 +812,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="AC4">
-        <v>380</v>
+        <v>544</v>
       </c>
       <c r="AD4" t="str">
         <v/>
@@ -946,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -1066,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="AR5">
-        <v>832</v>
+        <v>933</v>
       </c>
     </row>
     <row r="6">
@@ -1110,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>689</v>
+        <v>842</v>
       </c>
       <c r="O6" t="str">
         <v/>
@@ -1453,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>632</v>
+        <v>697</v>
       </c>
       <c r="AN8" t="str">
         <v/>
@@ -1542,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>341</v>
+        <v>450</v>
       </c>
       <c r="Y9" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -1706,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="AH10">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="AI10" t="str">
         <v/>
@@ -1840,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="AH11">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="AI11" t="str">
         <v/>
@@ -2078,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>297</v>
+        <v>536</v>
       </c>
       <c r="Y13" t="str">
         <v/>
@@ -2778,7 +2778,7 @@
         <v/>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AI18" t="str">
         <v/>
@@ -3001,7 +3001,7 @@
         <v/>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="T20" t="str">
         <v/>
@@ -3701,7 +3701,7 @@
         <v/>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AD25" t="str">
         <v/>
@@ -4058,7 +4058,7 @@
         <v/>
       </c>
       <c r="N28">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="O28" t="str">
         <v/>
@@ -4803,7 +4803,7 @@
         <v/>
       </c>
       <c r="AM33">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="AN33" t="str">
         <v/>
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>2891</v>
+        <v>3025</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>4544</v>
+        <v>4745</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>2791</v>
+        <v>2839</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="X45">
-        <v>3536</v>
+        <v>3884</v>
       </c>
       <c r="Y45" t="str">
         <v/>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AC45">
-        <v>2981</v>
+        <v>3159</v>
       </c>
       <c r="AD45" t="str">
         <v/>
@@ -6396,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="AH45">
-        <v>3967</v>
+        <v>4081</v>
       </c>
       <c r="AI45" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>4125</v>
+        <v>4226</v>
       </c>
       <c r="AN45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>5191</v>
+        <v>5292</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -857,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="T4" t="str">
         <v/>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="AR6">
-        <v>482</v>
+        <v>494</v>
       </c>
     </row>
     <row r="7">
@@ -1259,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>466</v>
+        <v>603</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -1304,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="AH7">
-        <v>703</v>
+        <v>755</v>
       </c>
       <c r="AI7" t="str">
         <v/>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="AR7">
-        <v>373</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8">
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>552</v>
+        <v>589</v>
       </c>
       <c r="AN9" t="str">
         <v/>
@@ -1631,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>694</v>
+        <v>853</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>721</v>
+        <v>799</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>655</v>
+        <v>750</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>668</v>
+        <v>771</v>
       </c>
       <c r="AN11" t="str">
         <v/>
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>654</v>
+        <v>684</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -2063,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="S13">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -3224,7 +3224,7 @@
         <v/>
       </c>
       <c r="D22">
-        <v>96</v>
+        <v>188</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="AC24">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="AD24" t="str">
         <v/>
@@ -4430,7 +4430,7 @@
         <v/>
       </c>
       <c r="D31">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -4922,7 +4922,7 @@
         <v/>
       </c>
       <c r="AH34">
-        <v>54</v>
+        <v>182</v>
       </c>
       <c r="AI34" t="str">
         <v/>
@@ -5488,7 +5488,7 @@
         <v/>
       </c>
       <c r="AR38">
-        <v>478</v>
+        <v>536</v>
       </c>
     </row>
     <row r="39">
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>3025</v>
+        <v>3157</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>3244</v>
+        <v>3511</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>4745</v>
+        <v>4840</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>2839</v>
+        <v>3013</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AC45">
-        <v>3159</v>
+        <v>3282</v>
       </c>
       <c r="AD45" t="str">
         <v/>
@@ -6396,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="AH45">
-        <v>4081</v>
+        <v>4261</v>
       </c>
       <c r="AI45" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>4226</v>
+        <v>4366</v>
       </c>
       <c r="AN45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>5292</v>
+        <v>5384</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -723,7 +723,7 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>619</v>
+        <v>701</v>
       </c>
       <c r="T3" t="str">
         <v/>
@@ -738,7 +738,7 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>235</v>
+        <v>275</v>
       </c>
       <c r="Y3" t="str">
         <v/>
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="AC3">
-        <v>393</v>
+        <v>437</v>
       </c>
       <c r="AD3" t="str">
         <v/>
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="AN3" t="str">
         <v/>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="AH5">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AI5" t="str">
         <v/>
@@ -1244,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>527</v>
+        <v>605</v>
       </c>
       <c r="O7" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>387</v>
+        <v>441</v>
       </c>
       <c r="AN7" t="str">
         <v/>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="AH8">
-        <v>765</v>
+        <v>814</v>
       </c>
       <c r="AI8" t="str">
         <v/>
@@ -1468,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="AR8">
-        <v>735</v>
+        <v>886</v>
       </c>
     </row>
     <row r="9">
@@ -1721,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>642</v>
+        <v>658</v>
       </c>
       <c r="AN10" t="str">
         <v/>
@@ -1750,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>892</v>
+        <v>904</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -1825,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="AC11">
-        <v>345</v>
+        <v>519</v>
       </c>
       <c r="AD11" t="str">
         <v/>
@@ -3433,7 +3433,7 @@
         <v/>
       </c>
       <c r="AC23">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AD23" t="str">
         <v/>
@@ -4296,7 +4296,7 @@
         <v/>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -5011,7 +5011,7 @@
         <v/>
       </c>
       <c r="S35">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="T35" t="str">
         <v/>
@@ -5115,7 +5115,7 @@
         <v/>
       </c>
       <c r="I36">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="J36" t="str">
         <v/>
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>3157</v>
+        <v>3291</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>3511</v>
+        <v>3523</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>4840</v>
+        <v>4918</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>3013</v>
+        <v>3168</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="X45">
-        <v>3884</v>
+        <v>3924</v>
       </c>
       <c r="Y45" t="str">
         <v/>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AC45">
-        <v>3282</v>
+        <v>3504</v>
       </c>
       <c r="AD45" t="str">
         <v/>
@@ -6396,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="AH45">
-        <v>4261</v>
+        <v>4312</v>
       </c>
       <c r="AI45" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>4366</v>
+        <v>4446</v>
       </c>
       <c r="AN45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>5384</v>
+        <v>5535</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -932,7 +932,7 @@
         <v>0</v>
       </c>
       <c r="AR4">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5">
@@ -946,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>404</v>
+        <v>490</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -1512,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>644</v>
+        <v>667</v>
       </c>
       <c r="O9" t="str">
         <v/>
@@ -1542,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="Y9" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>253</v>
+        <v>309</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -1706,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="AH10">
-        <v>326</v>
+        <v>375</v>
       </c>
       <c r="AI10" t="str">
         <v/>
@@ -1840,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="AH11">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="AI11" t="str">
         <v/>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="S12">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -1944,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <v>353</v>
+        <v>474</v>
       </c>
       <c r="Y12" t="str">
         <v/>
@@ -2078,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>536</v>
+        <v>623</v>
       </c>
       <c r="Y13" t="str">
         <v/>
@@ -2316,7 +2316,7 @@
         <v/>
       </c>
       <c r="N15">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -2778,7 +2778,7 @@
         <v/>
       </c>
       <c r="AH18">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="AI18" t="str">
         <v/>
@@ -2837,7 +2837,7 @@
         <v/>
       </c>
       <c r="I19">
-        <v>30</v>
+        <v>166</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -3001,7 +3001,7 @@
         <v/>
       </c>
       <c r="S20">
-        <v>38</v>
+        <v>145</v>
       </c>
       <c r="T20" t="str">
         <v/>
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>3291</v>
+        <v>3296</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>3523</v>
+        <v>3659</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>4918</v>
+        <v>5089</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>3168</v>
+        <v>3351</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="X45">
-        <v>3924</v>
+        <v>4162</v>
       </c>
       <c r="Y45" t="str">
         <v/>
@@ -6396,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="AH45">
-        <v>4312</v>
+        <v>4428</v>
       </c>
       <c r="AI45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>5535</v>
+        <v>5539</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>718</v>
+        <v>798</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -812,7 +812,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="AC4">
-        <v>544</v>
+        <v>679</v>
       </c>
       <c r="AD4" t="str">
         <v/>
@@ -1066,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="AR5">
-        <v>933</v>
+        <v>976</v>
       </c>
     </row>
     <row r="6">
@@ -1110,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>842</v>
+        <v>875</v>
       </c>
       <c r="O6" t="str">
         <v/>
@@ -1274,7 +1274,7 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>504</v>
+        <v>602</v>
       </c>
       <c r="Y7" t="str">
         <v/>
@@ -1616,7 +1616,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>498</v>
+        <v>563</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -1810,7 +1810,7 @@
         <v>0</v>
       </c>
       <c r="X11">
-        <v>483</v>
+        <v>531</v>
       </c>
       <c r="Y11" t="str">
         <v/>
@@ -2018,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>342</v>
+        <v>466</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>302</v>
+        <v>391</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>418</v>
+        <v>529</v>
       </c>
       <c r="AN13" t="str">
         <v/>
@@ -3969,7 +3969,7 @@
         <v/>
       </c>
       <c r="AC27">
-        <v>54</v>
+        <v>138</v>
       </c>
       <c r="AD27" t="str">
         <v/>
@@ -4058,7 +4058,7 @@
         <v/>
       </c>
       <c r="N28">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="O28" t="str">
         <v/>
@@ -4803,7 +4803,7 @@
         <v/>
       </c>
       <c r="AM33">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AN33" t="str">
         <v/>
@@ -5234,7 +5234,7 @@
         <v/>
       </c>
       <c r="D37">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>3296</v>
+        <v>3637</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>3659</v>
+        <v>3748</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>5089</v>
+        <v>5146</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="X45">
-        <v>4162</v>
+        <v>4308</v>
       </c>
       <c r="Y45" t="str">
         <v/>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AC45">
-        <v>3504</v>
+        <v>3723</v>
       </c>
       <c r="AD45" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>4446</v>
+        <v>4611</v>
       </c>
       <c r="AN45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>5539</v>
+        <v>5582</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="AC5">
-        <v>406</v>
+        <v>495</v>
       </c>
       <c r="AD5" t="str">
         <v/>
@@ -1259,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>603</v>
+        <v>653</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -1304,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="AH7">
-        <v>755</v>
+        <v>869</v>
       </c>
       <c r="AI7" t="str">
         <v/>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="AR7">
-        <v>395</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8">
@@ -1363,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -1572,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="AH9">
-        <v>269</v>
+        <v>381</v>
       </c>
       <c r="AI9" t="str">
         <v/>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="Y10" t="str">
         <v/>
@@ -1691,7 +1691,7 @@
         <v>0</v>
       </c>
       <c r="AC10">
-        <v>316</v>
+        <v>406</v>
       </c>
       <c r="AD10" t="str">
         <v/>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>750</v>
+        <v>828</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>771</v>
+        <v>792</v>
       </c>
       <c r="AN11" t="str">
         <v/>
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>684</v>
+        <v>781</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="AC12">
-        <v>641</v>
+        <v>682</v>
       </c>
       <c r="AD12" t="str">
         <v/>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="AR12">
-        <v>729</v>
+        <v>756</v>
       </c>
     </row>
     <row r="13">
@@ -2197,7 +2197,7 @@
         <v/>
       </c>
       <c r="S14">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -2406,7 +2406,7 @@
         <v/>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -4922,7 +4922,7 @@
         <v/>
       </c>
       <c r="AH34">
-        <v>182</v>
+        <v>363</v>
       </c>
       <c r="AI34" t="str">
         <v/>
@@ -5488,7 +5488,7 @@
         <v/>
       </c>
       <c r="AR38">
-        <v>536</v>
+        <v>626</v>
       </c>
     </row>
     <row r="39">
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>3748</v>
+        <v>3849</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>5146</v>
+        <v>5224</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>3351</v>
+        <v>3419</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="X45">
-        <v>4308</v>
+        <v>4314</v>
       </c>
       <c r="Y45" t="str">
         <v/>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AC45">
-        <v>3723</v>
+        <v>3943</v>
       </c>
       <c r="AD45" t="str">
         <v/>
@@ -6396,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="AH45">
-        <v>4428</v>
+        <v>4835</v>
       </c>
       <c r="AI45" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>4611</v>
+        <v>4632</v>
       </c>
       <c r="AN45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>5582</v>
+        <v>5823</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -902,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="AH4">
-        <v>281</v>
+        <v>455</v>
       </c>
       <c r="AI4" t="str">
         <v/>
@@ -946,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>489</v>
+        <v>537</v>
       </c>
       <c r="Y8" t="str">
         <v/>
@@ -1646,7 +1646,7 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>455</v>
+        <v>512</v>
       </c>
       <c r="O10" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -1706,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="AH10">
-        <v>375</v>
+        <v>407</v>
       </c>
       <c r="AI10" t="str">
         <v/>
@@ -1736,7 +1736,7 @@
         <v>0</v>
       </c>
       <c r="AR10">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11">
@@ -1840,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="AH11">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="AI11" t="str">
         <v/>
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="AR11">
-        <v>429</v>
+        <v>460</v>
       </c>
     </row>
     <row r="12">
@@ -1914,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <v>432</v>
+        <v>524</v>
       </c>
       <c r="O12" t="str">
         <v/>
@@ -1989,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>184</v>
+        <v>327</v>
       </c>
       <c r="AN12" t="str">
         <v/>
@@ -2078,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>623</v>
+        <v>818</v>
       </c>
       <c r="Y13" t="str">
         <v/>
@@ -2778,7 +2778,7 @@
         <v/>
       </c>
       <c r="AH18">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="AI18" t="str">
         <v/>
@@ -3001,7 +3001,7 @@
         <v/>
       </c>
       <c r="S20">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="T20" t="str">
         <v/>
@@ -4177,7 +4177,7 @@
         <v/>
       </c>
       <c r="I29">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="J29" t="str">
         <v/>
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>3637</v>
+        <v>3685</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>3849</v>
+        <v>3867</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>5224</v>
+        <v>5373</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>3419</v>
+        <v>3494</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="X45">
-        <v>4314</v>
+        <v>4557</v>
       </c>
       <c r="Y45" t="str">
         <v/>
@@ -6396,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="AH45">
-        <v>4835</v>
+        <v>5092</v>
       </c>
       <c r="AI45" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>4632</v>
+        <v>4775</v>
       </c>
       <c r="AN45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>5823</v>
+        <v>5858</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -738,7 +738,7 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="Y3" t="str">
         <v/>
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="AC3">
-        <v>437</v>
+        <v>499</v>
       </c>
       <c r="AD3" t="str">
         <v/>
@@ -768,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="AH3">
-        <v>364</v>
+        <v>424</v>
       </c>
       <c r="AI3" t="str">
         <v/>
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="AN3" t="str">
         <v/>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>490</v>
+        <v>568</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>441</v>
+        <v>505</v>
       </c>
       <c r="AN7" t="str">
         <v/>
@@ -1468,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="AR8">
-        <v>886</v>
+        <v>920</v>
       </c>
     </row>
     <row r="9">
@@ -1512,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>667</v>
+        <v>838</v>
       </c>
       <c r="O9" t="str">
         <v/>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="S12">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -1944,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <v>474</v>
+        <v>498</v>
       </c>
       <c r="Y12" t="str">
         <v/>
@@ -2316,7 +2316,7 @@
         <v/>
       </c>
       <c r="N15">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -2837,7 +2837,7 @@
         <v/>
       </c>
       <c r="I19">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -3433,7 +3433,7 @@
         <v/>
       </c>
       <c r="AC23">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="AD23" t="str">
         <v/>
@@ -4296,7 +4296,7 @@
         <v/>
       </c>
       <c r="D30">
-        <v>122</v>
+        <v>163</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -4669,7 +4669,7 @@
         <v/>
       </c>
       <c r="AM32">
-        <v>40</v>
+        <v>118</v>
       </c>
       <c r="AN32" t="str">
         <v/>
@@ -5011,7 +5011,7 @@
         <v/>
       </c>
       <c r="S35">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="T35" t="str">
         <v/>
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>3685</v>
+        <v>3726</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>3867</v>
+        <v>3879</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>5373</v>
+        <v>5658</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>3494</v>
+        <v>3533</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="X45">
-        <v>4557</v>
+        <v>4587</v>
       </c>
       <c r="Y45" t="str">
         <v/>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AC45">
-        <v>3943</v>
+        <v>4089</v>
       </c>
       <c r="AD45" t="str">
         <v/>
@@ -6396,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="AH45">
-        <v>5092</v>
+        <v>5152</v>
       </c>
       <c r="AI45" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>4775</v>
+        <v>4931</v>
       </c>
       <c r="AN45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>5858</v>
+        <v>5892</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>798</v>
+        <v>911</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -812,7 +812,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>144</v>
+        <v>244</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="AC4">
-        <v>679</v>
+        <v>763</v>
       </c>
       <c r="AD4" t="str">
         <v/>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="AC5">
-        <v>495</v>
+        <v>539</v>
       </c>
       <c r="AD5" t="str">
         <v/>
@@ -1066,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="AR5">
-        <v>976</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="6">
@@ -1110,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>875</v>
+        <v>996</v>
       </c>
       <c r="O6" t="str">
         <v/>
@@ -1363,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>332</v>
+        <v>378</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -1378,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="O8" t="str">
         <v/>
@@ -1453,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>697</v>
+        <v>814</v>
       </c>
       <c r="AN8" t="str">
         <v/>
@@ -1572,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="AH9">
-        <v>381</v>
+        <v>449</v>
       </c>
       <c r="AI9" t="str">
         <v/>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="Y10" t="str">
         <v/>
@@ -1691,7 +1691,7 @@
         <v>0</v>
       </c>
       <c r="AC10">
-        <v>406</v>
+        <v>453</v>
       </c>
       <c r="AD10" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="AC12">
-        <v>682</v>
+        <v>703</v>
       </c>
       <c r="AD12" t="str">
         <v/>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="AR12">
-        <v>756</v>
+        <v>763</v>
       </c>
     </row>
     <row r="13">
@@ -2197,7 +2197,7 @@
         <v/>
       </c>
       <c r="S14">
-        <v>90</v>
+        <v>299</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -3701,7 +3701,7 @@
         <v/>
       </c>
       <c r="AC25">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AD25" t="str">
         <v/>
@@ -4058,7 +4058,7 @@
         <v/>
       </c>
       <c r="N28">
-        <v>158</v>
+        <v>222</v>
       </c>
       <c r="O28" t="str">
         <v/>
@@ -4803,7 +4803,7 @@
         <v/>
       </c>
       <c r="AM33">
-        <v>138</v>
+        <v>186</v>
       </c>
       <c r="AN33" t="str">
         <v/>
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>3726</v>
+        <v>3939</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>3879</v>
+        <v>3925</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>5658</v>
+        <v>5855</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>3533</v>
+        <v>3742</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="X45">
-        <v>4587</v>
+        <v>4592</v>
       </c>
       <c r="Y45" t="str">
         <v/>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AC45">
-        <v>4089</v>
+        <v>4293</v>
       </c>
       <c r="AD45" t="str">
         <v/>
@@ -6396,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="AH45">
-        <v>5152</v>
+        <v>5220</v>
       </c>
       <c r="AI45" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>4931</v>
+        <v>5096</v>
       </c>
       <c r="AN45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>5892</v>
+        <v>5990</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -857,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>450</v>
+        <v>496</v>
       </c>
       <c r="T4" t="str">
         <v/>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="AN6" t="str">
         <v/>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="AR6">
-        <v>494</v>
+        <v>620</v>
       </c>
     </row>
     <row r="7">
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>537</v>
+        <v>597</v>
       </c>
       <c r="Y8" t="str">
         <v/>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>589</v>
+        <v>726</v>
       </c>
       <c r="AN9" t="str">
         <v/>
@@ -1631,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>853</v>
+        <v>873</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -1646,7 +1646,7 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="O10" t="str">
         <v/>
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="AR11">
-        <v>460</v>
+        <v>544</v>
       </c>
     </row>
     <row r="12">
@@ -1914,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <v>524</v>
+        <v>753</v>
       </c>
       <c r="O12" t="str">
         <v/>
@@ -1989,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>327</v>
+        <v>399</v>
       </c>
       <c r="AN12" t="str">
         <v/>
@@ -2063,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="S13">
-        <v>422</v>
+        <v>512</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -3224,7 +3224,7 @@
         <v/>
       </c>
       <c r="D22">
-        <v>188</v>
+        <v>250</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="AC24">
-        <v>131</v>
+        <v>184</v>
       </c>
       <c r="AD24" t="str">
         <v/>
@@ -3775,7 +3775,7 @@
         <v/>
       </c>
       <c r="I26">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="J26" t="str">
         <v/>
@@ -4177,7 +4177,7 @@
         <v/>
       </c>
       <c r="I29">
-        <v>46</v>
+        <v>188</v>
       </c>
       <c r="J29" t="str">
         <v/>
@@ -4430,7 +4430,7 @@
         <v/>
       </c>
       <c r="D31">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>3939</v>
+        <v>4007</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>3925</v>
+        <v>4127</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>5855</v>
+        <v>6097</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>3742</v>
+        <v>3878</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="X45">
-        <v>4592</v>
+        <v>4652</v>
       </c>
       <c r="Y45" t="str">
         <v/>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AC45">
-        <v>4293</v>
+        <v>4346</v>
       </c>
       <c r="AD45" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>5096</v>
+        <v>5319</v>
       </c>
       <c r="AN45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>5990</v>
+        <v>6200</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="AC3">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="AD3" t="str">
         <v/>
@@ -768,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="AH3">
-        <v>424</v>
+        <v>447</v>
       </c>
       <c r="AI3" t="str">
         <v/>
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="AN3" t="str">
         <v/>
@@ -1274,7 +1274,7 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>602</v>
+        <v>680</v>
       </c>
       <c r="Y7" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>505</v>
+        <v>574</v>
       </c>
       <c r="AN7" t="str">
         <v/>
@@ -1468,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="AR8">
-        <v>920</v>
+        <v>967</v>
       </c>
     </row>
     <row r="9">
@@ -1616,7 +1616,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>563</v>
+        <v>658</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -1810,7 +1810,7 @@
         <v>0</v>
       </c>
       <c r="X11">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="Y11" t="str">
         <v/>
@@ -2018,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>466</v>
+        <v>494</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>391</v>
+        <v>426</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>529</v>
+        <v>551</v>
       </c>
       <c r="AN13" t="str">
         <v/>
@@ -3165,7 +3165,7 @@
         <v/>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD21" t="str">
         <v/>
@@ -3433,7 +3433,7 @@
         <v/>
       </c>
       <c r="AC23">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="AD23" t="str">
         <v/>
@@ -3969,7 +3969,7 @@
         <v/>
       </c>
       <c r="AC27">
-        <v>138</v>
+        <v>231</v>
       </c>
       <c r="AD27" t="str">
         <v/>
@@ -4296,7 +4296,7 @@
         <v/>
       </c>
       <c r="D30">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -5011,7 +5011,7 @@
         <v/>
       </c>
       <c r="S35">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="T35" t="str">
         <v/>
@@ -5234,7 +5234,7 @@
         <v/>
       </c>
       <c r="D37">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>4007</v>
+        <v>4248</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>4127</v>
+        <v>4162</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>3878</v>
+        <v>3892</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="X45">
-        <v>4652</v>
+        <v>4734</v>
       </c>
       <c r="Y45" t="str">
         <v/>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AC45">
-        <v>4346</v>
+        <v>4456</v>
       </c>
       <c r="AD45" t="str">
         <v/>
@@ -6396,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="AH45">
-        <v>5220</v>
+        <v>5243</v>
       </c>
       <c r="AI45" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>5319</v>
+        <v>5420</v>
       </c>
       <c r="AN45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>6200</v>
+        <v>6247</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -723,7 +723,7 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>701</v>
+        <v>759</v>
       </c>
       <c r="T3" t="str">
         <v/>
@@ -1095,7 +1095,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -1244,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>605</v>
+        <v>719</v>
       </c>
       <c r="O7" t="str">
         <v/>
@@ -1259,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>653</v>
+        <v>845</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -1304,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="AH7">
-        <v>869</v>
+        <v>949</v>
       </c>
       <c r="AI7" t="str">
         <v/>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="AR7">
-        <v>483</v>
+        <v>586</v>
       </c>
     </row>
     <row r="8">
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="AH8">
-        <v>814</v>
+        <v>837</v>
       </c>
       <c r="AI8" t="str">
         <v/>
@@ -1721,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>658</v>
+        <v>673</v>
       </c>
       <c r="AN10" t="str">
         <v/>
@@ -1750,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>904</v>
+        <v>986</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>828</v>
+        <v>865</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>792</v>
+        <v>962</v>
       </c>
       <c r="AN11" t="str">
         <v/>
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>781</v>
+        <v>888</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -4922,7 +4922,7 @@
         <v/>
       </c>
       <c r="AH34">
-        <v>363</v>
+        <v>508</v>
       </c>
       <c r="AI34" t="str">
         <v/>
@@ -5488,7 +5488,7 @@
         <v/>
       </c>
       <c r="AR38">
-        <v>626</v>
+        <v>670</v>
       </c>
     </row>
     <row r="39">
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>4248</v>
+        <v>4330</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>4162</v>
+        <v>4283</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>6097</v>
+        <v>6248</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>3892</v>
+        <v>4142</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -6396,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="AH45">
-        <v>5243</v>
+        <v>5491</v>
       </c>
       <c r="AI45" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>5420</v>
+        <v>5605</v>
       </c>
       <c r="AN45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>6247</v>
+        <v>6394</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -857,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>496</v>
+        <v>554</v>
       </c>
       <c r="T4" t="str">
         <v/>
@@ -902,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="AH4">
-        <v>455</v>
+        <v>509</v>
       </c>
       <c r="AI4" t="str">
         <v/>
@@ -932,7 +932,7 @@
         <v>0</v>
       </c>
       <c r="AR4">
-        <v>354</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5">
@@ -946,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>568</v>
+        <v>626</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>224</v>
+        <v>314</v>
       </c>
       <c r="AN6" t="str">
         <v/>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="AR6">
-        <v>620</v>
+        <v>757</v>
       </c>
     </row>
     <row r="7">
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="Y8" t="str">
         <v/>
@@ -1512,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>838</v>
+        <v>919</v>
       </c>
       <c r="O9" t="str">
         <v/>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>726</v>
+        <v>758</v>
       </c>
       <c r="AN9" t="str">
         <v/>
@@ -1631,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>873</v>
+        <v>1060</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -1646,7 +1646,7 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="O10" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>323</v>
+        <v>353</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -1706,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="AH10">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AI10" t="str">
         <v/>
@@ -1736,7 +1736,7 @@
         <v>0</v>
       </c>
       <c r="AR10">
-        <v>272</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11">
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>801</v>
+        <v>811</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -1840,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="AH11">
-        <v>460</v>
+        <v>583</v>
       </c>
       <c r="AI11" t="str">
         <v/>
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="AR11">
-        <v>544</v>
+        <v>571</v>
       </c>
     </row>
     <row r="12">
@@ -1914,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <v>753</v>
+        <v>773</v>
       </c>
       <c r="O12" t="str">
         <v/>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="S12">
-        <v>240</v>
+        <v>274</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -1944,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <v>498</v>
+        <v>574</v>
       </c>
       <c r="Y12" t="str">
         <v/>
@@ -1989,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="AN12" t="str">
         <v/>
@@ -2063,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="S13">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -2078,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>818</v>
+        <v>852</v>
       </c>
       <c r="Y13" t="str">
         <v/>
@@ -2316,7 +2316,7 @@
         <v/>
       </c>
       <c r="N15">
-        <v>136</v>
+        <v>268</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -2778,7 +2778,7 @@
         <v/>
       </c>
       <c r="AH18">
-        <v>172</v>
+        <v>212</v>
       </c>
       <c r="AI18" t="str">
         <v/>
@@ -2837,7 +2837,7 @@
         <v/>
       </c>
       <c r="I19">
-        <v>178</v>
+        <v>267</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -3001,7 +3001,7 @@
         <v/>
       </c>
       <c r="S20">
-        <v>206</v>
+        <v>303</v>
       </c>
       <c r="T20" t="str">
         <v/>
@@ -3224,7 +3224,7 @@
         <v/>
       </c>
       <c r="D22">
-        <v>250</v>
+        <v>276</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="AC24">
-        <v>184</v>
+        <v>234</v>
       </c>
       <c r="AD24" t="str">
         <v/>
@@ -3775,7 +3775,7 @@
         <v/>
       </c>
       <c r="I26">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="J26" t="str">
         <v/>
@@ -4177,7 +4177,7 @@
         <v/>
       </c>
       <c r="I29">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="J29" t="str">
         <v/>
@@ -4430,7 +4430,7 @@
         <v/>
       </c>
       <c r="D31">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -4669,7 +4669,7 @@
         <v/>
       </c>
       <c r="AM32">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="AN32" t="str">
         <v/>
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>4330</v>
+        <v>4388</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>4283</v>
+        <v>4648</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>6248</v>
+        <v>6549</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>4142</v>
+        <v>4363</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="X45">
-        <v>4734</v>
+        <v>4858</v>
       </c>
       <c r="Y45" t="str">
         <v/>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AC45">
-        <v>4456</v>
+        <v>4506</v>
       </c>
       <c r="AD45" t="str">
         <v/>
@@ -6396,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="AH45">
-        <v>5491</v>
+        <v>5710</v>
       </c>
       <c r="AI45" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>5605</v>
+        <v>5738</v>
       </c>
       <c r="AN45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>6394</v>
+        <v>6643</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="AC3">
-        <v>505</v>
+        <v>523</v>
       </c>
       <c r="AD3" t="str">
         <v/>
@@ -768,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="AH3">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="AI3" t="str">
         <v/>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="AC5">
-        <v>539</v>
+        <v>637</v>
       </c>
       <c r="AD5" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>574</v>
+        <v>700</v>
       </c>
       <c r="AN7" t="str">
         <v/>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>281</v>
+        <v>394</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -1363,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -1378,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O8" t="str">
         <v/>
@@ -1468,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="AR8">
-        <v>967</v>
+        <v>988</v>
       </c>
     </row>
     <row r="9">
@@ -1572,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="AH9">
-        <v>449</v>
+        <v>484</v>
       </c>
       <c r="AI9" t="str">
         <v/>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>634</v>
+        <v>750</v>
       </c>
       <c r="Y10" t="str">
         <v/>
@@ -1691,7 +1691,7 @@
         <v>0</v>
       </c>
       <c r="AC10">
-        <v>453</v>
+        <v>477</v>
       </c>
       <c r="AD10" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="AC12">
-        <v>703</v>
+        <v>816</v>
       </c>
       <c r="AD12" t="str">
         <v/>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="AR12">
-        <v>763</v>
+        <v>805</v>
       </c>
     </row>
     <row r="13">
@@ -2197,7 +2197,7 @@
         <v/>
       </c>
       <c r="S14">
-        <v>299</v>
+        <v>381</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -3165,7 +3165,7 @@
         <v/>
       </c>
       <c r="AC21">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="AD21" t="str">
         <v/>
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>4388</v>
+        <v>4501</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>4648</v>
+        <v>4660</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>6549</v>
+        <v>6551</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>4363</v>
+        <v>4445</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="X45">
-        <v>4858</v>
+        <v>4974</v>
       </c>
       <c r="Y45" t="str">
         <v/>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AC45">
-        <v>4506</v>
+        <v>4809</v>
       </c>
       <c r="AD45" t="str">
         <v/>
@@ -6396,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="AH45">
-        <v>5710</v>
+        <v>5759</v>
       </c>
       <c r="AI45" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>5738</v>
+        <v>5864</v>
       </c>
       <c r="AN45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>6643</v>
+        <v>6706</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>911</v>
+        <v>952</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -812,7 +812,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>244</v>
+        <v>345</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="AC4">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="AD4" t="str">
         <v/>
@@ -1066,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="AR5">
-        <v>1067</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="6">
@@ -1110,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>996</v>
+        <v>1036</v>
       </c>
       <c r="O6" t="str">
         <v/>
@@ -1259,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>845</v>
+        <v>885</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -1304,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="AH7">
-        <v>949</v>
+        <v>1089</v>
       </c>
       <c r="AI7" t="str">
         <v/>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="AR7">
-        <v>586</v>
+        <v>694</v>
       </c>
     </row>
     <row r="8">
@@ -1453,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>814</v>
+        <v>838</v>
       </c>
       <c r="AN8" t="str">
         <v/>
@@ -1602,7 +1602,7 @@
         <v>0</v>
       </c>
       <c r="AR9">
-        <v>515</v>
+        <v>601</v>
       </c>
     </row>
     <row r="10">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>865</v>
+        <v>924</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>962</v>
+        <v>983</v>
       </c>
       <c r="AN11" t="str">
         <v/>
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>888</v>
+        <v>995</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -4058,7 +4058,7 @@
         <v/>
       </c>
       <c r="N28">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="O28" t="str">
         <v/>
@@ -4803,7 +4803,7 @@
         <v/>
       </c>
       <c r="AM33">
-        <v>186</v>
+        <v>264</v>
       </c>
       <c r="AN33" t="str">
         <v/>
@@ -4922,7 +4922,7 @@
         <v/>
       </c>
       <c r="AH34">
-        <v>508</v>
+        <v>657</v>
       </c>
       <c r="AI34" t="str">
         <v/>
@@ -5488,7 +5488,7 @@
         <v/>
       </c>
       <c r="AR38">
-        <v>670</v>
+        <v>758</v>
       </c>
     </row>
     <row r="39">
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>4501</v>
+        <v>4643</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>4660</v>
+        <v>4767</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>6551</v>
+        <v>6658</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>4445</v>
+        <v>4485</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AC45">
-        <v>4809</v>
+        <v>4811</v>
       </c>
       <c r="AD45" t="str">
         <v/>
@@ -6396,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="AH45">
-        <v>5759</v>
+        <v>6048</v>
       </c>
       <c r="AI45" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>5864</v>
+        <v>5987</v>
       </c>
       <c r="AN45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>6706</v>
+        <v>7004</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -857,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>554</v>
+        <v>612</v>
       </c>
       <c r="T4" t="str">
         <v/>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="AR6">
-        <v>757</v>
+        <v>771</v>
       </c>
     </row>
     <row r="7">
@@ -1274,7 +1274,7 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>680</v>
+        <v>732</v>
       </c>
       <c r="Y7" t="str">
         <v/>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>758</v>
+        <v>779</v>
       </c>
       <c r="AN9" t="str">
         <v/>
@@ -1616,7 +1616,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>658</v>
+        <v>716</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -1631,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>1060</v>
+        <v>1117</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>811</v>
+        <v>1004</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -1810,7 +1810,7 @@
         <v>0</v>
       </c>
       <c r="X11">
-        <v>535</v>
+        <v>620</v>
       </c>
       <c r="Y11" t="str">
         <v/>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>426</v>
+        <v>485</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -2063,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="S13">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>551</v>
+        <v>684</v>
       </c>
       <c r="AN13" t="str">
         <v/>
@@ -3224,7 +3224,7 @@
         <v/>
       </c>
       <c r="D22">
-        <v>276</v>
+        <v>358</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -3775,7 +3775,7 @@
         <v/>
       </c>
       <c r="I26">
-        <v>131</v>
+        <v>185</v>
       </c>
       <c r="J26" t="str">
         <v/>
@@ -3969,7 +3969,7 @@
         <v/>
       </c>
       <c r="AC27">
-        <v>231</v>
+        <v>365</v>
       </c>
       <c r="AD27" t="str">
         <v/>
@@ -5234,7 +5234,7 @@
         <v/>
       </c>
       <c r="D37">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>4643</v>
+        <v>4787</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>4767</v>
+        <v>5130</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>4485</v>
+        <v>4549</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="X45">
-        <v>4974</v>
+        <v>5111</v>
       </c>
       <c r="Y45" t="str">
         <v/>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AC45">
-        <v>4811</v>
+        <v>4945</v>
       </c>
       <c r="AD45" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>5987</v>
+        <v>6141</v>
       </c>
       <c r="AN45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>7004</v>
+        <v>7018</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -902,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="AH4">
-        <v>509</v>
+        <v>552</v>
       </c>
       <c r="AI4" t="str">
         <v/>
@@ -946,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>191</v>
+        <v>268</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="AC5">
-        <v>637</v>
+        <v>671</v>
       </c>
       <c r="AD5" t="str">
         <v/>
@@ -1363,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>390</v>
+        <v>448</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -1378,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="O8" t="str">
         <v/>
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>247</v>
+        <v>279</v>
       </c>
       <c r="T9" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="Y10" t="str">
         <v/>
@@ -1691,7 +1691,7 @@
         <v>0</v>
       </c>
       <c r="AC10">
-        <v>477</v>
+        <v>515</v>
       </c>
       <c r="AD10" t="str">
         <v/>
@@ -1840,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="AH11">
-        <v>583</v>
+        <v>742</v>
       </c>
       <c r="AI11" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="AC12">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="AD12" t="str">
         <v/>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="AR12">
-        <v>805</v>
+        <v>928</v>
       </c>
     </row>
     <row r="13">
@@ -2078,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>852</v>
+        <v>956</v>
       </c>
       <c r="Y13" t="str">
         <v/>
@@ -2197,7 +2197,7 @@
         <v/>
       </c>
       <c r="S14">
-        <v>381</v>
+        <v>418</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -2406,7 +2406,7 @@
         <v/>
       </c>
       <c r="AR15">
-        <v>36</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16">
@@ -3001,7 +3001,7 @@
         <v/>
       </c>
       <c r="S20">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="T20" t="str">
         <v/>
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>4787</v>
+        <v>4864</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>5130</v>
+        <v>5188</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>6658</v>
+        <v>6664</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>4549</v>
+        <v>4659</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="X45">
-        <v>5111</v>
+        <v>5265</v>
       </c>
       <c r="Y45" t="str">
         <v/>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AC45">
-        <v>4945</v>
+        <v>5029</v>
       </c>
       <c r="AD45" t="str">
         <v/>
@@ -6396,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="AH45">
-        <v>6048</v>
+        <v>6250</v>
       </c>
       <c r="AI45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>7018</v>
+        <v>7197</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>952</v>
+        <v>1090</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -723,7 +723,7 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>759</v>
+        <v>968</v>
       </c>
       <c r="T3" t="str">
         <v/>
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="AC3">
-        <v>523</v>
+        <v>539</v>
       </c>
       <c r="AD3" t="str">
         <v/>
@@ -768,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="AH3">
-        <v>461</v>
+        <v>567</v>
       </c>
       <c r="AI3" t="str">
         <v/>
@@ -812,7 +812,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>345</v>
+        <v>481</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>612</v>
+        <v>674</v>
       </c>
       <c r="T4" t="str">
         <v/>
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="AC4">
-        <v>765</v>
+        <v>779</v>
       </c>
       <c r="AD4" t="str">
         <v/>
@@ -932,7 +932,7 @@
         <v>0</v>
       </c>
       <c r="AR4">
-        <v>385</v>
+        <v>511</v>
       </c>
     </row>
     <row r="5">
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>626</v>
+        <v>698</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="AC5">
-        <v>671</v>
+        <v>711</v>
       </c>
       <c r="AD5" t="str">
         <v/>
@@ -1066,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="AR5">
-        <v>1083</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="6">
@@ -1110,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1036</v>
+        <v>1133</v>
       </c>
       <c r="O6" t="str">
         <v/>
@@ -1140,7 +1140,7 @@
         <v>0</v>
       </c>
       <c r="X6">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="Y6" t="str">
         <v/>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="AN6" t="str">
         <v/>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="AR6">
-        <v>771</v>
+        <v>777</v>
       </c>
     </row>
     <row r="7">
@@ -1259,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>885</v>
+        <v>899</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -1274,7 +1274,7 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>732</v>
+        <v>820</v>
       </c>
       <c r="Y7" t="str">
         <v/>
@@ -1304,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="AH7">
-        <v>1089</v>
+        <v>1111</v>
       </c>
       <c r="AI7" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>700</v>
+        <v>804</v>
       </c>
       <c r="AN7" t="str">
         <v/>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="AR7">
-        <v>694</v>
+        <v>698</v>
       </c>
     </row>
     <row r="8">
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>394</v>
+        <v>421</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -1363,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>448</v>
+        <v>484</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -1378,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>292</v>
+        <v>410</v>
       </c>
       <c r="O8" t="str">
         <v/>
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>611</v>
+        <v>659</v>
       </c>
       <c r="Y8" t="str">
         <v/>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="AH8">
-        <v>837</v>
+        <v>990</v>
       </c>
       <c r="AI8" t="str">
         <v/>
@@ -1453,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>838</v>
+        <v>861</v>
       </c>
       <c r="AN8" t="str">
         <v/>
@@ -1468,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="AR8">
-        <v>988</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="9">
@@ -1512,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>919</v>
+        <v>1036</v>
       </c>
       <c r="O9" t="str">
         <v/>
@@ -1572,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="AH9">
-        <v>484</v>
+        <v>551</v>
       </c>
       <c r="AI9" t="str">
         <v/>
@@ -1616,7 +1616,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>716</v>
+        <v>866</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -1631,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>1117</v>
+        <v>1201</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -1646,7 +1646,7 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="O10" t="str">
         <v/>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>800</v>
+        <v>810</v>
       </c>
       <c r="Y10" t="str">
         <v/>
@@ -1721,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>673</v>
+        <v>814</v>
       </c>
       <c r="AN10" t="str">
         <v/>
@@ -1750,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>986</v>
+        <v>1291</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>1004</v>
+        <v>1128</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>924</v>
+        <v>1029</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -1810,7 +1810,7 @@
         <v>0</v>
       </c>
       <c r="X11">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="Y11" t="str">
         <v/>
@@ -1825,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="AC11">
-        <v>519</v>
+        <v>632</v>
       </c>
       <c r="AD11" t="str">
         <v/>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>983</v>
+        <v>1152</v>
       </c>
       <c r="AN11" t="str">
         <v/>
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="AR11">
-        <v>571</v>
+        <v>650</v>
       </c>
     </row>
     <row r="12">
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>995</v>
+        <v>1108</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -1914,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <v>773</v>
+        <v>1163</v>
       </c>
       <c r="O12" t="str">
         <v/>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="S12">
-        <v>274</v>
+        <v>411</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -1944,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <v>574</v>
+        <v>616</v>
       </c>
       <c r="Y12" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="AC12">
-        <v>828</v>
+        <v>841</v>
       </c>
       <c r="AD12" t="str">
         <v/>
@@ -1989,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>404</v>
+        <v>520</v>
       </c>
       <c r="AN12" t="str">
         <v/>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="AR12">
-        <v>928</v>
+        <v>934</v>
       </c>
     </row>
     <row r="13">
@@ -2018,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>485</v>
+        <v>513</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -2048,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="O13" t="str">
         <v/>
@@ -2063,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="S13">
-        <v>520</v>
+        <v>592</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>684</v>
+        <v>854</v>
       </c>
       <c r="AN13" t="str">
         <v/>
@@ -2197,7 +2197,7 @@
         <v/>
       </c>
       <c r="S14">
-        <v>418</v>
+        <v>497</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -2837,7 +2837,7 @@
         <v/>
       </c>
       <c r="I19">
-        <v>267</v>
+        <v>315</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -3165,7 +3165,7 @@
         <v/>
       </c>
       <c r="AC21">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AD21" t="str">
         <v/>
@@ -3224,7 +3224,7 @@
         <v/>
       </c>
       <c r="D22">
-        <v>358</v>
+        <v>459</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="AC24">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="AD24" t="str">
         <v/>
@@ -3775,7 +3775,7 @@
         <v/>
       </c>
       <c r="I26">
-        <v>185</v>
+        <v>311</v>
       </c>
       <c r="J26" t="str">
         <v/>
@@ -3969,7 +3969,7 @@
         <v/>
       </c>
       <c r="AC27">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AD27" t="str">
         <v/>
@@ -4058,7 +4058,7 @@
         <v/>
       </c>
       <c r="N28">
-        <v>230</v>
+        <v>300</v>
       </c>
       <c r="O28" t="str">
         <v/>
@@ -4177,7 +4177,7 @@
         <v/>
       </c>
       <c r="I29">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="J29" t="str">
         <v/>
@@ -4430,7 +4430,7 @@
         <v/>
       </c>
       <c r="D31">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -4669,7 +4669,7 @@
         <v/>
       </c>
       <c r="AM32">
-        <v>124</v>
+        <v>179</v>
       </c>
       <c r="AN32" t="str">
         <v/>
@@ -4803,7 +4803,7 @@
         <v/>
       </c>
       <c r="AM33">
-        <v>264</v>
+        <v>368</v>
       </c>
       <c r="AN33" t="str">
         <v/>
@@ -4922,7 +4922,7 @@
         <v/>
       </c>
       <c r="AH34">
-        <v>657</v>
+        <v>671</v>
       </c>
       <c r="AI34" t="str">
         <v/>
@@ -5488,7 +5488,7 @@
         <v/>
       </c>
       <c r="AR38">
-        <v>758</v>
+        <v>810</v>
       </c>
     </row>
     <row r="39">
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>4864</v>
+        <v>5761</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>5188</v>
+        <v>5777</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>6664</v>
+        <v>7657</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>4659</v>
+        <v>5232</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="X45">
-        <v>5265</v>
+        <v>5486</v>
       </c>
       <c r="Y45" t="str">
         <v/>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AC45">
-        <v>5029</v>
+        <v>5283</v>
       </c>
       <c r="AD45" t="str">
         <v/>
@@ -6396,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="AH45">
-        <v>6250</v>
+        <v>6612</v>
       </c>
       <c r="AI45" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>6141</v>
+        <v>7041</v>
       </c>
       <c r="AN45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>7197</v>
+        <v>7614</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1090</v>
+        <v>1330</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -723,7 +723,7 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>968</v>
+        <v>1187</v>
       </c>
       <c r="T3" t="str">
         <v/>
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="AC3">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="AD3" t="str">
         <v/>
@@ -768,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="AH3">
-        <v>567</v>
+        <v>699</v>
       </c>
       <c r="AI3" t="str">
         <v/>
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>381</v>
+        <v>503</v>
       </c>
       <c r="AN3" t="str">
         <v/>
@@ -812,7 +812,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>674</v>
+        <v>766</v>
       </c>
       <c r="T4" t="str">
         <v/>
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="AC4">
-        <v>779</v>
+        <v>906</v>
       </c>
       <c r="AD4" t="str">
         <v/>
@@ -902,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="AH4">
-        <v>552</v>
+        <v>585</v>
       </c>
       <c r="AI4" t="str">
         <v/>
@@ -932,7 +932,7 @@
         <v>0</v>
       </c>
       <c r="AR4">
-        <v>511</v>
+        <v>624</v>
       </c>
     </row>
     <row r="5">
@@ -946,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>268</v>
+        <v>421</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="AC5">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="AD5" t="str">
         <v/>
@@ -1066,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="AR5">
-        <v>1135</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="6">
@@ -1110,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1133</v>
+        <v>1292</v>
       </c>
       <c r="O6" t="str">
         <v/>
@@ -1140,7 +1140,7 @@
         <v>0</v>
       </c>
       <c r="X6">
-        <v>167</v>
+        <v>248</v>
       </c>
       <c r="Y6" t="str">
         <v/>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="AR6">
-        <v>777</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="7">
@@ -1244,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>719</v>
+        <v>927</v>
       </c>
       <c r="O7" t="str">
         <v/>
@@ -1259,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>899</v>
+        <v>1039</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -1274,7 +1274,7 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>820</v>
+        <v>952</v>
       </c>
       <c r="Y7" t="str">
         <v/>
@@ -1304,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="AH7">
-        <v>1111</v>
+        <v>1424</v>
       </c>
       <c r="AI7" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>804</v>
+        <v>949</v>
       </c>
       <c r="AN7" t="str">
         <v/>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="AR7">
-        <v>698</v>
+        <v>761</v>
       </c>
     </row>
     <row r="8">
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>421</v>
+        <v>493</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -1363,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>484</v>
+        <v>566</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -1378,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>410</v>
+        <v>454</v>
       </c>
       <c r="O8" t="str">
         <v/>
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>659</v>
+        <v>747</v>
       </c>
       <c r="Y8" t="str">
         <v/>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="AH8">
-        <v>990</v>
+        <v>1419</v>
       </c>
       <c r="AI8" t="str">
         <v/>
@@ -1453,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>861</v>
+        <v>1062</v>
       </c>
       <c r="AN8" t="str">
         <v/>
@@ -1468,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="AR8">
-        <v>1080</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="9">
@@ -1512,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="O9" t="str">
         <v/>
@@ -1542,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>480</v>
+        <v>618</v>
       </c>
       <c r="Y9" t="str">
         <v/>
@@ -1572,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="AH9">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AI9" t="str">
         <v/>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>779</v>
+        <v>1078</v>
       </c>
       <c r="AN9" t="str">
         <v/>
@@ -1602,7 +1602,7 @@
         <v>0</v>
       </c>
       <c r="AR9">
-        <v>601</v>
+        <v>741</v>
       </c>
     </row>
     <row r="10">
@@ -1616,7 +1616,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>866</v>
+        <v>972</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -1631,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>1201</v>
+        <v>1313</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>375</v>
+        <v>443</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="Y10" t="str">
         <v/>
@@ -1691,7 +1691,7 @@
         <v>0</v>
       </c>
       <c r="AC10">
-        <v>515</v>
+        <v>617</v>
       </c>
       <c r="AD10" t="str">
         <v/>
@@ -1706,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="AH10">
-        <v>409</v>
+        <v>552</v>
       </c>
       <c r="AI10" t="str">
         <v/>
@@ -1721,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>814</v>
+        <v>933</v>
       </c>
       <c r="AN10" t="str">
         <v/>
@@ -1750,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1291</v>
+        <v>1722</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>1128</v>
+        <v>1248</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>1029</v>
+        <v>1276</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -1810,7 +1810,7 @@
         <v>0</v>
       </c>
       <c r="X11">
-        <v>624</v>
+        <v>660</v>
       </c>
       <c r="Y11" t="str">
         <v/>
@@ -1825,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="AC11">
-        <v>632</v>
+        <v>751</v>
       </c>
       <c r="AD11" t="str">
         <v/>
@@ -1840,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="AH11">
-        <v>742</v>
+        <v>791</v>
       </c>
       <c r="AI11" t="str">
         <v/>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>1152</v>
+        <v>1530</v>
       </c>
       <c r="AN11" t="str">
         <v/>
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="AR11">
-        <v>650</v>
+        <v>696</v>
       </c>
     </row>
     <row r="12">
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>1108</v>
+        <v>1416</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="S12">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -1944,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <v>616</v>
+        <v>662</v>
       </c>
       <c r="Y12" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="AC12">
-        <v>841</v>
+        <v>1052</v>
       </c>
       <c r="AD12" t="str">
         <v/>
@@ -1989,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="AN12" t="str">
         <v/>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="AR12">
-        <v>934</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="13">
@@ -2018,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>500</v>
+        <v>588</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>513</v>
+        <v>681</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -2048,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>354</v>
+        <v>451</v>
       </c>
       <c r="O13" t="str">
         <v/>
@@ -2063,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="S13">
-        <v>592</v>
+        <v>637</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -2078,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>956</v>
+        <v>1012</v>
       </c>
       <c r="Y13" t="str">
         <v/>
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>854</v>
+        <v>866</v>
       </c>
       <c r="AN13" t="str">
         <v/>
@@ -2197,7 +2197,7 @@
         <v/>
       </c>
       <c r="S14">
-        <v>497</v>
+        <v>541</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -2778,7 +2778,7 @@
         <v/>
       </c>
       <c r="AH18">
-        <v>212</v>
+        <v>312</v>
       </c>
       <c r="AI18" t="str">
         <v/>
@@ -2837,7 +2837,7 @@
         <v/>
       </c>
       <c r="I19">
-        <v>315</v>
+        <v>388</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -3001,7 +3001,7 @@
         <v/>
       </c>
       <c r="S20">
-        <v>322</v>
+        <v>354</v>
       </c>
       <c r="T20" t="str">
         <v/>
@@ -3224,7 +3224,7 @@
         <v/>
       </c>
       <c r="D22">
-        <v>459</v>
+        <v>570</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -3433,7 +3433,7 @@
         <v/>
       </c>
       <c r="AC23">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="AD23" t="str">
         <v/>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="AC24">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AD24" t="str">
         <v/>
@@ -3969,7 +3969,7 @@
         <v/>
       </c>
       <c r="AC27">
-        <v>375</v>
+        <v>465</v>
       </c>
       <c r="AD27" t="str">
         <v/>
@@ -4058,7 +4058,7 @@
         <v/>
       </c>
       <c r="N28">
-        <v>300</v>
+        <v>444</v>
       </c>
       <c r="O28" t="str">
         <v/>
@@ -4177,7 +4177,7 @@
         <v/>
       </c>
       <c r="I29">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="J29" t="str">
         <v/>
@@ -4430,7 +4430,7 @@
         <v/>
       </c>
       <c r="D31">
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -4803,7 +4803,7 @@
         <v/>
       </c>
       <c r="AM33">
-        <v>368</v>
+        <v>443</v>
       </c>
       <c r="AN33" t="str">
         <v/>
@@ -4922,7 +4922,7 @@
         <v/>
       </c>
       <c r="AH34">
-        <v>671</v>
+        <v>865</v>
       </c>
       <c r="AI34" t="str">
         <v/>
@@ -5115,7 +5115,7 @@
         <v/>
       </c>
       <c r="I36">
-        <v>72</v>
+        <v>323</v>
       </c>
       <c r="J36" t="str">
         <v/>
@@ -5234,7 +5234,7 @@
         <v/>
       </c>
       <c r="D37">
-        <v>41</v>
+        <v>184</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -5488,7 +5488,7 @@
         <v/>
       </c>
       <c r="AR38">
-        <v>810</v>
+        <v>999</v>
       </c>
     </row>
     <row r="39">
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>5761</v>
+        <v>7162</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>5777</v>
+        <v>6901</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>7657</v>
+        <v>8565</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>5232</v>
+        <v>5882</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="X45">
-        <v>5486</v>
+        <v>6065</v>
       </c>
       <c r="Y45" t="str">
         <v/>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AC45">
-        <v>5283</v>
+        <v>5976</v>
       </c>
       <c r="AD45" t="str">
         <v/>
@@ -6396,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="AH45">
-        <v>6612</v>
+        <v>8009</v>
       </c>
       <c r="AI45" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>7041</v>
+        <v>8398</v>
       </c>
       <c r="AN45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>7614</v>
+        <v>8890</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -857,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>766</v>
+        <v>852</v>
       </c>
       <c r="T4" t="str">
         <v/>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="AR6">
-        <v>1063</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="7">
@@ -1259,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>1039</v>
+        <v>1146</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -1304,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="AH7">
-        <v>1424</v>
+        <v>1485</v>
       </c>
       <c r="AI7" t="str">
         <v/>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="AR7">
-        <v>761</v>
+        <v>845</v>
       </c>
     </row>
     <row r="8">
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>1078</v>
+        <v>1123</v>
       </c>
       <c r="AN9" t="str">
         <v/>
@@ -1602,7 +1602,7 @@
         <v>0</v>
       </c>
       <c r="AR9">
-        <v>741</v>
+        <v>751</v>
       </c>
     </row>
     <row r="10">
@@ -1631,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>1313</v>
+        <v>1401</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>1248</v>
+        <v>1399</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>1276</v>
+        <v>1309</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>1530</v>
+        <v>1552</v>
       </c>
       <c r="AN11" t="str">
         <v/>
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>1416</v>
+        <v>1440</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -2063,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="S13">
-        <v>637</v>
+        <v>685</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -3224,7 +3224,7 @@
         <v/>
       </c>
       <c r="D22">
-        <v>570</v>
+        <v>583</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="AC24">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="AD24" t="str">
         <v/>
@@ -4922,7 +4922,7 @@
         <v/>
       </c>
       <c r="AH34">
-        <v>865</v>
+        <v>892</v>
       </c>
       <c r="AI34" t="str">
         <v/>
@@ -5488,7 +5488,7 @@
         <v/>
       </c>
       <c r="AR38">
-        <v>999</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="39">
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>7162</v>
+        <v>9029</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>6901</v>
+        <v>9074</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>8565</v>
+        <v>10329.5</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>5882</v>
+        <v>6965.5</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="X45">
-        <v>6065</v>
+        <v>7036</v>
       </c>
       <c r="Y45" t="str">
         <v/>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AC45">
-        <v>5976</v>
+        <v>7348.5</v>
       </c>
       <c r="AD45" t="str">
         <v/>
@@ -6396,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="AH45">
-        <v>8009</v>
+        <v>9391.5</v>
       </c>
       <c r="AI45" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>8398</v>
+        <v>10483.5</v>
       </c>
       <c r="AN45" t="str">
         <v/>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AR46">
-        <v>8890</v>
+        <v>10440.5</v>
       </c>
     </row>
   </sheetData>
